--- a/data/raw/Plan de accion/PA_2.xlsx
+++ b/data/raw/Plan de accion/PA_2.xlsx
@@ -1,21 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Sistema_Indicadores_Poli/data/raw/Plan de accion/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_C4BD844F18F46918874719FA9983E268DB8A1E7B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E29A010E-3510-4FF0-9024-EA98931DC292}"/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Worksheet" sheetId="1" r:id="rId4"/>
+    <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="999999" calcMode="auto" calcCompleted="0" fullCalcOnLoad="1"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Worksheet!$A$1:$AE$422</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5732" uniqueCount="1181">
   <si>
     <t>Id Acción</t>
   </si>
@@ -3860,26 +3868,19 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xml:space="preserve">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ h:mm"/>
+    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <b val="1"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
+      <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
@@ -3890,14 +3891,11 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF"/>
+        <fgColor rgb="FF0FFFFF"/>
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
@@ -3909,113 +3907,132 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFff0667"/>
+        <fgColor rgb="FFFF0667"/>
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFffff00"/>
+        <fgColor rgb="FFFFFF00"/>
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF99cc00"/>
+        <fgColor rgb="FF99CC00"/>
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
   </fills>
   <borders count="3">
-    <border/>
     <border>
-      <left style="thin">
-        <color rgb="00000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="00000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="00000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00000000"/>
-      </bottom>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="00000000"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="thin">
-        <color rgb="00000000"/>
+        <color rgb="FF000000"/>
       </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
       <bottom style="thin">
-        <color rgb="00000000"/>
+        <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="17">
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="2" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf xfId="0" fontId="0" numFmtId="164" fillId="0" borderId="2" applyFont="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    <xf numFmtId="10" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf xfId="0" fontId="0" numFmtId="10" fillId="2" borderId="2" applyFont="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="2" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf xfId="0" fontId="0" numFmtId="165" fillId="0" borderId="2" applyFont="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="1" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf xfId="0" fontId="0" numFmtId="164" fillId="0" borderId="1" applyFont="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    <xf numFmtId="10" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf xfId="0" fontId="0" numFmtId="10" fillId="3" borderId="1" applyFont="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="1" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf xfId="0" fontId="0" numFmtId="165" fillId="0" borderId="1" applyFont="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    <xf numFmtId="10" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf xfId="0" fontId="0" numFmtId="10" fillId="2" borderId="1" applyFont="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    <xf numFmtId="10" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf xfId="0" fontId="0" numFmtId="10" fillId="4" borderId="1" applyFont="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    <xf numFmtId="10" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf xfId="0" fontId="0" numFmtId="10" fillId="5" borderId="1" applyFont="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="10" fillId="6" borderId="1" applyFont="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    <xf numFmtId="10" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotTableStyle1"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4304,48 +4321,43 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
-  <dimension ref="A1:AF422"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AE422"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="30" max="30" width="8" bestFit="true" customWidth="true" style="0"/>
-    <col min="31" max="31" width="13" bestFit="true" customWidth="true" style="0"/>
-    <col min="32" max="32" width="9.10" bestFit="true" style="0"/>
-    <col min="1" max="1" width="11" bestFit="true" customWidth="true" style="0"/>
-    <col min="2" max="2" width="19" bestFit="true" customWidth="true" style="0"/>
-    <col min="3" max="3" width="21" bestFit="true" customWidth="true" style="0"/>
-    <col min="4" max="4" width="12" bestFit="true" customWidth="true" style="0"/>
-    <col min="5" max="5" width="28" bestFit="true" customWidth="true" style="0"/>
-    <col min="6" max="6" width="36" bestFit="true" customWidth="true" style="0"/>
-    <col min="7" max="7" width="50" customWidth="true" style="1"/>
-    <col min="8" max="8" width="50" customWidth="true" style="1"/>
-    <col min="9" max="9" width="29" bestFit="true" customWidth="true" style="0"/>
-    <col min="10" max="10" width="1655" bestFit="true" customWidth="true" style="0"/>
-    <col min="11" max="11" width="700" bestFit="true" customWidth="true" style="0"/>
-    <col min="12" max="12" width="71" bestFit="true" customWidth="true" style="0"/>
-    <col min="13" max="13" width="42" bestFit="true" customWidth="true" style="0"/>
-    <col min="14" max="14" width="30" bestFit="true" customWidth="true" style="0"/>
-    <col min="15" max="15" width="36" bestFit="true" customWidth="true" style="0"/>
-    <col min="16" max="16" width="50" customWidth="true" style="1"/>
-    <col min="17" max="17" width="31" bestFit="true" customWidth="true" style="0"/>
-    <col min="18" max="18" width="48" bestFit="true" customWidth="true" style="0"/>
-    <col min="19" max="19" width="31" bestFit="true" customWidth="true" style="0"/>
-    <col min="20" max="20" width="1172" bestFit="true" customWidth="true" style="0"/>
-    <col min="21" max="21" width="50" customWidth="true" style="1"/>
-    <col min="22" max="22" width="11" bestFit="true" customWidth="true" style="0"/>
-    <col min="23" max="23" width="11" bestFit="true" customWidth="true" style="0"/>
-    <col min="24" max="24" width="1172" bestFit="true" customWidth="true" style="0"/>
-    <col min="25" max="25" width="26" bestFit="true" customWidth="true" style="0"/>
-    <col min="26" max="26" width="1387" bestFit="true" customWidth="true" style="0"/>
-    <col min="27" max="27" width="28" bestFit="true" customWidth="true" style="0"/>
-    <col min="28" max="28" width="1206" bestFit="true" customWidth="true" style="0"/>
-    <col min="29" max="29" width="29" bestFit="true" customWidth="true" style="0"/>
+    <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="36" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="50" style="1" customWidth="1"/>
+    <col min="9" max="9" width="29" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="1655" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="700" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="71" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="42" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="30" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="36" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="50" style="1" customWidth="1"/>
+    <col min="17" max="17" width="31" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="48" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="31" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="1172" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="50" style="1" customWidth="1"/>
+    <col min="22" max="23" width="11" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="1172" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="26" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="1387" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="28" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="1206" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="29" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="8" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="13" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="9.109375" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" customHeight="1" ht="25">
+    <row r="1" spans="1:31" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -4440,12 +4452,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:32">
+    <row r="2" spans="1:31" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A2" s="8">
         <v>1141</v>
       </c>
       <c r="B2" s="9">
-        <v>45224.751793981</v>
+        <v>45224.751793980999</v>
       </c>
       <c r="C2" s="8" t="s">
         <v>29</v>
@@ -4519,12 +4531,12 @@
       <c r="AD2" s="8"/>
       <c r="AE2" s="8"/>
     </row>
-    <row r="3" spans="1:32">
+    <row r="3" spans="1:31" ht="72" x14ac:dyDescent="0.3">
       <c r="A3" s="8">
         <v>1142</v>
       </c>
       <c r="B3" s="9">
-        <v>45224.752685185</v>
+        <v>45224.752685184998</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>29</v>
@@ -4598,12 +4610,12 @@
       <c r="AD3" s="8"/>
       <c r="AE3" s="8"/>
     </row>
-    <row r="4" spans="1:32">
+    <row r="4" spans="1:31" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A4" s="8">
         <v>1244</v>
       </c>
       <c r="B4" s="9">
-        <v>45371.669421296</v>
+        <v>45371.669421295999</v>
       </c>
       <c r="C4" s="8" t="s">
         <v>46</v>
@@ -4677,12 +4689,12 @@
       <c r="AD4" s="8"/>
       <c r="AE4" s="8"/>
     </row>
-    <row r="5" spans="1:32">
+    <row r="5" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="8">
         <v>1280</v>
       </c>
       <c r="B5" s="9">
-        <v>45499.425752315</v>
+        <v>45499.425752315001</v>
       </c>
       <c r="C5" s="8" t="s">
         <v>29</v>
@@ -4756,12 +4768,12 @@
       <c r="AD5" s="8"/>
       <c r="AE5" s="8"/>
     </row>
-    <row r="6" spans="1:32">
+    <row r="6" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="8">
         <v>1285</v>
       </c>
       <c r="B6" s="9">
-        <v>45509.483344907</v>
+        <v>45509.483344906999</v>
       </c>
       <c r="C6" s="8" t="s">
         <v>29</v>
@@ -4827,12 +4839,12 @@
       <c r="AD6" s="8"/>
       <c r="AE6" s="8"/>
     </row>
-    <row r="7" spans="1:32">
+    <row r="7" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="8">
         <v>1292</v>
       </c>
       <c r="B7" s="9">
-        <v>45510.43349537</v>
+        <v>45510.433495370002</v>
       </c>
       <c r="C7" s="8" t="s">
         <v>69</v>
@@ -4896,12 +4908,12 @@
       <c r="AD7" s="8"/>
       <c r="AE7" s="8"/>
     </row>
-    <row r="8" spans="1:32">
+    <row r="8" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="8">
         <v>1293</v>
       </c>
       <c r="B8" s="9">
-        <v>45510.439074074</v>
+        <v>45510.439074073998</v>
       </c>
       <c r="C8" s="8" t="s">
         <v>69</v>
@@ -4965,12 +4977,12 @@
       <c r="AD8" s="8"/>
       <c r="AE8" s="8"/>
     </row>
-    <row r="9" spans="1:32">
+    <row r="9" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="8">
         <v>1294</v>
       </c>
       <c r="B9" s="9">
-        <v>45510.448240741</v>
+        <v>45510.448240741003</v>
       </c>
       <c r="C9" s="8" t="s">
         <v>69</v>
@@ -5034,12 +5046,12 @@
       <c r="AD9" s="8"/>
       <c r="AE9" s="8"/>
     </row>
-    <row r="10" spans="1:32">
+    <row r="10" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="8">
         <v>1295</v>
       </c>
       <c r="B10" s="9">
-        <v>45510.450138889</v>
+        <v>45510.450138888998</v>
       </c>
       <c r="C10" s="8" t="s">
         <v>69</v>
@@ -5103,12 +5115,12 @@
       <c r="AD10" s="8"/>
       <c r="AE10" s="8"/>
     </row>
-    <row r="11" spans="1:32">
+    <row r="11" spans="1:31" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A11" s="8">
         <v>1308</v>
       </c>
       <c r="B11" s="9">
-        <v>45531.479641204</v>
+        <v>45531.479641204001</v>
       </c>
       <c r="C11" s="8" t="s">
         <v>69</v>
@@ -5180,12 +5192,12 @@
       <c r="AD11" s="8"/>
       <c r="AE11" s="8"/>
     </row>
-    <row r="12" spans="1:32">
+    <row r="12" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="8">
         <v>1328</v>
       </c>
       <c r="B12" s="9">
-        <v>45538.343819444</v>
+        <v>45538.343819444002</v>
       </c>
       <c r="C12" s="8" t="s">
         <v>69</v>
@@ -5259,12 +5271,12 @@
       <c r="AD12" s="8"/>
       <c r="AE12" s="8"/>
     </row>
-    <row r="13" spans="1:32">
+    <row r="13" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="8">
         <v>1332</v>
       </c>
       <c r="B13" s="9">
-        <v>45544.496828704</v>
+        <v>45544.496828704003</v>
       </c>
       <c r="C13" s="8" t="s">
         <v>46</v>
@@ -5326,12 +5338,12 @@
       <c r="AD13" s="8"/>
       <c r="AE13" s="8"/>
     </row>
-    <row r="14" spans="1:32">
+    <row r="14" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A14" s="8">
         <v>1333</v>
       </c>
       <c r="B14" s="9">
-        <v>45544.497673611</v>
+        <v>45544.497673610997</v>
       </c>
       <c r="C14" s="8" t="s">
         <v>46</v>
@@ -5393,12 +5405,12 @@
       <c r="AD14" s="8"/>
       <c r="AE14" s="8"/>
     </row>
-    <row r="15" spans="1:32">
+    <row r="15" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A15" s="8">
         <v>1334</v>
       </c>
       <c r="B15" s="9">
-        <v>45544.498229167</v>
+        <v>45544.498229167002</v>
       </c>
       <c r="C15" s="8" t="s">
         <v>46</v>
@@ -5460,12 +5472,12 @@
       <c r="AD15" s="8"/>
       <c r="AE15" s="8"/>
     </row>
-    <row r="16" spans="1:32">
+    <row r="16" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A16" s="8">
         <v>1335</v>
       </c>
       <c r="B16" s="9">
-        <v>45544.498969907</v>
+        <v>45544.498969906999</v>
       </c>
       <c r="C16" s="8" t="s">
         <v>46</v>
@@ -5527,12 +5539,12 @@
       <c r="AD16" s="8"/>
       <c r="AE16" s="8"/>
     </row>
-    <row r="17" spans="1:32">
+    <row r="17" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A17" s="8">
         <v>1336</v>
       </c>
       <c r="B17" s="9">
-        <v>45544.599965278</v>
+        <v>45544.599965278001</v>
       </c>
       <c r="C17" s="8" t="s">
         <v>46</v>
@@ -5600,12 +5612,12 @@
       <c r="AD17" s="8"/>
       <c r="AE17" s="8"/>
     </row>
-    <row r="18" spans="1:32">
+    <row r="18" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A18" s="8">
         <v>1337</v>
       </c>
       <c r="B18" s="9">
-        <v>45544.600821759</v>
+        <v>45544.600821758999</v>
       </c>
       <c r="C18" s="8" t="s">
         <v>46</v>
@@ -5671,7 +5683,7 @@
       <c r="AD18" s="8"/>
       <c r="AE18" s="8"/>
     </row>
-    <row r="19" spans="1:32">
+    <row r="19" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A19" s="8">
         <v>1338</v>
       </c>
@@ -5742,7 +5754,7 @@
       <c r="AD19" s="8"/>
       <c r="AE19" s="8"/>
     </row>
-    <row r="20" spans="1:32">
+    <row r="20" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A20" s="8">
         <v>1339</v>
       </c>
@@ -5821,12 +5833,12 @@
       <c r="AD20" s="8"/>
       <c r="AE20" s="8"/>
     </row>
-    <row r="21" spans="1:32">
+    <row r="21" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A21" s="8">
         <v>1340</v>
       </c>
       <c r="B21" s="9">
-        <v>45544.611759259</v>
+        <v>45544.611759259002</v>
       </c>
       <c r="C21" s="8" t="s">
         <v>46</v>
@@ -5900,12 +5912,12 @@
       <c r="AD21" s="8"/>
       <c r="AE21" s="8"/>
     </row>
-    <row r="22" spans="1:32">
+    <row r="22" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A22" s="8">
         <v>1341</v>
       </c>
       <c r="B22" s="9">
-        <v>45544.612546296</v>
+        <v>45544.612546295997</v>
       </c>
       <c r="C22" s="8" t="s">
         <v>46</v>
@@ -5979,12 +5991,12 @@
       <c r="AD22" s="8"/>
       <c r="AE22" s="8"/>
     </row>
-    <row r="23" spans="1:32">
+    <row r="23" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A23" s="8">
         <v>1342</v>
       </c>
       <c r="B23" s="9">
-        <v>45544.613460648</v>
+        <v>45544.613460647997</v>
       </c>
       <c r="C23" s="8" t="s">
         <v>46</v>
@@ -6058,7 +6070,7 @@
       <c r="AD23" s="8"/>
       <c r="AE23" s="8"/>
     </row>
-    <row r="24" spans="1:32">
+    <row r="24" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A24" s="8">
         <v>1343</v>
       </c>
@@ -6137,12 +6149,12 @@
       <c r="AD24" s="8"/>
       <c r="AE24" s="8"/>
     </row>
-    <row r="25" spans="1:32">
+    <row r="25" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A25" s="8">
         <v>1344</v>
       </c>
       <c r="B25" s="9">
-        <v>45544.628391204</v>
+        <v>45544.628391204002</v>
       </c>
       <c r="C25" s="8" t="s">
         <v>46</v>
@@ -6216,12 +6228,12 @@
       <c r="AD25" s="8"/>
       <c r="AE25" s="8"/>
     </row>
-    <row r="26" spans="1:32">
+    <row r="26" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A26" s="8">
         <v>1345</v>
       </c>
       <c r="B26" s="9">
-        <v>45544.629606481</v>
+        <v>45544.629606481001</v>
       </c>
       <c r="C26" s="8" t="s">
         <v>46</v>
@@ -6295,12 +6307,12 @@
       <c r="AD26" s="8"/>
       <c r="AE26" s="8"/>
     </row>
-    <row r="27" spans="1:32">
+    <row r="27" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A27" s="8">
         <v>1346</v>
       </c>
       <c r="B27" s="9">
-        <v>45544.630405093</v>
+        <v>45544.630405092998</v>
       </c>
       <c r="C27" s="8" t="s">
         <v>46</v>
@@ -6374,12 +6386,12 @@
       <c r="AD27" s="8"/>
       <c r="AE27" s="8"/>
     </row>
-    <row r="28" spans="1:32">
+    <row r="28" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A28" s="8">
         <v>1347</v>
       </c>
       <c r="B28" s="9">
-        <v>45544.631145833</v>
+        <v>45544.631145833002</v>
       </c>
       <c r="C28" s="8" t="s">
         <v>46</v>
@@ -6453,7 +6465,7 @@
       <c r="AD28" s="8"/>
       <c r="AE28" s="8"/>
     </row>
-    <row r="29" spans="1:32">
+    <row r="29" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A29" s="8">
         <v>1348</v>
       </c>
@@ -6532,7 +6544,7 @@
       <c r="AD29" s="8"/>
       <c r="AE29" s="8"/>
     </row>
-    <row r="30" spans="1:32">
+    <row r="30" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A30" s="8">
         <v>1349</v>
       </c>
@@ -6611,12 +6623,12 @@
       <c r="AD30" s="8"/>
       <c r="AE30" s="8"/>
     </row>
-    <row r="31" spans="1:32">
+    <row r="31" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A31" s="8">
         <v>1350</v>
       </c>
       <c r="B31" s="9">
-        <v>45544.642488426</v>
+        <v>45544.642488425998</v>
       </c>
       <c r="C31" s="8" t="s">
         <v>46</v>
@@ -6690,12 +6702,12 @@
       <c r="AD31" s="8"/>
       <c r="AE31" s="8"/>
     </row>
-    <row r="32" spans="1:32">
+    <row r="32" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A32" s="8">
         <v>1351</v>
       </c>
       <c r="B32" s="9">
-        <v>45544.643449074</v>
+        <v>45544.643449073999</v>
       </c>
       <c r="C32" s="8" t="s">
         <v>46</v>
@@ -6769,12 +6781,12 @@
       <c r="AD32" s="8"/>
       <c r="AE32" s="8"/>
     </row>
-    <row r="33" spans="1:32">
+    <row r="33" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A33" s="8">
         <v>1353</v>
       </c>
       <c r="B33" s="9">
-        <v>45544.654791667</v>
+        <v>45544.654791667002</v>
       </c>
       <c r="C33" s="8" t="s">
         <v>46</v>
@@ -6848,12 +6860,12 @@
       <c r="AD33" s="8"/>
       <c r="AE33" s="8"/>
     </row>
-    <row r="34" spans="1:32">
+    <row r="34" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A34" s="8">
         <v>1354</v>
       </c>
       <c r="B34" s="9">
-        <v>45544.655972222</v>
+        <v>45544.655972221997</v>
       </c>
       <c r="C34" s="8" t="s">
         <v>46</v>
@@ -6927,12 +6939,12 @@
       <c r="AD34" s="8"/>
       <c r="AE34" s="8"/>
     </row>
-    <row r="35" spans="1:32">
+    <row r="35" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A35" s="8">
         <v>1355</v>
       </c>
       <c r="B35" s="9">
-        <v>45544.656840278</v>
+        <v>45544.656840278003</v>
       </c>
       <c r="C35" s="8" t="s">
         <v>46</v>
@@ -7006,12 +7018,12 @@
       <c r="AD35" s="8"/>
       <c r="AE35" s="8"/>
     </row>
-    <row r="36" spans="1:32">
+    <row r="36" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A36" s="8">
         <v>1356</v>
       </c>
       <c r="B36" s="9">
-        <v>45544.665069444</v>
+        <v>45544.665069444003</v>
       </c>
       <c r="C36" s="8" t="s">
         <v>46</v>
@@ -7085,12 +7097,12 @@
       <c r="AD36" s="8"/>
       <c r="AE36" s="8"/>
     </row>
-    <row r="37" spans="1:32">
+    <row r="37" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A37" s="8">
         <v>1357</v>
       </c>
       <c r="B37" s="9">
-        <v>45544.666006944</v>
+        <v>45544.666006943997</v>
       </c>
       <c r="C37" s="8" t="s">
         <v>46</v>
@@ -7164,12 +7176,12 @@
       <c r="AD37" s="8"/>
       <c r="AE37" s="8"/>
     </row>
-    <row r="38" spans="1:32">
+    <row r="38" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A38" s="8">
         <v>1358</v>
       </c>
       <c r="B38" s="9">
-        <v>45544.666770833</v>
+        <v>45544.666770832999</v>
       </c>
       <c r="C38" s="8" t="s">
         <v>46</v>
@@ -7243,12 +7255,12 @@
       <c r="AD38" s="8"/>
       <c r="AE38" s="8"/>
     </row>
-    <row r="39" spans="1:32">
+    <row r="39" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A39" s="8">
         <v>1359</v>
       </c>
       <c r="B39" s="9">
-        <v>45544.66775463</v>
+        <v>45544.667754629998</v>
       </c>
       <c r="C39" s="8" t="s">
         <v>46</v>
@@ -7322,12 +7334,12 @@
       <c r="AD39" s="8"/>
       <c r="AE39" s="8"/>
     </row>
-    <row r="40" spans="1:32">
+    <row r="40" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A40" s="8">
         <v>1360</v>
       </c>
       <c r="B40" s="9">
-        <v>45544.688148148</v>
+        <v>45544.688148148001</v>
       </c>
       <c r="C40" s="8" t="s">
         <v>46</v>
@@ -7401,12 +7413,12 @@
       <c r="AD40" s="8"/>
       <c r="AE40" s="8"/>
     </row>
-    <row r="41" spans="1:32">
+    <row r="41" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A41" s="8">
         <v>1361</v>
       </c>
       <c r="B41" s="9">
-        <v>45544.688981481</v>
+        <v>45544.688981480998</v>
       </c>
       <c r="C41" s="8" t="s">
         <v>46</v>
@@ -7480,12 +7492,12 @@
       <c r="AD41" s="8"/>
       <c r="AE41" s="8"/>
     </row>
-    <row r="42" spans="1:32">
+    <row r="42" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A42" s="8">
         <v>1362</v>
       </c>
       <c r="B42" s="9">
-        <v>45544.68962963</v>
+        <v>45544.689629629996</v>
       </c>
       <c r="C42" s="8" t="s">
         <v>46</v>
@@ -7559,12 +7571,12 @@
       <c r="AD42" s="8"/>
       <c r="AE42" s="8"/>
     </row>
-    <row r="43" spans="1:32">
+    <row r="43" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A43" s="8">
         <v>1363</v>
       </c>
       <c r="B43" s="9">
-        <v>45544.69068287</v>
+        <v>45544.690682870001</v>
       </c>
       <c r="C43" s="8" t="s">
         <v>46</v>
@@ -7640,7 +7652,7 @@
       <c r="AD43" s="8"/>
       <c r="AE43" s="8"/>
     </row>
-    <row r="44" spans="1:32">
+    <row r="44" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A44" s="8">
         <v>1364</v>
       </c>
@@ -7719,12 +7731,12 @@
       <c r="AD44" s="8"/>
       <c r="AE44" s="8"/>
     </row>
-    <row r="45" spans="1:32">
+    <row r="45" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A45" s="8">
         <v>1365</v>
       </c>
       <c r="B45" s="9">
-        <v>45544.696666667</v>
+        <v>45544.696666666998</v>
       </c>
       <c r="C45" s="8" t="s">
         <v>46</v>
@@ -7798,12 +7810,12 @@
       <c r="AD45" s="8"/>
       <c r="AE45" s="8"/>
     </row>
-    <row r="46" spans="1:32">
+    <row r="46" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A46" s="8">
         <v>1366</v>
       </c>
       <c r="B46" s="9">
-        <v>45544.697314815</v>
+        <v>45544.697314814999</v>
       </c>
       <c r="C46" s="8" t="s">
         <v>46</v>
@@ -7879,12 +7891,12 @@
       <c r="AD46" s="8"/>
       <c r="AE46" s="8"/>
     </row>
-    <row r="47" spans="1:32">
+    <row r="47" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A47" s="8">
         <v>1367</v>
       </c>
       <c r="B47" s="9">
-        <v>45544.69869213</v>
+        <v>45544.698692129998</v>
       </c>
       <c r="C47" s="8" t="s">
         <v>46</v>
@@ -7960,12 +7972,12 @@
       <c r="AD47" s="8"/>
       <c r="AE47" s="8"/>
     </row>
-    <row r="48" spans="1:32">
+    <row r="48" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A48" s="8">
         <v>1371</v>
       </c>
       <c r="B48" s="9">
-        <v>45544.710555556</v>
+        <v>45544.710555555997</v>
       </c>
       <c r="C48" s="8" t="s">
         <v>46</v>
@@ -8039,7 +8051,7 @@
       <c r="AD48" s="8"/>
       <c r="AE48" s="8"/>
     </row>
-    <row r="49" spans="1:32">
+    <row r="49" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A49" s="8">
         <v>1375</v>
       </c>
@@ -8118,12 +8130,12 @@
       <c r="AD49" s="8"/>
       <c r="AE49" s="8"/>
     </row>
-    <row r="50" spans="1:32">
+    <row r="50" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A50" s="8">
         <v>1377</v>
       </c>
       <c r="B50" s="9">
-        <v>45545.396979167</v>
+        <v>45545.396979167002</v>
       </c>
       <c r="C50" s="8" t="s">
         <v>46</v>
@@ -8197,12 +8209,12 @@
       <c r="AD50" s="8"/>
       <c r="AE50" s="8"/>
     </row>
-    <row r="51" spans="1:32">
+    <row r="51" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A51" s="8">
         <v>1378</v>
       </c>
       <c r="B51" s="9">
-        <v>45545.397581019</v>
+        <v>45545.397581019002</v>
       </c>
       <c r="C51" s="8" t="s">
         <v>46</v>
@@ -8276,12 +8288,12 @@
       <c r="AD51" s="8"/>
       <c r="AE51" s="8"/>
     </row>
-    <row r="52" spans="1:32">
+    <row r="52" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A52" s="8">
         <v>1379</v>
       </c>
       <c r="B52" s="9">
-        <v>45545.399212963</v>
+        <v>45545.399212962999</v>
       </c>
       <c r="C52" s="8" t="s">
         <v>46</v>
@@ -8353,12 +8365,12 @@
       <c r="AD52" s="8"/>
       <c r="AE52" s="8"/>
     </row>
-    <row r="53" spans="1:32">
+    <row r="53" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A53" s="8">
         <v>1382</v>
       </c>
       <c r="B53" s="9">
-        <v>45545.412789352</v>
+        <v>45545.412789351998</v>
       </c>
       <c r="C53" s="8" t="s">
         <v>46</v>
@@ -8432,12 +8444,12 @@
       <c r="AD53" s="8"/>
       <c r="AE53" s="8"/>
     </row>
-    <row r="54" spans="1:32">
+    <row r="54" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A54" s="8">
         <v>1383</v>
       </c>
       <c r="B54" s="9">
-        <v>45545.41349537</v>
+        <v>45545.413495369998</v>
       </c>
       <c r="C54" s="8" t="s">
         <v>46</v>
@@ -8511,12 +8523,12 @@
       <c r="AD54" s="8"/>
       <c r="AE54" s="8"/>
     </row>
-    <row r="55" spans="1:32">
+    <row r="55" spans="1:31" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A55" s="8">
         <v>1395</v>
       </c>
       <c r="B55" s="9">
-        <v>45554.472083333</v>
+        <v>45554.472083332999</v>
       </c>
       <c r="C55" s="8" t="s">
         <v>69</v>
@@ -8584,7 +8596,7 @@
       <c r="AD55" s="8"/>
       <c r="AE55" s="8"/>
     </row>
-    <row r="56" spans="1:32">
+    <row r="56" spans="1:31" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A56" s="8">
         <v>1401</v>
       </c>
@@ -8657,12 +8669,12 @@
       <c r="AD56" s="8"/>
       <c r="AE56" s="8"/>
     </row>
-    <row r="57" spans="1:32">
+    <row r="57" spans="1:31" ht="72" x14ac:dyDescent="0.3">
       <c r="A57" s="8">
         <v>1405</v>
       </c>
       <c r="B57" s="9">
-        <v>45555.424108796</v>
+        <v>45555.424108796004</v>
       </c>
       <c r="C57" s="8" t="s">
         <v>69</v>
@@ -8728,12 +8740,12 @@
       <c r="AD57" s="8"/>
       <c r="AE57" s="8"/>
     </row>
-    <row r="58" spans="1:32">
+    <row r="58" spans="1:31" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A58" s="8">
         <v>1406</v>
       </c>
       <c r="B58" s="9">
-        <v>45555.427326389</v>
+        <v>45555.427326388999</v>
       </c>
       <c r="C58" s="8" t="s">
         <v>69</v>
@@ -8801,7 +8813,7 @@
       <c r="AD58" s="8"/>
       <c r="AE58" s="8"/>
     </row>
-    <row r="59" spans="1:32">
+    <row r="59" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A59" s="8">
         <v>1413</v>
       </c>
@@ -8882,12 +8894,12 @@
       <c r="AD59" s="8"/>
       <c r="AE59" s="8"/>
     </row>
-    <row r="60" spans="1:32">
+    <row r="60" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A60" s="8">
         <v>1415</v>
       </c>
       <c r="B60" s="9">
-        <v>45566.5365625</v>
+        <v>45566.536562499998</v>
       </c>
       <c r="C60" s="8" t="s">
         <v>46</v>
@@ -8963,12 +8975,12 @@
       <c r="AD60" s="8"/>
       <c r="AE60" s="8"/>
     </row>
-    <row r="61" spans="1:32">
+    <row r="61" spans="1:31" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A61" s="8">
         <v>1433</v>
       </c>
       <c r="B61" s="9">
-        <v>45573.67931713</v>
+        <v>45573.679317130001</v>
       </c>
       <c r="C61" s="8" t="s">
         <v>238</v>
@@ -9042,7 +9054,7 @@
       <c r="AD61" s="8"/>
       <c r="AE61" s="8"/>
     </row>
-    <row r="62" spans="1:32">
+    <row r="62" spans="1:31" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A62" s="8">
         <v>1435</v>
       </c>
@@ -9117,12 +9129,12 @@
       <c r="AD62" s="8"/>
       <c r="AE62" s="8"/>
     </row>
-    <row r="63" spans="1:32">
+    <row r="63" spans="1:31" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A63" s="8">
         <v>1436</v>
       </c>
       <c r="B63" s="9">
-        <v>45575.982291667</v>
+        <v>45575.982291667002</v>
       </c>
       <c r="C63" s="8" t="s">
         <v>46</v>
@@ -9192,12 +9204,12 @@
       <c r="AD63" s="8"/>
       <c r="AE63" s="8"/>
     </row>
-    <row r="64" spans="1:32">
+    <row r="64" spans="1:31" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A64" s="8">
         <v>1437</v>
       </c>
       <c r="B64" s="9">
-        <v>45575.98349537</v>
+        <v>45575.983495369997</v>
       </c>
       <c r="C64" s="8" t="s">
         <v>46</v>
@@ -9267,12 +9279,12 @@
       <c r="AD64" s="8"/>
       <c r="AE64" s="8"/>
     </row>
-    <row r="65" spans="1:32">
+    <row r="65" spans="1:31" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A65" s="8">
         <v>1438</v>
       </c>
       <c r="B65" s="9">
-        <v>45576.343078704</v>
+        <v>45576.343078703998</v>
       </c>
       <c r="C65" s="8" t="s">
         <v>238</v>
@@ -9346,12 +9358,12 @@
       <c r="AD65" s="8"/>
       <c r="AE65" s="8"/>
     </row>
-    <row r="66" spans="1:32">
+    <row r="66" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A66" s="8">
         <v>1441</v>
       </c>
       <c r="B66" s="9">
-        <v>45576.554409722</v>
+        <v>45576.554409721997</v>
       </c>
       <c r="C66" s="8" t="s">
         <v>46</v>
@@ -9419,12 +9431,12 @@
       <c r="AD66" s="8"/>
       <c r="AE66" s="8"/>
     </row>
-    <row r="67" spans="1:32">
+    <row r="67" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A67" s="8">
         <v>1442</v>
       </c>
       <c r="B67" s="9">
-        <v>45576.555717593</v>
+        <v>45576.555717593001</v>
       </c>
       <c r="C67" s="8" t="s">
         <v>46</v>
@@ -9492,12 +9504,12 @@
       <c r="AD67" s="8"/>
       <c r="AE67" s="8"/>
     </row>
-    <row r="68" spans="1:32">
+    <row r="68" spans="1:31" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A68" s="8">
         <v>1445</v>
       </c>
       <c r="B68" s="9">
-        <v>45579.535856481</v>
+        <v>45579.535856481001</v>
       </c>
       <c r="C68" s="8" t="s">
         <v>46</v>
@@ -9567,12 +9579,12 @@
       <c r="AD68" s="8"/>
       <c r="AE68" s="8"/>
     </row>
-    <row r="69" spans="1:32">
+    <row r="69" spans="1:31" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A69" s="8">
         <v>1446</v>
       </c>
       <c r="B69" s="9">
-        <v>45579.537314815</v>
+        <v>45579.537314815003</v>
       </c>
       <c r="C69" s="8" t="s">
         <v>46</v>
@@ -9642,12 +9654,12 @@
       <c r="AD69" s="8"/>
       <c r="AE69" s="8"/>
     </row>
-    <row r="70" spans="1:32">
+    <row r="70" spans="1:31" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A70" s="8">
         <v>1447</v>
       </c>
       <c r="B70" s="9">
-        <v>45579.54056713</v>
+        <v>45579.540567130003</v>
       </c>
       <c r="C70" s="8" t="s">
         <v>46</v>
@@ -9717,12 +9729,12 @@
       <c r="AD70" s="8"/>
       <c r="AE70" s="8"/>
     </row>
-    <row r="71" spans="1:32">
+    <row r="71" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A71" s="8">
         <v>1468</v>
       </c>
       <c r="B71" s="9">
-        <v>45581.695543981</v>
+        <v>45581.695543980997</v>
       </c>
       <c r="C71" s="8" t="s">
         <v>46</v>
@@ -9786,12 +9798,12 @@
       <c r="AD71" s="8"/>
       <c r="AE71" s="8"/>
     </row>
-    <row r="72" spans="1:32">
+    <row r="72" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A72" s="8">
         <v>1469</v>
       </c>
       <c r="B72" s="9">
-        <v>45581.696875</v>
+        <v>45581.696875000001</v>
       </c>
       <c r="C72" s="8" t="s">
         <v>46</v>
@@ -9855,12 +9867,12 @@
       <c r="AD72" s="8"/>
       <c r="AE72" s="8"/>
     </row>
-    <row r="73" spans="1:32">
+    <row r="73" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A73" s="8">
         <v>1470</v>
       </c>
       <c r="B73" s="9">
-        <v>45581.697708333</v>
+        <v>45581.697708332998</v>
       </c>
       <c r="C73" s="8" t="s">
         <v>46</v>
@@ -9924,12 +9936,12 @@
       <c r="AD73" s="8"/>
       <c r="AE73" s="8"/>
     </row>
-    <row r="74" spans="1:32">
+    <row r="74" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A74" s="8">
         <v>1471</v>
       </c>
       <c r="B74" s="9">
-        <v>45581.698773148</v>
+        <v>45581.698773147997</v>
       </c>
       <c r="C74" s="8" t="s">
         <v>46</v>
@@ -9993,12 +10005,12 @@
       <c r="AD74" s="8"/>
       <c r="AE74" s="8"/>
     </row>
-    <row r="75" spans="1:32">
+    <row r="75" spans="1:31" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A75" s="8">
         <v>1476</v>
       </c>
       <c r="B75" s="9">
-        <v>45583.412581019</v>
+        <v>45583.412581019002</v>
       </c>
       <c r="C75" s="8" t="s">
         <v>46</v>
@@ -10064,12 +10076,12 @@
       <c r="AD75" s="8"/>
       <c r="AE75" s="8"/>
     </row>
-    <row r="76" spans="1:32">
+    <row r="76" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A76" s="8">
         <v>1478</v>
       </c>
       <c r="B76" s="9">
-        <v>45589.495601852</v>
+        <v>45589.495601852002</v>
       </c>
       <c r="C76" s="8" t="s">
         <v>238</v>
@@ -10143,7 +10155,7 @@
       <c r="AD76" s="8"/>
       <c r="AE76" s="8"/>
     </row>
-    <row r="77" spans="1:32">
+    <row r="77" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A77" s="8">
         <v>1479</v>
       </c>
@@ -10222,12 +10234,12 @@
       <c r="AD77" s="8"/>
       <c r="AE77" s="8"/>
     </row>
-    <row r="78" spans="1:32">
+    <row r="78" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A78" s="8">
         <v>1480</v>
       </c>
       <c r="B78" s="9">
-        <v>45589.497418981</v>
+        <v>45589.497418981002</v>
       </c>
       <c r="C78" s="8" t="s">
         <v>69</v>
@@ -10301,12 +10313,12 @@
       <c r="AD78" s="8"/>
       <c r="AE78" s="8"/>
     </row>
-    <row r="79" spans="1:32">
+    <row r="79" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A79" s="8">
         <v>1481</v>
       </c>
       <c r="B79" s="9">
-        <v>45589.498298611</v>
+        <v>45589.498298610997</v>
       </c>
       <c r="C79" s="8" t="s">
         <v>69</v>
@@ -10380,12 +10392,12 @@
       <c r="AD79" s="8"/>
       <c r="AE79" s="8"/>
     </row>
-    <row r="80" spans="1:32">
+    <row r="80" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A80" s="8">
         <v>1482</v>
       </c>
       <c r="B80" s="9">
-        <v>45589.498958333</v>
+        <v>45589.498958333003</v>
       </c>
       <c r="C80" s="8" t="s">
         <v>69</v>
@@ -10461,12 +10473,12 @@
       <c r="AD80" s="8"/>
       <c r="AE80" s="8"/>
     </row>
-    <row r="81" spans="1:32">
+    <row r="81" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A81" s="8">
         <v>1483</v>
       </c>
       <c r="B81" s="9">
-        <v>45589.499733796</v>
+        <v>45589.499733796001</v>
       </c>
       <c r="C81" s="8" t="s">
         <v>69</v>
@@ -10542,12 +10554,12 @@
       <c r="AD81" s="8"/>
       <c r="AE81" s="8"/>
     </row>
-    <row r="82" spans="1:32">
+    <row r="82" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A82" s="8">
         <v>1484</v>
       </c>
       <c r="B82" s="9">
-        <v>45589.500671296</v>
+        <v>45589.500671296002</v>
       </c>
       <c r="C82" s="8" t="s">
         <v>69</v>
@@ -10623,12 +10635,12 @@
       <c r="AD82" s="8"/>
       <c r="AE82" s="8"/>
     </row>
-    <row r="83" spans="1:32">
+    <row r="83" spans="1:31" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A83" s="8">
         <v>1485</v>
       </c>
       <c r="B83" s="9">
-        <v>45589.501921296</v>
+        <v>45589.501921296003</v>
       </c>
       <c r="C83" s="8" t="s">
         <v>69</v>
@@ -10702,12 +10714,12 @@
       <c r="AD83" s="8"/>
       <c r="AE83" s="8"/>
     </row>
-    <row r="84" spans="1:32">
+    <row r="84" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A84" s="8">
         <v>1487</v>
       </c>
       <c r="B84" s="9">
-        <v>45595.453900463</v>
+        <v>45595.453900462999</v>
       </c>
       <c r="C84" s="8" t="s">
         <v>69</v>
@@ -10769,12 +10781,12 @@
       <c r="AD84" s="8"/>
       <c r="AE84" s="8"/>
     </row>
-    <row r="85" spans="1:32">
+    <row r="85" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A85" s="8">
         <v>1489</v>
       </c>
       <c r="B85" s="9">
-        <v>45595.479398148</v>
+        <v>45595.479398148003</v>
       </c>
       <c r="C85" s="8" t="s">
         <v>69</v>
@@ -10836,12 +10848,12 @@
       <c r="AD85" s="8"/>
       <c r="AE85" s="8"/>
     </row>
-    <row r="86" spans="1:32">
+    <row r="86" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A86" s="8">
         <v>1490</v>
       </c>
       <c r="B86" s="9">
-        <v>45609.379756944</v>
+        <v>45609.379756943999</v>
       </c>
       <c r="C86" s="8" t="s">
         <v>238</v>
@@ -10915,12 +10927,12 @@
       <c r="AD86" s="8"/>
       <c r="AE86" s="8"/>
     </row>
-    <row r="87" spans="1:32">
+    <row r="87" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A87" s="8">
         <v>1491</v>
       </c>
       <c r="B87" s="9">
-        <v>45609.380659722</v>
+        <v>45609.380659722003</v>
       </c>
       <c r="C87" s="8" t="s">
         <v>238</v>
@@ -10994,12 +11006,12 @@
       <c r="AD87" s="8"/>
       <c r="AE87" s="8"/>
     </row>
-    <row r="88" spans="1:32">
+    <row r="88" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A88" s="8">
         <v>1492</v>
       </c>
       <c r="B88" s="9">
-        <v>45609.381782407</v>
+        <v>45609.381782406999</v>
       </c>
       <c r="C88" s="8" t="s">
         <v>69</v>
@@ -11073,7 +11085,7 @@
       <c r="AD88" s="8"/>
       <c r="AE88" s="8"/>
     </row>
-    <row r="89" spans="1:32">
+    <row r="89" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A89" s="8">
         <v>1493</v>
       </c>
@@ -11152,12 +11164,12 @@
       <c r="AD89" s="8"/>
       <c r="AE89" s="8"/>
     </row>
-    <row r="90" spans="1:32">
+    <row r="90" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A90" s="8">
         <v>1494</v>
       </c>
       <c r="B90" s="9">
-        <v>45609.383738426</v>
+        <v>45609.383738425997</v>
       </c>
       <c r="C90" s="8" t="s">
         <v>69</v>
@@ -11231,12 +11243,12 @@
       <c r="AD90" s="8"/>
       <c r="AE90" s="8"/>
     </row>
-    <row r="91" spans="1:32">
+    <row r="91" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A91" s="8">
         <v>1495</v>
       </c>
       <c r="B91" s="9">
-        <v>45609.384259259</v>
+        <v>45609.384259259001</v>
       </c>
       <c r="C91" s="8" t="s">
         <v>69</v>
@@ -11310,12 +11322,12 @@
       <c r="AD91" s="8"/>
       <c r="AE91" s="8"/>
     </row>
-    <row r="92" spans="1:32">
+    <row r="92" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A92" s="8">
         <v>1496</v>
       </c>
       <c r="B92" s="9">
-        <v>45609.384907407</v>
+        <v>45609.384907407002</v>
       </c>
       <c r="C92" s="8" t="s">
         <v>69</v>
@@ -11389,12 +11401,12 @@
       <c r="AD92" s="8"/>
       <c r="AE92" s="8"/>
     </row>
-    <row r="93" spans="1:32">
+    <row r="93" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A93" s="8">
         <v>1497</v>
       </c>
       <c r="B93" s="9">
-        <v>45609.386053241</v>
+        <v>45609.386053241004</v>
       </c>
       <c r="C93" s="8" t="s">
         <v>69</v>
@@ -11468,12 +11480,12 @@
       <c r="AD93" s="8"/>
       <c r="AE93" s="8"/>
     </row>
-    <row r="94" spans="1:32">
+    <row r="94" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A94" s="8">
         <v>1498</v>
       </c>
       <c r="B94" s="9">
-        <v>45609.504756944</v>
+        <v>45609.504756943999</v>
       </c>
       <c r="C94" s="8" t="s">
         <v>238</v>
@@ -11549,12 +11561,12 @@
       <c r="AD94" s="8"/>
       <c r="AE94" s="8"/>
     </row>
-    <row r="95" spans="1:32">
+    <row r="95" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A95" s="8">
         <v>1499</v>
       </c>
       <c r="B95" s="9">
-        <v>45609.517314815</v>
+        <v>45609.517314814999</v>
       </c>
       <c r="C95" s="8" t="s">
         <v>69</v>
@@ -11630,12 +11642,12 @@
       <c r="AD95" s="8"/>
       <c r="AE95" s="8"/>
     </row>
-    <row r="96" spans="1:32">
+    <row r="96" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A96" s="8">
         <v>1500</v>
       </c>
       <c r="B96" s="9">
-        <v>45609.523576389</v>
+        <v>45609.523576389001</v>
       </c>
       <c r="C96" s="8" t="s">
         <v>69</v>
@@ -11711,12 +11723,12 @@
       <c r="AD96" s="8"/>
       <c r="AE96" s="8"/>
     </row>
-    <row r="97" spans="1:32">
+    <row r="97" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A97" s="8">
         <v>1501</v>
       </c>
       <c r="B97" s="9">
-        <v>45609.524537037</v>
+        <v>45609.524537037003</v>
       </c>
       <c r="C97" s="8" t="s">
         <v>69</v>
@@ -11790,12 +11802,12 @@
       <c r="AD97" s="8"/>
       <c r="AE97" s="8"/>
     </row>
-    <row r="98" spans="1:32">
+    <row r="98" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A98" s="8">
         <v>1504</v>
       </c>
       <c r="B98" s="9">
-        <v>45610.456423611</v>
+        <v>45610.456423611002</v>
       </c>
       <c r="C98" s="8" t="s">
         <v>69</v>
@@ -11869,12 +11881,12 @@
       <c r="AD98" s="8"/>
       <c r="AE98" s="8"/>
     </row>
-    <row r="99" spans="1:32">
+    <row r="99" spans="1:31" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A99" s="8">
         <v>1505</v>
       </c>
       <c r="B99" s="9">
-        <v>45610.465798611</v>
+        <v>45610.465798611003</v>
       </c>
       <c r="C99" s="8" t="s">
         <v>69</v>
@@ -11948,12 +11960,12 @@
       <c r="AD99" s="8"/>
       <c r="AE99" s="8"/>
     </row>
-    <row r="100" spans="1:32">
+    <row r="100" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A100" s="8">
         <v>1506</v>
       </c>
       <c r="B100" s="9">
-        <v>45610.473391204</v>
+        <v>45610.473391204003</v>
       </c>
       <c r="C100" s="8" t="s">
         <v>69</v>
@@ -12027,12 +12039,12 @@
       <c r="AD100" s="8"/>
       <c r="AE100" s="8"/>
     </row>
-    <row r="101" spans="1:32">
+    <row r="101" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A101" s="8">
         <v>1507</v>
       </c>
       <c r="B101" s="9">
-        <v>45616.583969907</v>
+        <v>45616.583969906998</v>
       </c>
       <c r="C101" s="8" t="s">
         <v>46</v>
@@ -12104,12 +12116,12 @@
       <c r="AD101" s="8"/>
       <c r="AE101" s="8"/>
     </row>
-    <row r="102" spans="1:32">
+    <row r="102" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A102" s="8">
         <v>1508</v>
       </c>
       <c r="B102" s="9">
-        <v>45616.584803241</v>
+        <v>45616.584803240999</v>
       </c>
       <c r="C102" s="8" t="s">
         <v>46</v>
@@ -12181,12 +12193,12 @@
       <c r="AD102" s="8"/>
       <c r="AE102" s="8"/>
     </row>
-    <row r="103" spans="1:32">
+    <row r="103" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A103" s="8">
         <v>1509</v>
       </c>
       <c r="B103" s="9">
-        <v>45616.585520833</v>
+        <v>45616.585520833003</v>
       </c>
       <c r="C103" s="8" t="s">
         <v>46</v>
@@ -12258,7 +12270,7 @@
       <c r="AD103" s="8"/>
       <c r="AE103" s="8"/>
     </row>
-    <row r="104" spans="1:32">
+    <row r="104" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A104" s="8">
         <v>1510</v>
       </c>
@@ -12337,12 +12349,12 @@
       <c r="AD104" s="8"/>
       <c r="AE104" s="8"/>
     </row>
-    <row r="105" spans="1:32">
+    <row r="105" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A105" s="8">
         <v>1511</v>
       </c>
       <c r="B105" s="9">
-        <v>45616.587407407</v>
+        <v>45616.587407407002</v>
       </c>
       <c r="C105" s="8" t="s">
         <v>46</v>
@@ -12414,12 +12426,12 @@
       <c r="AD105" s="8"/>
       <c r="AE105" s="8"/>
     </row>
-    <row r="106" spans="1:32">
+    <row r="106" spans="1:31" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A106" s="8">
         <v>1512</v>
       </c>
       <c r="B106" s="9">
-        <v>45617.412361111</v>
+        <v>45617.412361110997</v>
       </c>
       <c r="C106" s="8" t="s">
         <v>69</v>
@@ -12493,12 +12505,12 @@
       <c r="AD106" s="8"/>
       <c r="AE106" s="8"/>
     </row>
-    <row r="107" spans="1:32">
+    <row r="107" spans="1:31" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A107" s="8">
         <v>1513</v>
       </c>
       <c r="B107" s="9">
-        <v>45617.413611111</v>
+        <v>45617.413611110998</v>
       </c>
       <c r="C107" s="8" t="s">
         <v>69</v>
@@ -12574,12 +12586,12 @@
       <c r="AD107" s="8"/>
       <c r="AE107" s="8"/>
     </row>
-    <row r="108" spans="1:32">
+    <row r="108" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A108" s="8">
         <v>1515</v>
       </c>
       <c r="B108" s="9">
-        <v>45621.473854167</v>
+        <v>45621.473854167001</v>
       </c>
       <c r="C108" s="8" t="s">
         <v>46</v>
@@ -12653,12 +12665,12 @@
       <c r="AD108" s="8"/>
       <c r="AE108" s="8"/>
     </row>
-    <row r="109" spans="1:32">
+    <row r="109" spans="1:31" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A109" s="8">
         <v>1518</v>
       </c>
       <c r="B109" s="9">
-        <v>45621.477777778</v>
+        <v>45621.477777777996</v>
       </c>
       <c r="C109" s="8" t="s">
         <v>46</v>
@@ -12732,7 +12744,7 @@
       <c r="AD109" s="8"/>
       <c r="AE109" s="8"/>
     </row>
-    <row r="110" spans="1:32">
+    <row r="110" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A110" s="8">
         <v>1519</v>
       </c>
@@ -12811,12 +12823,12 @@
       <c r="AD110" s="8"/>
       <c r="AE110" s="8"/>
     </row>
-    <row r="111" spans="1:32">
+    <row r="111" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A111" s="8">
         <v>1520</v>
       </c>
       <c r="B111" s="9">
-        <v>45622.433865741</v>
+        <v>45622.433865740997</v>
       </c>
       <c r="C111" s="8" t="s">
         <v>46</v>
@@ -12890,12 +12902,12 @@
       <c r="AD111" s="8"/>
       <c r="AE111" s="8"/>
     </row>
-    <row r="112" spans="1:32">
+    <row r="112" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A112" s="8">
         <v>1521</v>
       </c>
       <c r="B112" s="9">
-        <v>45688.534976852</v>
+        <v>45688.534976852003</v>
       </c>
       <c r="C112" s="8" t="s">
         <v>46</v>
@@ -12971,12 +12983,12 @@
       <c r="AD112" s="8"/>
       <c r="AE112" s="8"/>
     </row>
-    <row r="113" spans="1:32">
+    <row r="113" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A113" s="8">
         <v>1522</v>
       </c>
       <c r="B113" s="9">
-        <v>45688.537337963</v>
+        <v>45688.537337962996</v>
       </c>
       <c r="C113" s="8" t="s">
         <v>46</v>
@@ -13052,12 +13064,12 @@
       <c r="AD113" s="8"/>
       <c r="AE113" s="8"/>
     </row>
-    <row r="114" spans="1:32">
+    <row r="114" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A114" s="8">
         <v>1523</v>
       </c>
       <c r="B114" s="9">
-        <v>45688.540844907</v>
+        <v>45688.540844907002</v>
       </c>
       <c r="C114" s="8" t="s">
         <v>46</v>
@@ -13133,12 +13145,12 @@
       <c r="AD114" s="8"/>
       <c r="AE114" s="8"/>
     </row>
-    <row r="115" spans="1:32">
+    <row r="115" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A115" s="8">
         <v>1524</v>
       </c>
       <c r="B115" s="9">
-        <v>45688.541886574</v>
+        <v>45688.541886573999</v>
       </c>
       <c r="C115" s="8" t="s">
         <v>46</v>
@@ -13214,12 +13226,12 @@
       <c r="AD115" s="8"/>
       <c r="AE115" s="8"/>
     </row>
-    <row r="116" spans="1:32">
+    <row r="116" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A116" s="8">
         <v>1525</v>
       </c>
       <c r="B116" s="9">
-        <v>45688.543090278</v>
+        <v>45688.543090277999</v>
       </c>
       <c r="C116" s="8" t="s">
         <v>46</v>
@@ -13295,12 +13307,12 @@
       <c r="AD116" s="8"/>
       <c r="AE116" s="8"/>
     </row>
-    <row r="117" spans="1:32">
+    <row r="117" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A117" s="8">
         <v>1527</v>
       </c>
       <c r="B117" s="9">
-        <v>45712.46337963</v>
+        <v>45712.463379629997</v>
       </c>
       <c r="C117" s="8" t="s">
         <v>29</v>
@@ -13376,12 +13388,12 @@
       <c r="AD117" s="8"/>
       <c r="AE117" s="8"/>
     </row>
-    <row r="118" spans="1:32">
+    <row r="118" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A118" s="8">
         <v>1529</v>
       </c>
       <c r="B118" s="9">
-        <v>45712.466296296</v>
+        <v>45712.466296295999</v>
       </c>
       <c r="C118" s="8" t="s">
         <v>29</v>
@@ -13457,12 +13469,12 @@
       <c r="AD118" s="8"/>
       <c r="AE118" s="8"/>
     </row>
-    <row r="119" spans="1:32">
+    <row r="119" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A119" s="8">
         <v>1530</v>
       </c>
       <c r="B119" s="9">
-        <v>45712.467673611</v>
+        <v>45712.467673610998</v>
       </c>
       <c r="C119" s="8" t="s">
         <v>29</v>
@@ -13538,12 +13550,12 @@
       <c r="AD119" s="8"/>
       <c r="AE119" s="8"/>
     </row>
-    <row r="120" spans="1:32">
+    <row r="120" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A120" s="8">
         <v>1531</v>
       </c>
       <c r="B120" s="9">
-        <v>45712.468645833</v>
+        <v>45712.468645833003</v>
       </c>
       <c r="C120" s="8" t="s">
         <v>29</v>
@@ -13619,12 +13631,12 @@
       <c r="AD120" s="8"/>
       <c r="AE120" s="8"/>
     </row>
-    <row r="121" spans="1:32">
+    <row r="121" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A121" s="8">
         <v>1532</v>
       </c>
       <c r="B121" s="9">
-        <v>45712.469814815</v>
+        <v>45712.469814814998</v>
       </c>
       <c r="C121" s="8" t="s">
         <v>29</v>
@@ -13700,7 +13712,7 @@
       <c r="AD121" s="8"/>
       <c r="AE121" s="8"/>
     </row>
-    <row r="122" spans="1:32">
+    <row r="122" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A122" s="8">
         <v>1533</v>
       </c>
@@ -13781,12 +13793,12 @@
       <c r="AD122" s="8"/>
       <c r="AE122" s="8"/>
     </row>
-    <row r="123" spans="1:32">
+    <row r="123" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A123" s="8">
         <v>1534</v>
       </c>
       <c r="B123" s="9">
-        <v>45712.489282407</v>
+        <v>45712.489282406998</v>
       </c>
       <c r="C123" s="8" t="s">
         <v>29</v>
@@ -13862,12 +13874,12 @@
       <c r="AD123" s="8"/>
       <c r="AE123" s="8"/>
     </row>
-    <row r="124" spans="1:32">
+    <row r="124" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A124" s="8">
         <v>1535</v>
       </c>
       <c r="B124" s="9">
-        <v>45712.490300926</v>
+        <v>45712.490300926002</v>
       </c>
       <c r="C124" s="8" t="s">
         <v>29</v>
@@ -13943,12 +13955,12 @@
       <c r="AD124" s="8"/>
       <c r="AE124" s="8"/>
     </row>
-    <row r="125" spans="1:32">
+    <row r="125" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A125" s="8">
         <v>1536</v>
       </c>
       <c r="B125" s="9">
-        <v>45712.491215278</v>
+        <v>45712.491215278002</v>
       </c>
       <c r="C125" s="8" t="s">
         <v>29</v>
@@ -14024,7 +14036,7 @@
       <c r="AD125" s="8"/>
       <c r="AE125" s="8"/>
     </row>
-    <row r="126" spans="1:32">
+    <row r="126" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A126" s="8">
         <v>1537</v>
       </c>
@@ -14103,12 +14115,12 @@
       <c r="AD126" s="8"/>
       <c r="AE126" s="8"/>
     </row>
-    <row r="127" spans="1:32">
+    <row r="127" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A127" s="8">
         <v>1538</v>
       </c>
       <c r="B127" s="9">
-        <v>45713.600509259</v>
+        <v>45713.600509258998</v>
       </c>
       <c r="C127" s="8" t="s">
         <v>238</v>
@@ -14176,12 +14188,12 @@
       <c r="AD127" s="8"/>
       <c r="AE127" s="8"/>
     </row>
-    <row r="128" spans="1:32">
+    <row r="128" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A128" s="8">
         <v>1541</v>
       </c>
       <c r="B128" s="9">
-        <v>45713.631793981</v>
+        <v>45713.631793981003</v>
       </c>
       <c r="C128" s="8" t="s">
         <v>238</v>
@@ -14249,12 +14261,12 @@
       <c r="AD128" s="8"/>
       <c r="AE128" s="8"/>
     </row>
-    <row r="129" spans="1:32">
+    <row r="129" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A129" s="8">
         <v>1542</v>
       </c>
       <c r="B129" s="9">
-        <v>45713.632685185</v>
+        <v>45713.632685185003</v>
       </c>
       <c r="C129" s="8" t="s">
         <v>238</v>
@@ -14322,7 +14334,7 @@
       <c r="AD129" s="8"/>
       <c r="AE129" s="8"/>
     </row>
-    <row r="130" spans="1:32">
+    <row r="130" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A130" s="8">
         <v>1543</v>
       </c>
@@ -14395,12 +14407,12 @@
       <c r="AD130" s="8"/>
       <c r="AE130" s="8"/>
     </row>
-    <row r="131" spans="1:32">
+    <row r="131" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A131" s="8">
         <v>1546</v>
       </c>
       <c r="B131" s="9">
-        <v>45713.640659722</v>
+        <v>45713.640659721998</v>
       </c>
       <c r="C131" s="8" t="s">
         <v>69</v>
@@ -14468,12 +14480,12 @@
       <c r="AD131" s="8"/>
       <c r="AE131" s="8"/>
     </row>
-    <row r="132" spans="1:32">
+    <row r="132" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A132" s="8">
         <v>1549</v>
       </c>
       <c r="B132" s="9">
-        <v>45713.656921296</v>
+        <v>45713.656921296002</v>
       </c>
       <c r="C132" s="8" t="s">
         <v>238</v>
@@ -14541,12 +14553,12 @@
       <c r="AD132" s="8"/>
       <c r="AE132" s="8"/>
     </row>
-    <row r="133" spans="1:32">
+    <row r="133" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A133" s="8">
         <v>1550</v>
       </c>
       <c r="B133" s="9">
-        <v>45713.660115741</v>
+        <v>45713.660115740997</v>
       </c>
       <c r="C133" s="8" t="s">
         <v>69</v>
@@ -14614,7 +14626,7 @@
       <c r="AD133" s="8"/>
       <c r="AE133" s="8"/>
     </row>
-    <row r="134" spans="1:32">
+    <row r="134" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A134" s="8">
         <v>1551</v>
       </c>
@@ -14687,12 +14699,12 @@
       <c r="AD134" s="8"/>
       <c r="AE134" s="8"/>
     </row>
-    <row r="135" spans="1:32">
+    <row r="135" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A135" s="8">
         <v>1552</v>
       </c>
       <c r="B135" s="9">
-        <v>45714.354895833</v>
+        <v>45714.354895832999</v>
       </c>
       <c r="C135" s="8" t="s">
         <v>238</v>
@@ -14760,12 +14772,12 @@
       <c r="AD135" s="8"/>
       <c r="AE135" s="8"/>
     </row>
-    <row r="136" spans="1:32">
+    <row r="136" spans="1:31" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A136" s="8">
         <v>1555</v>
       </c>
       <c r="B136" s="9">
-        <v>45714.364293981</v>
+        <v>45714.364293981002</v>
       </c>
       <c r="C136" s="8" t="s">
         <v>69</v>
@@ -14833,12 +14845,12 @@
       <c r="AD136" s="8"/>
       <c r="AE136" s="8"/>
     </row>
-    <row r="137" spans="1:32">
+    <row r="137" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A137" s="8">
         <v>1558</v>
       </c>
       <c r="B137" s="9">
-        <v>45714.370069444</v>
+        <v>45714.370069443998</v>
       </c>
       <c r="C137" s="8" t="s">
         <v>69</v>
@@ -14906,12 +14918,12 @@
       <c r="AD137" s="8"/>
       <c r="AE137" s="8"/>
     </row>
-    <row r="138" spans="1:32">
+    <row r="138" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A138" s="8">
         <v>1559</v>
       </c>
       <c r="B138" s="9">
-        <v>45714.390613426</v>
+        <v>45714.390613426003</v>
       </c>
       <c r="C138" s="8" t="s">
         <v>238</v>
@@ -14981,12 +14993,12 @@
       <c r="AD138" s="8"/>
       <c r="AE138" s="8"/>
     </row>
-    <row r="139" spans="1:32">
+    <row r="139" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A139" s="8">
         <v>1560</v>
       </c>
       <c r="B139" s="9">
-        <v>45714.397638889</v>
+        <v>45714.397638889001</v>
       </c>
       <c r="C139" s="8" t="s">
         <v>69</v>
@@ -15058,12 +15070,12 @@
       <c r="AD139" s="8"/>
       <c r="AE139" s="8"/>
     </row>
-    <row r="140" spans="1:32">
+    <row r="140" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A140" s="8">
         <v>1561</v>
       </c>
       <c r="B140" s="9">
-        <v>45714.404664352</v>
+        <v>45714.404664351998</v>
       </c>
       <c r="C140" s="8" t="s">
         <v>69</v>
@@ -15135,7 +15147,7 @@
       <c r="AD140" s="8"/>
       <c r="AE140" s="8"/>
     </row>
-    <row r="141" spans="1:32">
+    <row r="141" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A141" s="8">
         <v>1562</v>
       </c>
@@ -15212,12 +15224,12 @@
       <c r="AD141" s="8"/>
       <c r="AE141" s="8"/>
     </row>
-    <row r="142" spans="1:32">
+    <row r="142" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A142" s="8">
         <v>1563</v>
       </c>
       <c r="B142" s="9">
-        <v>45714.414270833</v>
+        <v>45714.414270832996</v>
       </c>
       <c r="C142" s="8" t="s">
         <v>238</v>
@@ -15289,12 +15301,12 @@
       <c r="AD142" s="8"/>
       <c r="AE142" s="8"/>
     </row>
-    <row r="143" spans="1:32">
+    <row r="143" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A143" s="8">
         <v>1564</v>
       </c>
       <c r="B143" s="9">
-        <v>45714.425625</v>
+        <v>45714.425625000003</v>
       </c>
       <c r="C143" s="8" t="s">
         <v>69</v>
@@ -15366,7 +15378,7 @@
       <c r="AD143" s="8"/>
       <c r="AE143" s="8"/>
     </row>
-    <row r="144" spans="1:32">
+    <row r="144" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A144" s="8">
         <v>1565</v>
       </c>
@@ -15443,12 +15455,12 @@
       <c r="AD144" s="8"/>
       <c r="AE144" s="8"/>
     </row>
-    <row r="145" spans="1:32">
+    <row r="145" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A145" s="8">
         <v>1566</v>
       </c>
       <c r="B145" s="9">
-        <v>45714.498622685</v>
+        <v>45714.498622685001</v>
       </c>
       <c r="C145" s="8" t="s">
         <v>69</v>
@@ -15520,12 +15532,12 @@
       <c r="AD145" s="8"/>
       <c r="AE145" s="8"/>
     </row>
-    <row r="146" spans="1:32">
+    <row r="146" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A146" s="8">
         <v>1567</v>
       </c>
       <c r="B146" s="9">
-        <v>45714.596863426</v>
+        <v>45714.596863425999</v>
       </c>
       <c r="C146" s="8" t="s">
         <v>69</v>
@@ -15597,12 +15609,12 @@
       <c r="AD146" s="8"/>
       <c r="AE146" s="8"/>
     </row>
-    <row r="147" spans="1:32">
+    <row r="147" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A147" s="8">
         <v>1569</v>
       </c>
       <c r="B147" s="9">
-        <v>45714.610763889</v>
+        <v>45714.610763889003</v>
       </c>
       <c r="C147" s="8" t="s">
         <v>69</v>
@@ -15672,12 +15684,12 @@
       <c r="AD147" s="8"/>
       <c r="AE147" s="8"/>
     </row>
-    <row r="148" spans="1:32">
+    <row r="148" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A148" s="8">
         <v>1572</v>
       </c>
       <c r="B148" s="9">
-        <v>45714.619189815</v>
+        <v>45714.619189814999</v>
       </c>
       <c r="C148" s="8" t="s">
         <v>69</v>
@@ -15749,12 +15761,12 @@
       <c r="AD148" s="8"/>
       <c r="AE148" s="8"/>
     </row>
-    <row r="149" spans="1:32">
+    <row r="149" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A149" s="8">
         <v>1573</v>
       </c>
       <c r="B149" s="9">
-        <v>45714.630706019</v>
+        <v>45714.630706019001</v>
       </c>
       <c r="C149" s="8" t="s">
         <v>238</v>
@@ -15822,12 +15834,12 @@
       <c r="AD149" s="8"/>
       <c r="AE149" s="8"/>
     </row>
-    <row r="150" spans="1:32">
+    <row r="150" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A150" s="8">
         <v>1576</v>
       </c>
       <c r="B150" s="9">
-        <v>45714.641238426</v>
+        <v>45714.641238425997</v>
       </c>
       <c r="C150" s="8" t="s">
         <v>69</v>
@@ -15895,12 +15907,12 @@
       <c r="AD150" s="8"/>
       <c r="AE150" s="8"/>
     </row>
-    <row r="151" spans="1:32">
+    <row r="151" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A151" s="8">
         <v>1577</v>
       </c>
       <c r="B151" s="9">
-        <v>45714.644722222</v>
+        <v>45714.644722222001</v>
       </c>
       <c r="C151" s="8" t="s">
         <v>69</v>
@@ -15968,12 +15980,12 @@
       <c r="AD151" s="8"/>
       <c r="AE151" s="8"/>
     </row>
-    <row r="152" spans="1:32">
+    <row r="152" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A152" s="8">
         <v>1580</v>
       </c>
       <c r="B152" s="9">
-        <v>45715.35900463</v>
+        <v>45715.359004630001</v>
       </c>
       <c r="C152" s="8" t="s">
         <v>69</v>
@@ -16041,12 +16053,12 @@
       <c r="AD152" s="8"/>
       <c r="AE152" s="8"/>
     </row>
-    <row r="153" spans="1:32">
+    <row r="153" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A153" s="8">
         <v>1581</v>
       </c>
       <c r="B153" s="9">
-        <v>45715.359768519</v>
+        <v>45715.359768519003</v>
       </c>
       <c r="C153" s="8" t="s">
         <v>69</v>
@@ -16114,12 +16126,12 @@
       <c r="AD153" s="8"/>
       <c r="AE153" s="8"/>
     </row>
-    <row r="154" spans="1:32">
+    <row r="154" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A154" s="8">
         <v>1586</v>
       </c>
       <c r="B154" s="9">
-        <v>45715.388923611</v>
+        <v>45715.388923610997</v>
       </c>
       <c r="C154" s="8" t="s">
         <v>69</v>
@@ -16183,12 +16195,12 @@
       <c r="AD154" s="8"/>
       <c r="AE154" s="8"/>
     </row>
-    <row r="155" spans="1:32">
+    <row r="155" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A155" s="8">
         <v>1587</v>
       </c>
       <c r="B155" s="9">
-        <v>45715.390138889</v>
+        <v>45715.390138889001</v>
       </c>
       <c r="C155" s="8" t="s">
         <v>69</v>
@@ -16252,12 +16264,12 @@
       <c r="AD155" s="8"/>
       <c r="AE155" s="8"/>
     </row>
-    <row r="156" spans="1:32">
+    <row r="156" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A156" s="8">
         <v>1589</v>
       </c>
       <c r="B156" s="9">
-        <v>45715.391574074</v>
+        <v>45715.391574073998</v>
       </c>
       <c r="C156" s="8" t="s">
         <v>69</v>
@@ -16321,12 +16333,12 @@
       <c r="AD156" s="8"/>
       <c r="AE156" s="8"/>
     </row>
-    <row r="157" spans="1:32">
+    <row r="157" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A157" s="8">
         <v>1590</v>
       </c>
       <c r="B157" s="9">
-        <v>45715.392175926</v>
+        <v>45715.392175925997</v>
       </c>
       <c r="C157" s="8" t="s">
         <v>69</v>
@@ -16390,12 +16402,12 @@
       <c r="AD157" s="8"/>
       <c r="AE157" s="8"/>
     </row>
-    <row r="158" spans="1:32">
+    <row r="158" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A158" s="8">
         <v>1591</v>
       </c>
       <c r="B158" s="9">
-        <v>45715.393553241</v>
+        <v>45715.393553241003</v>
       </c>
       <c r="C158" s="8" t="s">
         <v>238</v>
@@ -16461,12 +16473,12 @@
       <c r="AD158" s="8"/>
       <c r="AE158" s="8"/>
     </row>
-    <row r="159" spans="1:32">
+    <row r="159" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A159" s="8">
         <v>1592</v>
       </c>
       <c r="B159" s="9">
-        <v>45715.394247685</v>
+        <v>45715.394247684999</v>
       </c>
       <c r="C159" s="8" t="s">
         <v>69</v>
@@ -16534,12 +16546,12 @@
       <c r="AD159" s="8"/>
       <c r="AE159" s="8"/>
     </row>
-    <row r="160" spans="1:32">
+    <row r="160" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A160" s="8">
         <v>1593</v>
       </c>
       <c r="B160" s="9">
-        <v>45715.3946875</v>
+        <v>45715.394687499997</v>
       </c>
       <c r="C160" s="8" t="s">
         <v>69</v>
@@ -16607,12 +16619,12 @@
       <c r="AD160" s="8"/>
       <c r="AE160" s="8"/>
     </row>
-    <row r="161" spans="1:32">
+    <row r="161" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A161" s="8">
         <v>1594</v>
       </c>
       <c r="B161" s="9">
-        <v>45715.395266204</v>
+        <v>45715.395266204003</v>
       </c>
       <c r="C161" s="8" t="s">
         <v>69</v>
@@ -16680,7 +16692,7 @@
       <c r="AD161" s="8"/>
       <c r="AE161" s="8"/>
     </row>
-    <row r="162" spans="1:32">
+    <row r="162" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A162" s="8">
         <v>1595</v>
       </c>
@@ -16761,12 +16773,12 @@
       <c r="AD162" s="8"/>
       <c r="AE162" s="8"/>
     </row>
-    <row r="163" spans="1:32">
+    <row r="163" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A163" s="8">
         <v>1596</v>
       </c>
       <c r="B163" s="9">
-        <v>45736.501215278</v>
+        <v>45736.501215277996</v>
       </c>
       <c r="C163" s="8" t="s">
         <v>46</v>
@@ -16842,12 +16854,12 @@
       <c r="AD163" s="8"/>
       <c r="AE163" s="8"/>
     </row>
-    <row r="164" spans="1:32">
+    <row r="164" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A164" s="8">
         <v>1597</v>
       </c>
       <c r="B164" s="9">
-        <v>45736.502372685</v>
+        <v>45736.502372684998</v>
       </c>
       <c r="C164" s="8" t="s">
         <v>46</v>
@@ -16923,12 +16935,12 @@
       <c r="AD164" s="8"/>
       <c r="AE164" s="8"/>
     </row>
-    <row r="165" spans="1:32">
+    <row r="165" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A165" s="8">
         <v>1598</v>
       </c>
       <c r="B165" s="9">
-        <v>45736.506319444</v>
+        <v>45736.506319444001</v>
       </c>
       <c r="C165" s="8" t="s">
         <v>46</v>
@@ -17004,12 +17016,12 @@
       <c r="AD165" s="8"/>
       <c r="AE165" s="8"/>
     </row>
-    <row r="166" spans="1:32">
+    <row r="166" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A166" s="8">
         <v>1599</v>
       </c>
       <c r="B166" s="9">
-        <v>45736.507997685</v>
+        <v>45736.507997685003</v>
       </c>
       <c r="C166" s="8" t="s">
         <v>46</v>
@@ -17085,12 +17097,12 @@
       <c r="AD166" s="8"/>
       <c r="AE166" s="8"/>
     </row>
-    <row r="167" spans="1:32">
+    <row r="167" spans="1:31" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A167" s="8">
         <v>1600</v>
       </c>
       <c r="B167" s="9">
-        <v>45748.449236111</v>
+        <v>45748.449236111002</v>
       </c>
       <c r="C167" s="8" t="s">
         <v>69</v>
@@ -17158,12 +17170,12 @@
       <c r="AD167" s="8"/>
       <c r="AE167" s="8"/>
     </row>
-    <row r="168" spans="1:32">
+    <row r="168" spans="1:31" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A168" s="8">
         <v>1601</v>
       </c>
       <c r="B168" s="9">
-        <v>45748.45755787</v>
+        <v>45748.457557870002</v>
       </c>
       <c r="C168" s="8" t="s">
         <v>69</v>
@@ -17231,12 +17243,12 @@
       <c r="AD168" s="8"/>
       <c r="AE168" s="8"/>
     </row>
-    <row r="169" spans="1:32">
+    <row r="169" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A169" s="8">
         <v>1602</v>
       </c>
       <c r="B169" s="9">
-        <v>45756.572581019</v>
+        <v>45756.572581018998</v>
       </c>
       <c r="C169" s="8" t="s">
         <v>69</v>
@@ -17298,12 +17310,12 @@
       <c r="AD169" s="8"/>
       <c r="AE169" s="8"/>
     </row>
-    <row r="170" spans="1:32">
+    <row r="170" spans="1:31" ht="316.8" x14ac:dyDescent="0.3">
       <c r="A170" s="8">
         <v>1603</v>
       </c>
       <c r="B170" s="9">
-        <v>45769.425451389</v>
+        <v>45769.425451388997</v>
       </c>
       <c r="C170" s="8" t="s">
         <v>46</v>
@@ -17381,12 +17393,12 @@
       <c r="AD170" s="8"/>
       <c r="AE170" s="8"/>
     </row>
-    <row r="171" spans="1:32">
+    <row r="171" spans="1:31" ht="316.8" x14ac:dyDescent="0.3">
       <c r="A171" s="8">
         <v>1604</v>
       </c>
       <c r="B171" s="9">
-        <v>45769.426481481</v>
+        <v>45769.426481481001</v>
       </c>
       <c r="C171" s="8" t="s">
         <v>46</v>
@@ -17464,7 +17476,7 @@
       <c r="AD171" s="8"/>
       <c r="AE171" s="8"/>
     </row>
-    <row r="172" spans="1:32">
+    <row r="172" spans="1:31" ht="316.8" x14ac:dyDescent="0.3">
       <c r="A172" s="8">
         <v>1605</v>
       </c>
@@ -17547,12 +17559,12 @@
       <c r="AD172" s="8"/>
       <c r="AE172" s="8"/>
     </row>
-    <row r="173" spans="1:32">
+    <row r="173" spans="1:31" ht="316.8" x14ac:dyDescent="0.3">
       <c r="A173" s="8">
         <v>1606</v>
       </c>
       <c r="B173" s="9">
-        <v>45769.430104167</v>
+        <v>45769.430104166997</v>
       </c>
       <c r="C173" s="8" t="s">
         <v>46</v>
@@ -17632,12 +17644,12 @@
       <c r="AD173" s="8"/>
       <c r="AE173" s="8"/>
     </row>
-    <row r="174" spans="1:32">
+    <row r="174" spans="1:31" ht="316.8" x14ac:dyDescent="0.3">
       <c r="A174" s="8">
         <v>1607</v>
       </c>
       <c r="B174" s="9">
-        <v>45769.430960648</v>
+        <v>45769.430960648002</v>
       </c>
       <c r="C174" s="8" t="s">
         <v>46</v>
@@ -17717,12 +17729,12 @@
       <c r="AD174" s="8"/>
       <c r="AE174" s="8"/>
     </row>
-    <row r="175" spans="1:32">
+    <row r="175" spans="1:31" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A175" s="8">
         <v>1608</v>
       </c>
       <c r="B175" s="9">
-        <v>45798.59875</v>
+        <v>45798.598749999997</v>
       </c>
       <c r="C175" s="8" t="s">
         <v>46</v>
@@ -17788,12 +17800,12 @@
       <c r="AD175" s="8"/>
       <c r="AE175" s="8"/>
     </row>
-    <row r="176" spans="1:32">
+    <row r="176" spans="1:31" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A176" s="8">
         <v>1609</v>
       </c>
       <c r="B176" s="9">
-        <v>45798.602916667</v>
+        <v>45798.602916666998</v>
       </c>
       <c r="C176" s="8" t="s">
         <v>46</v>
@@ -17859,12 +17871,12 @@
       <c r="AD176" s="8"/>
       <c r="AE176" s="8"/>
     </row>
-    <row r="177" spans="1:32">
+    <row r="177" spans="1:31" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A177" s="8">
         <v>1610</v>
       </c>
       <c r="B177" s="9">
-        <v>45798.606770833</v>
+        <v>45798.606770833001</v>
       </c>
       <c r="C177" s="8" t="s">
         <v>46</v>
@@ -17930,12 +17942,12 @@
       <c r="AD177" s="8"/>
       <c r="AE177" s="8"/>
     </row>
-    <row r="178" spans="1:32">
+    <row r="178" spans="1:31" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A178" s="8">
         <v>1611</v>
       </c>
       <c r="B178" s="9">
-        <v>45798.607384259</v>
+        <v>45798.607384258998</v>
       </c>
       <c r="C178" s="8" t="s">
         <v>46</v>
@@ -18001,12 +18013,12 @@
       <c r="AD178" s="8"/>
       <c r="AE178" s="8"/>
     </row>
-    <row r="179" spans="1:32">
+    <row r="179" spans="1:31" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A179" s="8">
         <v>1612</v>
       </c>
       <c r="B179" s="9">
-        <v>45798.608159722</v>
+        <v>45798.608159722004</v>
       </c>
       <c r="C179" s="8" t="s">
         <v>46</v>
@@ -18068,12 +18080,12 @@
       <c r="AD179" s="8"/>
       <c r="AE179" s="8"/>
     </row>
-    <row r="180" spans="1:32">
+    <row r="180" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A180" s="8">
         <v>1614</v>
       </c>
       <c r="B180" s="9">
-        <v>45798.615</v>
+        <v>45798.614999999998</v>
       </c>
       <c r="C180" s="8" t="s">
         <v>46</v>
@@ -18149,12 +18161,12 @@
       <c r="AD180" s="8"/>
       <c r="AE180" s="8"/>
     </row>
-    <row r="181" spans="1:32">
+    <row r="181" spans="1:31" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A181" s="8">
         <v>1615</v>
       </c>
       <c r="B181" s="9">
-        <v>45798.615949074</v>
+        <v>45798.615949074003</v>
       </c>
       <c r="C181" s="8" t="s">
         <v>46</v>
@@ -18230,12 +18242,12 @@
       <c r="AD181" s="8"/>
       <c r="AE181" s="8"/>
     </row>
-    <row r="182" spans="1:32">
+    <row r="182" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A182" s="8">
         <v>1616</v>
       </c>
       <c r="B182" s="9">
-        <v>45798.617731481</v>
+        <v>45798.617731480997</v>
       </c>
       <c r="C182" s="8" t="s">
         <v>46</v>
@@ -18311,12 +18323,12 @@
       <c r="AD182" s="8"/>
       <c r="AE182" s="8"/>
     </row>
-    <row r="183" spans="1:32">
+    <row r="183" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A183" s="8">
         <v>1617</v>
       </c>
       <c r="B183" s="9">
-        <v>45798.619039352</v>
+        <v>45798.619039352001</v>
       </c>
       <c r="C183" s="8" t="s">
         <v>46</v>
@@ -18392,12 +18404,12 @@
       <c r="AD183" s="8"/>
       <c r="AE183" s="8"/>
     </row>
-    <row r="184" spans="1:32">
+    <row r="184" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A184" s="8">
         <v>1618</v>
       </c>
       <c r="B184" s="9">
-        <v>45798.619895833</v>
+        <v>45798.619895832999</v>
       </c>
       <c r="C184" s="8" t="s">
         <v>46</v>
@@ -18473,12 +18485,12 @@
       <c r="AD184" s="8"/>
       <c r="AE184" s="8"/>
     </row>
-    <row r="185" spans="1:32">
+    <row r="185" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A185" s="8">
         <v>1621</v>
       </c>
       <c r="B185" s="9">
-        <v>45807.428020833</v>
+        <v>45807.428020833002</v>
       </c>
       <c r="C185" s="8" t="s">
         <v>46</v>
@@ -18554,12 +18566,12 @@
       <c r="AD185" s="8"/>
       <c r="AE185" s="8"/>
     </row>
-    <row r="186" spans="1:32">
+    <row r="186" spans="1:31" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A186" s="8">
         <v>1622</v>
       </c>
       <c r="B186" s="9">
-        <v>45807.428935185</v>
+        <v>45807.428935185002</v>
       </c>
       <c r="C186" s="8" t="s">
         <v>46</v>
@@ -18635,12 +18647,12 @@
       <c r="AD186" s="8"/>
       <c r="AE186" s="8"/>
     </row>
-    <row r="187" spans="1:32">
+    <row r="187" spans="1:31" ht="72" x14ac:dyDescent="0.3">
       <c r="A187" s="8">
         <v>1623</v>
       </c>
       <c r="B187" s="9">
-        <v>45807.429664352</v>
+        <v>45807.429664351999</v>
       </c>
       <c r="C187" s="8" t="s">
         <v>46</v>
@@ -18716,12 +18728,12 @@
       <c r="AD187" s="8"/>
       <c r="AE187" s="8"/>
     </row>
-    <row r="188" spans="1:32">
+    <row r="188" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A188" s="8">
         <v>1624</v>
       </c>
       <c r="B188" s="9">
-        <v>45807.431006944</v>
+        <v>45807.431006944003</v>
       </c>
       <c r="C188" s="8" t="s">
         <v>46</v>
@@ -18797,12 +18809,12 @@
       <c r="AD188" s="8"/>
       <c r="AE188" s="8"/>
     </row>
-    <row r="189" spans="1:32">
+    <row r="189" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A189" s="8">
         <v>1625</v>
       </c>
       <c r="B189" s="9">
-        <v>45807.452743056</v>
+        <v>45807.452743055997</v>
       </c>
       <c r="C189" s="8" t="s">
         <v>46</v>
@@ -18878,12 +18890,12 @@
       <c r="AD189" s="8"/>
       <c r="AE189" s="8"/>
     </row>
-    <row r="190" spans="1:32">
+    <row r="190" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A190" s="8">
         <v>1627</v>
       </c>
       <c r="B190" s="9">
-        <v>45807.490324074</v>
+        <v>45807.490324074002</v>
       </c>
       <c r="C190" s="8" t="s">
         <v>46</v>
@@ -18949,12 +18961,12 @@
       <c r="AD190" s="8"/>
       <c r="AE190" s="8"/>
     </row>
-    <row r="191" spans="1:32">
+    <row r="191" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A191" s="8">
         <v>1628</v>
       </c>
       <c r="B191" s="9">
-        <v>45807.491377315</v>
+        <v>45807.491377314996</v>
       </c>
       <c r="C191" s="8" t="s">
         <v>46</v>
@@ -19020,12 +19032,12 @@
       <c r="AD191" s="8"/>
       <c r="AE191" s="8"/>
     </row>
-    <row r="192" spans="1:32">
+    <row r="192" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A192" s="8">
         <v>1629</v>
       </c>
       <c r="B192" s="9">
-        <v>45807.492418981</v>
+        <v>45807.492418980997</v>
       </c>
       <c r="C192" s="8" t="s">
         <v>46</v>
@@ -19091,12 +19103,12 @@
       <c r="AD192" s="8"/>
       <c r="AE192" s="8"/>
     </row>
-    <row r="193" spans="1:32">
+    <row r="193" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A193" s="8">
         <v>1630</v>
       </c>
       <c r="B193" s="9">
-        <v>45807.49318287</v>
+        <v>45807.493182869999</v>
       </c>
       <c r="C193" s="8" t="s">
         <v>46</v>
@@ -19162,12 +19174,12 @@
       <c r="AD193" s="8"/>
       <c r="AE193" s="8"/>
     </row>
-    <row r="194" spans="1:32">
+    <row r="194" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A194" s="8">
         <v>1631</v>
       </c>
       <c r="B194" s="9">
-        <v>45807.494074074</v>
+        <v>45807.494074073998</v>
       </c>
       <c r="C194" s="8" t="s">
         <v>46</v>
@@ -19229,12 +19241,12 @@
       <c r="AD194" s="8"/>
       <c r="AE194" s="8"/>
     </row>
-    <row r="195" spans="1:32">
+    <row r="195" spans="1:31" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A195" s="8">
         <v>1632</v>
       </c>
       <c r="B195" s="9">
-        <v>45807.511226852</v>
+        <v>45807.511226852002</v>
       </c>
       <c r="C195" s="8" t="s">
         <v>46</v>
@@ -19310,12 +19322,12 @@
       <c r="AD195" s="8"/>
       <c r="AE195" s="8"/>
     </row>
-    <row r="196" spans="1:32">
+    <row r="196" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A196" s="8">
         <v>1633</v>
       </c>
       <c r="B196" s="9">
-        <v>45807.512002315</v>
+        <v>45807.512002315001</v>
       </c>
       <c r="C196" s="8" t="s">
         <v>46</v>
@@ -19391,12 +19403,12 @@
       <c r="AD196" s="8"/>
       <c r="AE196" s="8"/>
     </row>
-    <row r="197" spans="1:32">
+    <row r="197" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A197" s="8">
         <v>1634</v>
       </c>
       <c r="B197" s="9">
-        <v>45807.512523148</v>
+        <v>45807.512523147998</v>
       </c>
       <c r="C197" s="8" t="s">
         <v>46</v>
@@ -19472,12 +19484,12 @@
       <c r="AD197" s="8"/>
       <c r="AE197" s="8"/>
     </row>
-    <row r="198" spans="1:32">
+    <row r="198" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A198" s="8">
         <v>1635</v>
       </c>
       <c r="B198" s="9">
-        <v>45807.513043981</v>
+        <v>45807.513043981002</v>
       </c>
       <c r="C198" s="8" t="s">
         <v>46</v>
@@ -19553,7 +19565,7 @@
       <c r="AD198" s="8"/>
       <c r="AE198" s="8"/>
     </row>
-    <row r="199" spans="1:32">
+    <row r="199" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A199" s="8">
         <v>1636</v>
       </c>
@@ -19636,7 +19648,7 @@
       <c r="AD199" s="8"/>
       <c r="AE199" s="8"/>
     </row>
-    <row r="200" spans="1:32">
+    <row r="200" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A200" s="8">
         <v>1640</v>
       </c>
@@ -19715,12 +19727,12 @@
       <c r="AD200" s="8"/>
       <c r="AE200" s="8"/>
     </row>
-    <row r="201" spans="1:32">
+    <row r="201" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A201" s="8">
         <v>1641</v>
       </c>
       <c r="B201" s="9">
-        <v>45851.846712963</v>
+        <v>45851.846712963001</v>
       </c>
       <c r="C201" s="8" t="s">
         <v>69</v>
@@ -19794,12 +19806,12 @@
       <c r="AD201" s="8"/>
       <c r="AE201" s="8"/>
     </row>
-    <row r="202" spans="1:32">
+    <row r="202" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A202" s="8">
         <v>1642</v>
       </c>
       <c r="B202" s="9">
-        <v>45851.848541667</v>
+        <v>45851.848541667001</v>
       </c>
       <c r="C202" s="8" t="s">
         <v>69</v>
@@ -19873,7 +19885,7 @@
       <c r="AD202" s="8"/>
       <c r="AE202" s="8"/>
     </row>
-    <row r="203" spans="1:32">
+    <row r="203" spans="1:31" ht="144" x14ac:dyDescent="0.3">
       <c r="A203" s="8">
         <v>1643</v>
       </c>
@@ -19950,12 +19962,12 @@
       <c r="AD203" s="8"/>
       <c r="AE203" s="8"/>
     </row>
-    <row r="204" spans="1:32">
+    <row r="204" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A204" s="8">
         <v>1644</v>
       </c>
       <c r="B204" s="9">
-        <v>45852.431493056</v>
+        <v>45852.431493055999</v>
       </c>
       <c r="C204" s="8" t="s">
         <v>69</v>
@@ -20027,12 +20039,12 @@
       <c r="AD204" s="8"/>
       <c r="AE204" s="8"/>
     </row>
-    <row r="205" spans="1:32">
+    <row r="205" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A205" s="8">
         <v>1645</v>
       </c>
       <c r="B205" s="9">
-        <v>45852.433101852</v>
+        <v>45852.433101852002</v>
       </c>
       <c r="C205" s="8" t="s">
         <v>69</v>
@@ -20102,12 +20114,12 @@
       <c r="AD205" s="8"/>
       <c r="AE205" s="8"/>
     </row>
-    <row r="206" spans="1:32">
+    <row r="206" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A206" s="8">
         <v>1646</v>
       </c>
       <c r="B206" s="9">
-        <v>45852.434421296</v>
+        <v>45852.434421295999</v>
       </c>
       <c r="C206" s="8" t="s">
         <v>69</v>
@@ -20177,7 +20189,7 @@
       <c r="AD206" s="8"/>
       <c r="AE206" s="8"/>
     </row>
-    <row r="207" spans="1:32">
+    <row r="207" spans="1:31" ht="72" x14ac:dyDescent="0.3">
       <c r="A207" s="8">
         <v>1647</v>
       </c>
@@ -20252,12 +20264,12 @@
       <c r="AD207" s="8"/>
       <c r="AE207" s="8"/>
     </row>
-    <row r="208" spans="1:32">
+    <row r="208" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A208" s="8">
         <v>1648</v>
       </c>
       <c r="B208" s="9">
-        <v>45853.439398148</v>
+        <v>45853.439398148003</v>
       </c>
       <c r="C208" s="8" t="s">
         <v>69</v>
@@ -20327,12 +20339,12 @@
       <c r="AD208" s="8"/>
       <c r="AE208" s="8"/>
     </row>
-    <row r="209" spans="1:32">
+    <row r="209" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A209" s="8">
         <v>1649</v>
       </c>
       <c r="B209" s="9">
-        <v>45853.440381944</v>
+        <v>45853.440381943998</v>
       </c>
       <c r="C209" s="8" t="s">
         <v>69</v>
@@ -20402,12 +20414,12 @@
       <c r="AD209" s="8"/>
       <c r="AE209" s="8"/>
     </row>
-    <row r="210" spans="1:32">
+    <row r="210" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A210" s="8">
         <v>1650</v>
       </c>
       <c r="B210" s="9">
-        <v>45853.441724537</v>
+        <v>45853.441724536999</v>
       </c>
       <c r="C210" s="8" t="s">
         <v>69</v>
@@ -20477,12 +20489,12 @@
       <c r="AD210" s="8"/>
       <c r="AE210" s="8"/>
     </row>
-    <row r="211" spans="1:32">
+    <row r="211" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A211" s="8">
         <v>1653</v>
       </c>
       <c r="B211" s="9">
-        <v>45855.662916667</v>
+        <v>45855.662916667003</v>
       </c>
       <c r="C211" s="8" t="s">
         <v>46</v>
@@ -20546,12 +20558,12 @@
       <c r="AD211" s="8"/>
       <c r="AE211" s="8"/>
     </row>
-    <row r="212" spans="1:32">
+    <row r="212" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A212" s="8">
         <v>1654</v>
       </c>
       <c r="B212" s="9">
-        <v>45855.694166667</v>
+        <v>45855.694166667003</v>
       </c>
       <c r="C212" s="8" t="s">
         <v>46</v>
@@ -20615,12 +20627,12 @@
       <c r="AD212" s="8"/>
       <c r="AE212" s="8"/>
     </row>
-    <row r="213" spans="1:32">
+    <row r="213" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A213" s="8">
         <v>1655</v>
       </c>
       <c r="B213" s="9">
-        <v>45855.695277778</v>
+        <v>45855.695277778002</v>
       </c>
       <c r="C213" s="8" t="s">
         <v>46</v>
@@ -20686,7 +20698,7 @@
       <c r="AD213" s="8"/>
       <c r="AE213" s="8"/>
     </row>
-    <row r="214" spans="1:32">
+    <row r="214" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A214" s="8">
         <v>1656</v>
       </c>
@@ -20757,12 +20769,12 @@
       <c r="AD214" s="8"/>
       <c r="AE214" s="8"/>
     </row>
-    <row r="215" spans="1:32">
+    <row r="215" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A215" s="8">
         <v>1657</v>
       </c>
       <c r="B215" s="9">
-        <v>45855.733622685</v>
+        <v>45855.733622685002</v>
       </c>
       <c r="C215" s="8" t="s">
         <v>46</v>
@@ -20824,12 +20836,12 @@
       <c r="AD215" s="8"/>
       <c r="AE215" s="8"/>
     </row>
-    <row r="216" spans="1:32">
+    <row r="216" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A216" s="8">
         <v>1658</v>
       </c>
       <c r="B216" s="9">
-        <v>45856.442604167</v>
+        <v>45856.442604167001</v>
       </c>
       <c r="C216" s="8" t="s">
         <v>29</v>
@@ -20895,12 +20907,12 @@
       <c r="AD216" s="8"/>
       <c r="AE216" s="8"/>
     </row>
-    <row r="217" spans="1:32">
+    <row r="217" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A217" s="8">
         <v>1659</v>
       </c>
       <c r="B217" s="9">
-        <v>45856.443043981</v>
+        <v>45856.443043981002</v>
       </c>
       <c r="C217" s="8" t="s">
         <v>29</v>
@@ -20966,12 +20978,12 @@
       <c r="AD217" s="8"/>
       <c r="AE217" s="8"/>
     </row>
-    <row r="218" spans="1:32">
+    <row r="218" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A218" s="8">
         <v>1660</v>
       </c>
       <c r="B218" s="9">
-        <v>45856.443680556</v>
+        <v>45856.443680556004</v>
       </c>
       <c r="C218" s="8" t="s">
         <v>29</v>
@@ -21035,12 +21047,12 @@
       <c r="AD218" s="8"/>
       <c r="AE218" s="8"/>
     </row>
-    <row r="219" spans="1:32">
+    <row r="219" spans="1:31" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A219" s="8">
         <v>1661</v>
       </c>
       <c r="B219" s="9">
-        <v>45856.444548611</v>
+        <v>45856.444548610998</v>
       </c>
       <c r="C219" s="8" t="s">
         <v>29</v>
@@ -21104,12 +21116,12 @@
       <c r="AD219" s="8"/>
       <c r="AE219" s="8"/>
     </row>
-    <row r="220" spans="1:32">
+    <row r="220" spans="1:31" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A220" s="8">
         <v>1662</v>
       </c>
       <c r="B220" s="9">
-        <v>45856.445127315</v>
+        <v>45856.445127314997</v>
       </c>
       <c r="C220" s="8" t="s">
         <v>29</v>
@@ -21173,7 +21185,7 @@
       <c r="AD220" s="8"/>
       <c r="AE220" s="8"/>
     </row>
-    <row r="221" spans="1:32">
+    <row r="221" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A221" s="8">
         <v>1663</v>
       </c>
@@ -21240,12 +21252,12 @@
       <c r="AD221" s="8"/>
       <c r="AE221" s="8"/>
     </row>
-    <row r="222" spans="1:32">
+    <row r="222" spans="1:31" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A222" s="8">
         <v>1664</v>
       </c>
       <c r="B222" s="9">
-        <v>45856.486828704</v>
+        <v>45856.486828704001</v>
       </c>
       <c r="C222" s="8" t="s">
         <v>29</v>
@@ -21309,12 +21321,12 @@
       <c r="AD222" s="8"/>
       <c r="AE222" s="8"/>
     </row>
-    <row r="223" spans="1:32">
+    <row r="223" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A223" s="8">
         <v>1665</v>
       </c>
       <c r="B223" s="9">
-        <v>45856.487407407</v>
+        <v>45856.487407407003</v>
       </c>
       <c r="C223" s="8" t="s">
         <v>29</v>
@@ -21376,12 +21388,12 @@
       <c r="AD223" s="8"/>
       <c r="AE223" s="8"/>
     </row>
-    <row r="224" spans="1:32">
+    <row r="224" spans="1:31" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A224" s="8">
         <v>1666</v>
       </c>
       <c r="B224" s="9">
-        <v>45856.708043981</v>
+        <v>45856.708043981002</v>
       </c>
       <c r="C224" s="8" t="s">
         <v>29</v>
@@ -21447,12 +21459,12 @@
       <c r="AD224" s="8"/>
       <c r="AE224" s="8"/>
     </row>
-    <row r="225" spans="1:32">
+    <row r="225" spans="1:31" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A225" s="8">
         <v>1667</v>
       </c>
       <c r="B225" s="9">
-        <v>45856.708541667</v>
+        <v>45856.708541667002</v>
       </c>
       <c r="C225" s="8" t="s">
         <v>29</v>
@@ -21518,7 +21530,7 @@
       <c r="AD225" s="8"/>
       <c r="AE225" s="8"/>
     </row>
-    <row r="226" spans="1:32">
+    <row r="226" spans="1:31" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A226" s="8">
         <v>1668</v>
       </c>
@@ -21585,12 +21597,12 @@
       <c r="AD226" s="8"/>
       <c r="AE226" s="8"/>
     </row>
-    <row r="227" spans="1:32">
+    <row r="227" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A227" s="8">
         <v>1671</v>
       </c>
       <c r="B227" s="9">
-        <v>45862.40875</v>
+        <v>45862.408750000002</v>
       </c>
       <c r="C227" s="8" t="s">
         <v>46</v>
@@ -21666,12 +21678,12 @@
       <c r="AD227" s="8"/>
       <c r="AE227" s="8"/>
     </row>
-    <row r="228" spans="1:32">
+    <row r="228" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A228" s="8">
         <v>1672</v>
       </c>
       <c r="B228" s="9">
-        <v>45862.409861111</v>
+        <v>45862.409861111002</v>
       </c>
       <c r="C228" s="8" t="s">
         <v>46</v>
@@ -21747,12 +21759,12 @@
       <c r="AD228" s="8"/>
       <c r="AE228" s="8"/>
     </row>
-    <row r="229" spans="1:32">
+    <row r="229" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A229" s="8">
         <v>1673</v>
       </c>
       <c r="B229" s="9">
-        <v>45862.410659722</v>
+        <v>45862.410659722002</v>
       </c>
       <c r="C229" s="8" t="s">
         <v>46</v>
@@ -21828,12 +21840,12 @@
       <c r="AD229" s="8"/>
       <c r="AE229" s="8"/>
     </row>
-    <row r="230" spans="1:32">
+    <row r="230" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A230" s="8">
         <v>1674</v>
       </c>
       <c r="B230" s="9">
-        <v>45862.411539352</v>
+        <v>45862.411539351997</v>
       </c>
       <c r="C230" s="8" t="s">
         <v>46</v>
@@ -21909,12 +21921,12 @@
       <c r="AD230" s="8"/>
       <c r="AE230" s="8"/>
     </row>
-    <row r="231" spans="1:32">
+    <row r="231" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A231" s="8">
         <v>1675</v>
       </c>
       <c r="B231" s="9">
-        <v>45862.412303241</v>
+        <v>45862.412303240999</v>
       </c>
       <c r="C231" s="8" t="s">
         <v>46</v>
@@ -21990,12 +22002,12 @@
       <c r="AD231" s="8"/>
       <c r="AE231" s="8"/>
     </row>
-    <row r="232" spans="1:32">
+    <row r="232" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A232" s="8">
         <v>1677</v>
       </c>
       <c r="B232" s="9">
-        <v>45889.630949074</v>
+        <v>45889.630949074002</v>
       </c>
       <c r="C232" s="8" t="s">
         <v>46</v>
@@ -22071,12 +22083,12 @@
       <c r="AD232" s="8"/>
       <c r="AE232" s="8"/>
     </row>
-    <row r="233" spans="1:32">
+    <row r="233" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A233" s="8">
         <v>1678</v>
       </c>
       <c r="B233" s="9">
-        <v>45889.632685185</v>
+        <v>45889.632685185003</v>
       </c>
       <c r="C233" s="8" t="s">
         <v>46</v>
@@ -22152,12 +22164,12 @@
       <c r="AD233" s="8"/>
       <c r="AE233" s="8"/>
     </row>
-    <row r="234" spans="1:32">
+    <row r="234" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A234" s="8">
         <v>1679</v>
       </c>
       <c r="B234" s="9">
-        <v>45889.63494213</v>
+        <v>45889.634942129996</v>
       </c>
       <c r="C234" s="8" t="s">
         <v>46</v>
@@ -22233,12 +22245,12 @@
       <c r="AD234" s="8"/>
       <c r="AE234" s="8"/>
     </row>
-    <row r="235" spans="1:32">
+    <row r="235" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A235" s="8">
         <v>1680</v>
       </c>
       <c r="B235" s="9">
-        <v>45889.636342593</v>
+        <v>45889.636342593003</v>
       </c>
       <c r="C235" s="8" t="s">
         <v>46</v>
@@ -22314,12 +22326,12 @@
       <c r="AD235" s="8"/>
       <c r="AE235" s="8"/>
     </row>
-    <row r="236" spans="1:32">
+    <row r="236" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A236" s="8">
         <v>1682</v>
       </c>
       <c r="B236" s="9">
-        <v>45898.357384259</v>
+        <v>45898.357384258998</v>
       </c>
       <c r="C236" s="8" t="s">
         <v>46</v>
@@ -22385,12 +22397,12 @@
       <c r="AD236" s="8"/>
       <c r="AE236" s="8"/>
     </row>
-    <row r="237" spans="1:32">
+    <row r="237" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A237" s="8">
         <v>1683</v>
       </c>
       <c r="B237" s="9">
-        <v>45898.358032407</v>
+        <v>45898.358032406999</v>
       </c>
       <c r="C237" s="8" t="s">
         <v>46</v>
@@ -22456,7 +22468,7 @@
       <c r="AD237" s="8"/>
       <c r="AE237" s="8"/>
     </row>
-    <row r="238" spans="1:32">
+    <row r="238" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A238" s="8">
         <v>1684</v>
       </c>
@@ -22527,12 +22539,12 @@
       <c r="AD238" s="8"/>
       <c r="AE238" s="8"/>
     </row>
-    <row r="239" spans="1:32">
+    <row r="239" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A239" s="8">
         <v>1685</v>
       </c>
       <c r="B239" s="9">
-        <v>45898.359791667</v>
+        <v>45898.359791666997</v>
       </c>
       <c r="C239" s="8" t="s">
         <v>46</v>
@@ -22594,12 +22606,12 @@
       <c r="AD239" s="8"/>
       <c r="AE239" s="8"/>
     </row>
-    <row r="240" spans="1:32">
+    <row r="240" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A240" s="8">
         <v>1686</v>
       </c>
       <c r="B240" s="9">
-        <v>45898.360856481</v>
+        <v>45898.360856480998</v>
       </c>
       <c r="C240" s="8" t="s">
         <v>46</v>
@@ -22661,12 +22673,12 @@
       <c r="AD240" s="8"/>
       <c r="AE240" s="8"/>
     </row>
-    <row r="241" spans="1:32">
+    <row r="241" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A241" s="8">
         <v>1688</v>
       </c>
       <c r="B241" s="9">
-        <v>45904.520358796</v>
+        <v>45904.520358795999</v>
       </c>
       <c r="C241" s="8" t="s">
         <v>238</v>
@@ -22740,7 +22752,7 @@
       <c r="AD241" s="8"/>
       <c r="AE241" s="8"/>
     </row>
-    <row r="242" spans="1:32">
+    <row r="242" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A242" s="8">
         <v>1689</v>
       </c>
@@ -22819,12 +22831,12 @@
       <c r="AD242" s="8"/>
       <c r="AE242" s="8"/>
     </row>
-    <row r="243" spans="1:32">
+    <row r="243" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A243" s="8">
         <v>1690</v>
       </c>
       <c r="B243" s="9">
-        <v>45904.525821759</v>
+        <v>45904.525821759002</v>
       </c>
       <c r="C243" s="8" t="s">
         <v>69</v>
@@ -22898,12 +22910,12 @@
       <c r="AD243" s="8"/>
       <c r="AE243" s="8"/>
     </row>
-    <row r="244" spans="1:32">
+    <row r="244" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A244" s="8">
         <v>1691</v>
       </c>
       <c r="B244" s="9">
-        <v>45904.589143519</v>
+        <v>45904.589143518999</v>
       </c>
       <c r="C244" s="8" t="s">
         <v>69</v>
@@ -22977,12 +22989,12 @@
       <c r="AD244" s="8"/>
       <c r="AE244" s="8"/>
     </row>
-    <row r="245" spans="1:32">
+    <row r="245" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A245" s="8">
         <v>1692</v>
       </c>
       <c r="B245" s="9">
-        <v>45904.589826389</v>
+        <v>45904.589826388998</v>
       </c>
       <c r="C245" s="8" t="s">
         <v>69</v>
@@ -23056,12 +23068,12 @@
       <c r="AD245" s="8"/>
       <c r="AE245" s="8"/>
     </row>
-    <row r="246" spans="1:32">
+    <row r="246" spans="1:31" ht="72" x14ac:dyDescent="0.3">
       <c r="A246" s="8">
         <v>1693</v>
       </c>
       <c r="B246" s="9">
-        <v>45904.655763889</v>
+        <v>45904.655763889001</v>
       </c>
       <c r="C246" s="8" t="s">
         <v>69</v>
@@ -23127,7 +23139,7 @@
       <c r="AD246" s="8"/>
       <c r="AE246" s="8"/>
     </row>
-    <row r="247" spans="1:32">
+    <row r="247" spans="1:31" ht="72" x14ac:dyDescent="0.3">
       <c r="A247" s="8">
         <v>1694</v>
       </c>
@@ -23196,12 +23208,12 @@
       <c r="AD247" s="8"/>
       <c r="AE247" s="8"/>
     </row>
-    <row r="248" spans="1:32">
+    <row r="248" spans="1:31" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A248" s="8">
         <v>1695</v>
       </c>
       <c r="B248" s="9">
-        <v>45904.659074074</v>
+        <v>45904.659074073999</v>
       </c>
       <c r="C248" s="8" t="s">
         <v>69</v>
@@ -23267,12 +23279,12 @@
       <c r="AD248" s="8"/>
       <c r="AE248" s="8"/>
     </row>
-    <row r="249" spans="1:32">
+    <row r="249" spans="1:31" ht="72" x14ac:dyDescent="0.3">
       <c r="A249" s="8">
         <v>1696</v>
       </c>
       <c r="B249" s="9">
-        <v>45904.661400463</v>
+        <v>45904.661400463003</v>
       </c>
       <c r="C249" s="8" t="s">
         <v>69</v>
@@ -23338,12 +23350,12 @@
       <c r="AD249" s="8"/>
       <c r="AE249" s="8"/>
     </row>
-    <row r="250" spans="1:32">
+    <row r="250" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A250" s="8">
         <v>1697</v>
       </c>
       <c r="B250" s="9">
-        <v>45911.677430556</v>
+        <v>45911.677430556003</v>
       </c>
       <c r="C250" s="8" t="s">
         <v>238</v>
@@ -23409,12 +23421,12 @@
       <c r="AD250" s="8"/>
       <c r="AE250" s="8"/>
     </row>
-    <row r="251" spans="1:32">
+    <row r="251" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A251" s="8">
         <v>1698</v>
       </c>
       <c r="B251" s="9">
-        <v>45911.687534722</v>
+        <v>45911.687534721998</v>
       </c>
       <c r="C251" s="8" t="s">
         <v>69</v>
@@ -23480,7 +23492,7 @@
       <c r="AD251" s="8"/>
       <c r="AE251" s="8"/>
     </row>
-    <row r="252" spans="1:32">
+    <row r="252" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A252" s="8">
         <v>1699</v>
       </c>
@@ -23551,12 +23563,12 @@
       <c r="AD252" s="8"/>
       <c r="AE252" s="8"/>
     </row>
-    <row r="253" spans="1:32">
+    <row r="253" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A253" s="8">
         <v>1700</v>
       </c>
       <c r="B253" s="9">
-        <v>45911.708159722</v>
+        <v>45911.708159722002</v>
       </c>
       <c r="C253" s="8" t="s">
         <v>69</v>
@@ -23622,12 +23634,12 @@
       <c r="AD253" s="8"/>
       <c r="AE253" s="8"/>
     </row>
-    <row r="254" spans="1:32">
+    <row r="254" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A254" s="8">
         <v>1701</v>
       </c>
       <c r="B254" s="9">
-        <v>45911.709895833</v>
+        <v>45911.709895833003</v>
       </c>
       <c r="C254" s="8" t="s">
         <v>69</v>
@@ -23693,12 +23705,12 @@
       <c r="AD254" s="8"/>
       <c r="AE254" s="8"/>
     </row>
-    <row r="255" spans="1:32">
+    <row r="255" spans="1:31" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A255" s="8">
         <v>1707</v>
       </c>
       <c r="B255" s="9">
-        <v>45926.389016204</v>
+        <v>45926.389016203997</v>
       </c>
       <c r="C255" s="8" t="s">
         <v>238</v>
@@ -23774,12 +23786,12 @@
       <c r="AD255" s="8"/>
       <c r="AE255" s="8"/>
     </row>
-    <row r="256" spans="1:32">
+    <row r="256" spans="1:31" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A256" s="8">
         <v>1708</v>
       </c>
       <c r="B256" s="9">
-        <v>45926.389976852</v>
+        <v>45926.389976851999</v>
       </c>
       <c r="C256" s="8" t="s">
         <v>238</v>
@@ -23855,12 +23867,12 @@
       <c r="AD256" s="8"/>
       <c r="AE256" s="8"/>
     </row>
-    <row r="257" spans="1:32">
+    <row r="257" spans="1:31" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A257" s="8">
         <v>1709</v>
       </c>
       <c r="B257" s="9">
-        <v>45926.395416667</v>
+        <v>45926.395416667001</v>
       </c>
       <c r="C257" s="8" t="s">
         <v>238</v>
@@ -23936,7 +23948,7 @@
       <c r="AD257" s="8"/>
       <c r="AE257" s="8"/>
     </row>
-    <row r="258" spans="1:32">
+    <row r="258" spans="1:31" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A258" s="8">
         <v>1710</v>
       </c>
@@ -24017,12 +24029,12 @@
       <c r="AD258" s="8"/>
       <c r="AE258" s="8"/>
     </row>
-    <row r="259" spans="1:32">
+    <row r="259" spans="1:31" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A259" s="8">
         <v>1711</v>
       </c>
       <c r="B259" s="9">
-        <v>45926.397384259</v>
+        <v>45926.397384258998</v>
       </c>
       <c r="C259" s="8" t="s">
         <v>69</v>
@@ -24098,7 +24110,7 @@
       <c r="AD259" s="8"/>
       <c r="AE259" s="8"/>
     </row>
-    <row r="260" spans="1:32">
+    <row r="260" spans="1:31" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A260" s="8">
         <v>1712</v>
       </c>
@@ -24179,12 +24191,12 @@
       <c r="AD260" s="8"/>
       <c r="AE260" s="8"/>
     </row>
-    <row r="261" spans="1:32">
+    <row r="261" spans="1:31" ht="144" x14ac:dyDescent="0.3">
       <c r="A261" s="8">
         <v>1713</v>
       </c>
       <c r="B261" s="9">
-        <v>45926.411909722</v>
+        <v>45926.411909722003</v>
       </c>
       <c r="C261" s="8" t="s">
         <v>238</v>
@@ -24250,12 +24262,12 @@
       <c r="AD261" s="8"/>
       <c r="AE261" s="8"/>
     </row>
-    <row r="262" spans="1:32">
+    <row r="262" spans="1:31" ht="144" x14ac:dyDescent="0.3">
       <c r="A262" s="8">
         <v>1714</v>
       </c>
       <c r="B262" s="9">
-        <v>45926.412824074</v>
+        <v>45926.412824074003</v>
       </c>
       <c r="C262" s="8" t="s">
         <v>238</v>
@@ -24323,12 +24335,12 @@
       <c r="AD262" s="8"/>
       <c r="AE262" s="8"/>
     </row>
-    <row r="263" spans="1:32">
+    <row r="263" spans="1:31" ht="144" x14ac:dyDescent="0.3">
       <c r="A263" s="8">
         <v>1715</v>
       </c>
       <c r="B263" s="9">
-        <v>45926.413483796</v>
+        <v>45926.413483796001</v>
       </c>
       <c r="C263" s="8" t="s">
         <v>69</v>
@@ -24396,12 +24408,12 @@
       <c r="AD263" s="8"/>
       <c r="AE263" s="8"/>
     </row>
-    <row r="264" spans="1:32">
+    <row r="264" spans="1:31" ht="144" x14ac:dyDescent="0.3">
       <c r="A264" s="8">
         <v>1716</v>
       </c>
       <c r="B264" s="9">
-        <v>45926.413993056</v>
+        <v>45926.413993055998</v>
       </c>
       <c r="C264" s="8" t="s">
         <v>69</v>
@@ -24469,12 +24481,12 @@
       <c r="AD264" s="8"/>
       <c r="AE264" s="8"/>
     </row>
-    <row r="265" spans="1:32">
+    <row r="265" spans="1:31" ht="144" x14ac:dyDescent="0.3">
       <c r="A265" s="8">
         <v>1717</v>
       </c>
       <c r="B265" s="9">
-        <v>45926.414583333</v>
+        <v>45926.414583332997</v>
       </c>
       <c r="C265" s="8" t="s">
         <v>69</v>
@@ -24542,7 +24554,7 @@
       <c r="AD265" s="8"/>
       <c r="AE265" s="8"/>
     </row>
-    <row r="266" spans="1:32">
+    <row r="266" spans="1:31" ht="144" x14ac:dyDescent="0.3">
       <c r="A266" s="8">
         <v>1718</v>
       </c>
@@ -24615,12 +24627,12 @@
       <c r="AD266" s="8"/>
       <c r="AE266" s="8"/>
     </row>
-    <row r="267" spans="1:32">
+    <row r="267" spans="1:31" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A267" s="8">
         <v>1719</v>
       </c>
       <c r="B267" s="9">
-        <v>45926.438125</v>
+        <v>45926.438125000001</v>
       </c>
       <c r="C267" s="8" t="s">
         <v>238</v>
@@ -24694,12 +24706,12 @@
       <c r="AD267" s="8"/>
       <c r="AE267" s="8"/>
     </row>
-    <row r="268" spans="1:32">
+    <row r="268" spans="1:31" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A268" s="8">
         <v>1720</v>
       </c>
       <c r="B268" s="9">
-        <v>45926.439270833</v>
+        <v>45926.439270832998</v>
       </c>
       <c r="C268" s="8" t="s">
         <v>238</v>
@@ -24773,12 +24785,12 @@
       <c r="AD268" s="8"/>
       <c r="AE268" s="8"/>
     </row>
-    <row r="269" spans="1:32">
+    <row r="269" spans="1:31" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A269" s="8">
         <v>1721</v>
       </c>
       <c r="B269" s="9">
-        <v>45926.443113426</v>
+        <v>45926.443113426001</v>
       </c>
       <c r="C269" s="8" t="s">
         <v>238</v>
@@ -24852,12 +24864,12 @@
       <c r="AD269" s="8"/>
       <c r="AE269" s="8"/>
     </row>
-    <row r="270" spans="1:32">
+    <row r="270" spans="1:31" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A270" s="8">
         <v>1722</v>
       </c>
       <c r="B270" s="9">
-        <v>45926.445474537</v>
+        <v>45926.445474537002</v>
       </c>
       <c r="C270" s="8" t="s">
         <v>69</v>
@@ -24933,12 +24945,12 @@
       <c r="AD270" s="8"/>
       <c r="AE270" s="8"/>
     </row>
-    <row r="271" spans="1:32">
+    <row r="271" spans="1:31" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A271" s="8">
         <v>1723</v>
       </c>
       <c r="B271" s="9">
-        <v>45926.446412037</v>
+        <v>45926.446412037003</v>
       </c>
       <c r="C271" s="8" t="s">
         <v>69</v>
@@ -25012,12 +25024,12 @@
       <c r="AD271" s="8"/>
       <c r="AE271" s="8"/>
     </row>
-    <row r="272" spans="1:32">
+    <row r="272" spans="1:31" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A272" s="8">
         <v>1724</v>
       </c>
       <c r="B272" s="9">
-        <v>45926.447789352</v>
+        <v>45926.447789352002</v>
       </c>
       <c r="C272" s="8" t="s">
         <v>69</v>
@@ -25093,12 +25105,12 @@
       <c r="AD272" s="8"/>
       <c r="AE272" s="8"/>
     </row>
-    <row r="273" spans="1:32">
+    <row r="273" spans="1:31" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A273" s="8">
         <v>1725</v>
       </c>
       <c r="B273" s="9">
-        <v>45926.46931713</v>
+        <v>45926.469317130002</v>
       </c>
       <c r="C273" s="8" t="s">
         <v>238</v>
@@ -25166,12 +25178,12 @@
       <c r="AD273" s="8"/>
       <c r="AE273" s="8"/>
     </row>
-    <row r="274" spans="1:32">
+    <row r="274" spans="1:31" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A274" s="8">
         <v>1726</v>
       </c>
       <c r="B274" s="9">
-        <v>45926.469907407</v>
+        <v>45926.469907407001</v>
       </c>
       <c r="C274" s="8" t="s">
         <v>238</v>
@@ -25239,12 +25251,12 @@
       <c r="AD274" s="8"/>
       <c r="AE274" s="8"/>
     </row>
-    <row r="275" spans="1:32">
+    <row r="275" spans="1:31" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A275" s="8">
         <v>1727</v>
       </c>
       <c r="B275" s="9">
-        <v>45926.472569444</v>
+        <v>45926.472569443999</v>
       </c>
       <c r="C275" s="8" t="s">
         <v>238</v>
@@ -25312,7 +25324,7 @@
       <c r="AD275" s="8"/>
       <c r="AE275" s="8"/>
     </row>
-    <row r="276" spans="1:32">
+    <row r="276" spans="1:31" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A276" s="8">
         <v>1728</v>
       </c>
@@ -25385,12 +25397,12 @@
       <c r="AD276" s="8"/>
       <c r="AE276" s="8"/>
     </row>
-    <row r="277" spans="1:32">
+    <row r="277" spans="1:31" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A277" s="8">
         <v>1729</v>
       </c>
       <c r="B277" s="9">
-        <v>45926.47369213</v>
+        <v>45926.473692129999</v>
       </c>
       <c r="C277" s="8" t="s">
         <v>69</v>
@@ -25458,12 +25470,12 @@
       <c r="AD277" s="8"/>
       <c r="AE277" s="8"/>
     </row>
-    <row r="278" spans="1:32">
+    <row r="278" spans="1:31" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A278" s="8">
         <v>1730</v>
       </c>
       <c r="B278" s="9">
-        <v>45926.47443287</v>
+        <v>45926.474432870004</v>
       </c>
       <c r="C278" s="8" t="s">
         <v>69</v>
@@ -25531,12 +25543,12 @@
       <c r="AD278" s="8"/>
       <c r="AE278" s="8"/>
     </row>
-    <row r="279" spans="1:32">
+    <row r="279" spans="1:31" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A279" s="8">
         <v>1731</v>
       </c>
       <c r="B279" s="9">
-        <v>45926.475115741</v>
+        <v>45926.475115740999</v>
       </c>
       <c r="C279" s="8" t="s">
         <v>69</v>
@@ -25602,7 +25614,7 @@
       <c r="AD279" s="8"/>
       <c r="AE279" s="8"/>
     </row>
-    <row r="280" spans="1:32">
+    <row r="280" spans="1:31" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A280" s="8">
         <v>1732</v>
       </c>
@@ -25675,12 +25687,12 @@
       <c r="AD280" s="8"/>
       <c r="AE280" s="8"/>
     </row>
-    <row r="281" spans="1:32">
+    <row r="281" spans="1:31" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A281" s="8">
         <v>1733</v>
       </c>
       <c r="B281" s="9">
-        <v>45926.477002315</v>
+        <v>45926.477002314998</v>
       </c>
       <c r="C281" s="8" t="s">
         <v>69</v>
@@ -25746,12 +25758,12 @@
       <c r="AD281" s="8"/>
       <c r="AE281" s="8"/>
     </row>
-    <row r="282" spans="1:32">
+    <row r="282" spans="1:31" ht="331.2" x14ac:dyDescent="0.3">
       <c r="A282" s="8">
         <v>1734</v>
       </c>
       <c r="B282" s="9">
-        <v>45938.428900463</v>
+        <v>45938.428900462997</v>
       </c>
       <c r="C282" s="8" t="s">
         <v>29</v>
@@ -25815,12 +25827,12 @@
       <c r="AD282" s="8"/>
       <c r="AE282" s="8"/>
     </row>
-    <row r="283" spans="1:32">
+    <row r="283" spans="1:31" ht="331.2" x14ac:dyDescent="0.3">
       <c r="A283" s="8">
         <v>1735</v>
       </c>
       <c r="B283" s="9">
-        <v>45938.431319444</v>
+        <v>45938.431319443996</v>
       </c>
       <c r="C283" s="8" t="s">
         <v>238</v>
@@ -25888,12 +25900,12 @@
       <c r="AD283" s="8"/>
       <c r="AE283" s="8"/>
     </row>
-    <row r="284" spans="1:32">
+    <row r="284" spans="1:31" ht="331.2" x14ac:dyDescent="0.3">
       <c r="A284" s="8">
         <v>1736</v>
       </c>
       <c r="B284" s="9">
-        <v>45938.432291667</v>
+        <v>45938.432291666999</v>
       </c>
       <c r="C284" s="8" t="s">
         <v>238</v>
@@ -25959,12 +25971,12 @@
       <c r="AD284" s="8"/>
       <c r="AE284" s="8"/>
     </row>
-    <row r="285" spans="1:32">
+    <row r="285" spans="1:31" ht="331.2" x14ac:dyDescent="0.3">
       <c r="A285" s="8">
         <v>1737</v>
       </c>
       <c r="B285" s="9">
-        <v>45938.433125</v>
+        <v>45938.433125000003</v>
       </c>
       <c r="C285" s="8" t="s">
         <v>46</v>
@@ -26030,12 +26042,12 @@
       <c r="AD285" s="8"/>
       <c r="AE285" s="8"/>
     </row>
-    <row r="286" spans="1:32">
+    <row r="286" spans="1:31" ht="331.2" x14ac:dyDescent="0.3">
       <c r="A286" s="8">
         <v>1738</v>
       </c>
       <c r="B286" s="9">
-        <v>45938.434895833</v>
+        <v>45938.434895833001</v>
       </c>
       <c r="C286" s="8" t="s">
         <v>29</v>
@@ -26103,12 +26115,12 @@
       <c r="AD286" s="8"/>
       <c r="AE286" s="8"/>
     </row>
-    <row r="287" spans="1:32">
+    <row r="287" spans="1:31" ht="331.2" x14ac:dyDescent="0.3">
       <c r="A287" s="8">
         <v>1739</v>
       </c>
       <c r="B287" s="9">
-        <v>45938.435833333</v>
+        <v>45938.435833333002</v>
       </c>
       <c r="C287" s="8" t="s">
         <v>29</v>
@@ -26172,12 +26184,12 @@
       <c r="AD287" s="8"/>
       <c r="AE287" s="8"/>
     </row>
-    <row r="288" spans="1:32">
+    <row r="288" spans="1:31" ht="331.2" x14ac:dyDescent="0.3">
       <c r="A288" s="8">
         <v>1740</v>
       </c>
       <c r="B288" s="9">
-        <v>45938.437025463</v>
+        <v>45938.437025462998</v>
       </c>
       <c r="C288" s="8" t="s">
         <v>46</v>
@@ -26245,12 +26257,12 @@
       <c r="AD288" s="8"/>
       <c r="AE288" s="8"/>
     </row>
-    <row r="289" spans="1:32">
+    <row r="289" spans="1:31" ht="331.2" x14ac:dyDescent="0.3">
       <c r="A289" s="8">
         <v>1741</v>
       </c>
       <c r="B289" s="9">
-        <v>45938.438113426</v>
+        <v>45938.438113425997</v>
       </c>
       <c r="C289" s="8" t="s">
         <v>29</v>
@@ -26314,12 +26326,12 @@
       <c r="AD289" s="8"/>
       <c r="AE289" s="8"/>
     </row>
-    <row r="290" spans="1:32">
+    <row r="290" spans="1:31" ht="331.2" x14ac:dyDescent="0.3">
       <c r="A290" s="8">
         <v>1742</v>
       </c>
       <c r="B290" s="9">
-        <v>45938.438842593</v>
+        <v>45938.438842593001</v>
       </c>
       <c r="C290" s="8" t="s">
         <v>29</v>
@@ -26383,12 +26395,12 @@
       <c r="AD290" s="8"/>
       <c r="AE290" s="8"/>
     </row>
-    <row r="291" spans="1:32">
+    <row r="291" spans="1:31" ht="331.2" x14ac:dyDescent="0.3">
       <c r="A291" s="8">
         <v>1743</v>
       </c>
       <c r="B291" s="9">
-        <v>45938.439548611</v>
+        <v>45938.439548611001</v>
       </c>
       <c r="C291" s="8" t="s">
         <v>29</v>
@@ -26456,12 +26468,12 @@
       <c r="AD291" s="8"/>
       <c r="AE291" s="8"/>
     </row>
-    <row r="292" spans="1:32">
+    <row r="292" spans="1:31" ht="331.2" x14ac:dyDescent="0.3">
       <c r="A292" s="8">
         <v>1744</v>
       </c>
       <c r="B292" s="9">
-        <v>45938.440358796</v>
+        <v>45938.440358795997</v>
       </c>
       <c r="C292" s="8" t="s">
         <v>29</v>
@@ -26527,7 +26539,7 @@
       <c r="AD292" s="8"/>
       <c r="AE292" s="8"/>
     </row>
-    <row r="293" spans="1:32">
+    <row r="293" spans="1:31" ht="331.2" x14ac:dyDescent="0.3">
       <c r="A293" s="8">
         <v>1745</v>
       </c>
@@ -26596,12 +26608,12 @@
       <c r="AD293" s="8"/>
       <c r="AE293" s="8"/>
     </row>
-    <row r="294" spans="1:32">
+    <row r="294" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A294" s="8">
         <v>1746</v>
       </c>
       <c r="B294" s="9">
-        <v>45938.730405093</v>
+        <v>45938.730405093003</v>
       </c>
       <c r="C294" s="8" t="s">
         <v>46</v>
@@ -26677,12 +26689,12 @@
       <c r="AD294" s="8"/>
       <c r="AE294" s="8"/>
     </row>
-    <row r="295" spans="1:32">
+    <row r="295" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A295" s="8">
         <v>1747</v>
       </c>
       <c r="B295" s="9">
-        <v>45938.731006944</v>
+        <v>45938.731006943999</v>
       </c>
       <c r="C295" s="8" t="s">
         <v>46</v>
@@ -26758,12 +26770,12 @@
       <c r="AD295" s="8"/>
       <c r="AE295" s="8"/>
     </row>
-    <row r="296" spans="1:32">
+    <row r="296" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A296" s="8">
         <v>1748</v>
       </c>
       <c r="B296" s="9">
-        <v>45938.732372685</v>
+        <v>45938.732372685001</v>
       </c>
       <c r="C296" s="8" t="s">
         <v>46</v>
@@ -26839,12 +26851,12 @@
       <c r="AD296" s="8"/>
       <c r="AE296" s="8"/>
     </row>
-    <row r="297" spans="1:32">
+    <row r="297" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A297" s="8">
         <v>1749</v>
       </c>
       <c r="B297" s="9">
-        <v>45938.732962963</v>
+        <v>45938.732962962997</v>
       </c>
       <c r="C297" s="8" t="s">
         <v>46</v>
@@ -26920,7 +26932,7 @@
       <c r="AD297" s="8"/>
       <c r="AE297" s="8"/>
     </row>
-    <row r="298" spans="1:32">
+    <row r="298" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A298" s="8">
         <v>1750</v>
       </c>
@@ -27001,12 +27013,12 @@
       <c r="AD298" s="8"/>
       <c r="AE298" s="8"/>
     </row>
-    <row r="299" spans="1:32">
+    <row r="299" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A299" s="8">
         <v>1752</v>
       </c>
       <c r="B299" s="9">
-        <v>45938.740127315</v>
+        <v>45938.740127315003</v>
       </c>
       <c r="C299" s="8" t="s">
         <v>46</v>
@@ -27082,12 +27094,12 @@
       <c r="AD299" s="8"/>
       <c r="AE299" s="8"/>
     </row>
-    <row r="300" spans="1:32">
+    <row r="300" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A300" s="8">
         <v>1753</v>
       </c>
       <c r="B300" s="9">
-        <v>45938.740891204</v>
+        <v>45938.740891203997</v>
       </c>
       <c r="C300" s="8" t="s">
         <v>46</v>
@@ -27163,12 +27175,12 @@
       <c r="AD300" s="8"/>
       <c r="AE300" s="8"/>
     </row>
-    <row r="301" spans="1:32">
+    <row r="301" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A301" s="8">
         <v>1754</v>
       </c>
       <c r="B301" s="9">
-        <v>45938.742928241</v>
+        <v>45938.742928241001</v>
       </c>
       <c r="C301" s="8" t="s">
         <v>46</v>
@@ -27244,12 +27256,12 @@
       <c r="AD301" s="8"/>
       <c r="AE301" s="8"/>
     </row>
-    <row r="302" spans="1:32">
+    <row r="302" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A302" s="8">
         <v>1755</v>
       </c>
       <c r="B302" s="9">
-        <v>45938.743645833</v>
+        <v>45938.743645832998</v>
       </c>
       <c r="C302" s="8" t="s">
         <v>46</v>
@@ -27325,12 +27337,12 @@
       <c r="AD302" s="8"/>
       <c r="AE302" s="8"/>
     </row>
-    <row r="303" spans="1:32">
+    <row r="303" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A303" s="8">
         <v>1756</v>
       </c>
       <c r="B303" s="9">
-        <v>45938.744548611</v>
+        <v>45938.744548611001</v>
       </c>
       <c r="C303" s="8" t="s">
         <v>46</v>
@@ -27406,12 +27418,12 @@
       <c r="AD303" s="8"/>
       <c r="AE303" s="8"/>
     </row>
-    <row r="304" spans="1:32">
+    <row r="304" spans="1:31" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A304" s="8">
         <v>1759</v>
       </c>
       <c r="B304" s="9">
-        <v>45940.400729167</v>
+        <v>45940.400729166999</v>
       </c>
       <c r="C304" s="8" t="s">
         <v>29</v>
@@ -27477,7 +27489,7 @@
       <c r="AD304" s="8"/>
       <c r="AE304" s="8"/>
     </row>
-    <row r="305" spans="1:32">
+    <row r="305" spans="1:31" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A305" s="8">
         <v>1760</v>
       </c>
@@ -27548,12 +27560,12 @@
       <c r="AD305" s="8"/>
       <c r="AE305" s="8"/>
     </row>
-    <row r="306" spans="1:32">
+    <row r="306" spans="1:31" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A306" s="8">
         <v>1762</v>
       </c>
       <c r="B306" s="9">
-        <v>45940.405</v>
+        <v>45940.404999999999</v>
       </c>
       <c r="C306" s="8" t="s">
         <v>238</v>
@@ -27619,12 +27631,12 @@
       <c r="AD306" s="8"/>
       <c r="AE306" s="8"/>
     </row>
-    <row r="307" spans="1:32">
+    <row r="307" spans="1:31" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A307" s="8">
         <v>1763</v>
       </c>
       <c r="B307" s="9">
-        <v>45940.406400463</v>
+        <v>45940.406400462998</v>
       </c>
       <c r="C307" s="8" t="s">
         <v>238</v>
@@ -27692,12 +27704,12 @@
       <c r="AD307" s="8"/>
       <c r="AE307" s="8"/>
     </row>
-    <row r="308" spans="1:32">
+    <row r="308" spans="1:31" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A308" s="8">
         <v>1764</v>
       </c>
       <c r="B308" s="9">
-        <v>45940.408854167</v>
+        <v>45940.408854166999</v>
       </c>
       <c r="C308" s="8" t="s">
         <v>238</v>
@@ -27763,12 +27775,12 @@
       <c r="AD308" s="8"/>
       <c r="AE308" s="8"/>
     </row>
-    <row r="309" spans="1:32">
+    <row r="309" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A309" s="8">
         <v>1767</v>
       </c>
       <c r="B309" s="9">
-        <v>45954.446493056</v>
+        <v>45954.446493055999</v>
       </c>
       <c r="C309" s="8" t="s">
         <v>69</v>
@@ -27834,12 +27846,12 @@
       <c r="AD309" s="8"/>
       <c r="AE309" s="8"/>
     </row>
-    <row r="310" spans="1:32">
+    <row r="310" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A310" s="8">
         <v>1768</v>
       </c>
       <c r="B310" s="9">
-        <v>45954.452453704</v>
+        <v>45954.452453703998</v>
       </c>
       <c r="C310" s="8" t="s">
         <v>69</v>
@@ -27905,12 +27917,12 @@
       <c r="AD310" s="8"/>
       <c r="AE310" s="8"/>
     </row>
-    <row r="311" spans="1:32">
+    <row r="311" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A311" s="8">
         <v>1769</v>
       </c>
       <c r="B311" s="9">
-        <v>45954.453773148</v>
+        <v>45954.453773148001</v>
       </c>
       <c r="C311" s="8" t="s">
         <v>69</v>
@@ -27976,12 +27988,12 @@
       <c r="AD311" s="8"/>
       <c r="AE311" s="8"/>
     </row>
-    <row r="312" spans="1:32">
+    <row r="312" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A312" s="8">
         <v>1770</v>
       </c>
       <c r="B312" s="9">
-        <v>45954.455335648</v>
+        <v>45954.455335648003</v>
       </c>
       <c r="C312" s="8" t="s">
         <v>238</v>
@@ -28047,12 +28059,12 @@
       <c r="AD312" s="8"/>
       <c r="AE312" s="8"/>
     </row>
-    <row r="313" spans="1:32">
+    <row r="313" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A313" s="8">
         <v>1771</v>
       </c>
       <c r="B313" s="9">
-        <v>45954.457349537</v>
+        <v>45954.457349536999</v>
       </c>
       <c r="C313" s="8" t="s">
         <v>949</v>
@@ -28118,12 +28130,12 @@
       <c r="AD313" s="8"/>
       <c r="AE313" s="8"/>
     </row>
-    <row r="314" spans="1:32">
+    <row r="314" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A314" s="8">
         <v>1772</v>
       </c>
       <c r="B314" s="9">
-        <v>45959.508854167</v>
+        <v>45959.508854166997</v>
       </c>
       <c r="C314" s="8" t="s">
         <v>238</v>
@@ -28195,12 +28207,12 @@
       <c r="AD314" s="8"/>
       <c r="AE314" s="8"/>
     </row>
-    <row r="315" spans="1:32">
+    <row r="315" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A315" s="8">
         <v>1773</v>
       </c>
       <c r="B315" s="9">
-        <v>45959.51125</v>
+        <v>45959.511250000003</v>
       </c>
       <c r="C315" s="8" t="s">
         <v>46</v>
@@ -28274,12 +28286,12 @@
       <c r="AD315" s="8"/>
       <c r="AE315" s="8"/>
     </row>
-    <row r="316" spans="1:32">
+    <row r="316" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A316" s="8">
         <v>1774</v>
       </c>
       <c r="B316" s="9">
-        <v>45959.512106481</v>
+        <v>45959.512106481001</v>
       </c>
       <c r="C316" s="8" t="s">
         <v>46</v>
@@ -28351,12 +28363,12 @@
       <c r="AD316" s="8"/>
       <c r="AE316" s="8"/>
     </row>
-    <row r="317" spans="1:32">
+    <row r="317" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A317" s="8">
         <v>1775</v>
       </c>
       <c r="B317" s="9">
-        <v>45959.513703704</v>
+        <v>45959.513703703997</v>
       </c>
       <c r="C317" s="8" t="s">
         <v>949</v>
@@ -28428,12 +28440,12 @@
       <c r="AD317" s="8"/>
       <c r="AE317" s="8"/>
     </row>
-    <row r="318" spans="1:32">
+    <row r="318" spans="1:31" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A318" s="8">
         <v>1776</v>
       </c>
       <c r="B318" s="9">
-        <v>45960.3525</v>
+        <v>45960.352500000001</v>
       </c>
       <c r="C318" s="8" t="s">
         <v>46</v>
@@ -28499,12 +28511,12 @@
       <c r="AD318" s="8"/>
       <c r="AE318" s="8"/>
     </row>
-    <row r="319" spans="1:32">
+    <row r="319" spans="1:31" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A319" s="8">
         <v>1777</v>
       </c>
       <c r="B319" s="9">
-        <v>45960.353252315</v>
+        <v>45960.353252314999</v>
       </c>
       <c r="C319" s="8" t="s">
         <v>46</v>
@@ -28570,12 +28582,12 @@
       <c r="AD319" s="8"/>
       <c r="AE319" s="8"/>
     </row>
-    <row r="320" spans="1:32">
+    <row r="320" spans="1:31" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A320" s="8">
         <v>1778</v>
       </c>
       <c r="B320" s="9">
-        <v>45960.353796296</v>
+        <v>45960.353796296004</v>
       </c>
       <c r="C320" s="8" t="s">
         <v>46</v>
@@ -28641,12 +28653,12 @@
       <c r="AD320" s="8"/>
       <c r="AE320" s="8"/>
     </row>
-    <row r="321" spans="1:32">
+    <row r="321" spans="1:31" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A321" s="8">
         <v>1779</v>
       </c>
       <c r="B321" s="9">
-        <v>45960.448773148</v>
+        <v>45960.448773147997</v>
       </c>
       <c r="C321" s="8" t="s">
         <v>46</v>
@@ -28712,12 +28724,12 @@
       <c r="AD321" s="8"/>
       <c r="AE321" s="8"/>
     </row>
-    <row r="322" spans="1:32">
+    <row r="322" spans="1:31" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A322" s="8">
         <v>1780</v>
       </c>
       <c r="B322" s="9">
-        <v>45960.830439815</v>
+        <v>45960.830439814999</v>
       </c>
       <c r="C322" s="8" t="s">
         <v>46</v>
@@ -28781,12 +28793,12 @@
       <c r="AD322" s="8"/>
       <c r="AE322" s="8"/>
     </row>
-    <row r="323" spans="1:32">
+    <row r="323" spans="1:31" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A323" s="8">
         <v>1781</v>
       </c>
       <c r="B323" s="9">
-        <v>45960.83505787</v>
+        <v>45960.835057869997</v>
       </c>
       <c r="C323" s="8" t="s">
         <v>46</v>
@@ -28850,7 +28862,7 @@
       <c r="AD323" s="8"/>
       <c r="AE323" s="8"/>
     </row>
-    <row r="324" spans="1:32">
+    <row r="324" spans="1:31" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A324" s="8">
         <v>1782</v>
       </c>
@@ -28917,12 +28929,12 @@
       <c r="AD324" s="8"/>
       <c r="AE324" s="8"/>
     </row>
-    <row r="325" spans="1:32">
+    <row r="325" spans="1:31" ht="302.39999999999998" x14ac:dyDescent="0.3">
       <c r="A325" s="8">
         <v>1783</v>
       </c>
       <c r="B325" s="9">
-        <v>45961.332928241</v>
+        <v>45961.332928240998</v>
       </c>
       <c r="C325" s="8" t="s">
         <v>46</v>
@@ -28986,7 +28998,7 @@
       <c r="AD325" s="8"/>
       <c r="AE325" s="8"/>
     </row>
-    <row r="326" spans="1:32">
+    <row r="326" spans="1:31" ht="302.39999999999998" x14ac:dyDescent="0.3">
       <c r="A326" s="8">
         <v>1784</v>
       </c>
@@ -29053,12 +29065,12 @@
       <c r="AD326" s="8"/>
       <c r="AE326" s="8"/>
     </row>
-    <row r="327" spans="1:32">
+    <row r="327" spans="1:31" ht="302.39999999999998" x14ac:dyDescent="0.3">
       <c r="A327" s="8">
         <v>1785</v>
       </c>
       <c r="B327" s="9">
-        <v>45961.335185185</v>
+        <v>45961.335185185002</v>
       </c>
       <c r="C327" s="8" t="s">
         <v>46</v>
@@ -29120,12 +29132,12 @@
       <c r="AD327" s="8"/>
       <c r="AE327" s="8"/>
     </row>
-    <row r="328" spans="1:32">
+    <row r="328" spans="1:31" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A328" s="8">
         <v>1792</v>
       </c>
       <c r="B328" s="9">
-        <v>45962.708113426</v>
+        <v>45962.708113426001</v>
       </c>
       <c r="C328" s="8" t="s">
         <v>46</v>
@@ -29187,12 +29199,12 @@
       <c r="AD328" s="8"/>
       <c r="AE328" s="8"/>
     </row>
-    <row r="329" spans="1:32">
+    <row r="329" spans="1:31" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A329" s="8">
         <v>1793</v>
       </c>
       <c r="B329" s="9">
-        <v>45962.709502315</v>
+        <v>45962.709502315003</v>
       </c>
       <c r="C329" s="8" t="s">
         <v>69</v>
@@ -29254,12 +29266,12 @@
       <c r="AD329" s="8"/>
       <c r="AE329" s="8"/>
     </row>
-    <row r="330" spans="1:32">
+    <row r="330" spans="1:31" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A330" s="8">
         <v>1794</v>
       </c>
       <c r="B330" s="9">
-        <v>45962.710462963</v>
+        <v>45962.710462962998</v>
       </c>
       <c r="C330" s="8" t="s">
         <v>46</v>
@@ -29321,12 +29333,12 @@
       <c r="AD330" s="8"/>
       <c r="AE330" s="8"/>
     </row>
-    <row r="331" spans="1:32">
+    <row r="331" spans="1:31" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A331" s="8">
         <v>1795</v>
       </c>
       <c r="B331" s="9">
-        <v>45962.77443287</v>
+        <v>45962.774432869999</v>
       </c>
       <c r="C331" s="8" t="s">
         <v>69</v>
@@ -29392,12 +29404,12 @@
       <c r="AD331" s="8"/>
       <c r="AE331" s="8"/>
     </row>
-    <row r="332" spans="1:32">
+    <row r="332" spans="1:31" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A332" s="8">
         <v>1796</v>
       </c>
       <c r="B332" s="9">
-        <v>45962.781145833</v>
+        <v>45962.781145833003</v>
       </c>
       <c r="C332" s="8" t="s">
         <v>69</v>
@@ -29463,12 +29475,12 @@
       <c r="AD332" s="8"/>
       <c r="AE332" s="8"/>
     </row>
-    <row r="333" spans="1:32">
+    <row r="333" spans="1:31" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A333" s="8">
         <v>1797</v>
       </c>
       <c r="B333" s="9">
-        <v>45962.7871875</v>
+        <v>45962.787187499998</v>
       </c>
       <c r="C333" s="8" t="s">
         <v>69</v>
@@ -29534,12 +29546,12 @@
       <c r="AD333" s="8"/>
       <c r="AE333" s="8"/>
     </row>
-    <row r="334" spans="1:32">
+    <row r="334" spans="1:31" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A334" s="8">
         <v>1798</v>
       </c>
       <c r="B334" s="9">
-        <v>45962.788576389</v>
+        <v>45962.788576389001</v>
       </c>
       <c r="C334" s="8" t="s">
         <v>238</v>
@@ -29607,12 +29619,12 @@
       <c r="AD334" s="8"/>
       <c r="AE334" s="8"/>
     </row>
-    <row r="335" spans="1:32">
+    <row r="335" spans="1:31" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A335" s="8">
         <v>1799</v>
       </c>
       <c r="B335" s="9">
-        <v>45962.790381944</v>
+        <v>45962.790381944003</v>
       </c>
       <c r="C335" s="8" t="s">
         <v>238</v>
@@ -29678,12 +29690,12 @@
       <c r="AD335" s="8"/>
       <c r="AE335" s="8"/>
     </row>
-    <row r="336" spans="1:32">
+    <row r="336" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A336" s="8">
         <v>1800</v>
       </c>
       <c r="B336" s="9">
-        <v>45962.840324074</v>
+        <v>45962.840324074001</v>
       </c>
       <c r="C336" s="8" t="s">
         <v>29</v>
@@ -29747,12 +29759,12 @@
       <c r="AD336" s="8"/>
       <c r="AE336" s="8"/>
     </row>
-    <row r="337" spans="1:32">
+    <row r="337" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A337" s="8">
         <v>1801</v>
       </c>
       <c r="B337" s="9">
-        <v>45962.841053241</v>
+        <v>45962.841053240998</v>
       </c>
       <c r="C337" s="8" t="s">
         <v>29</v>
@@ -29814,7 +29826,7 @@
       <c r="AD337" s="8"/>
       <c r="AE337" s="8"/>
     </row>
-    <row r="338" spans="1:32">
+    <row r="338" spans="1:31" ht="144" x14ac:dyDescent="0.3">
       <c r="A338" s="8">
         <v>1811</v>
       </c>
@@ -29885,12 +29897,12 @@
       <c r="AD338" s="8"/>
       <c r="AE338" s="8"/>
     </row>
-    <row r="339" spans="1:32">
+    <row r="339" spans="1:31" ht="144" x14ac:dyDescent="0.3">
       <c r="A339" s="8">
         <v>1812</v>
       </c>
       <c r="B339" s="9">
-        <v>45965.660729167</v>
+        <v>45965.660729167001</v>
       </c>
       <c r="C339" s="8" t="s">
         <v>238</v>
@@ -29956,12 +29968,12 @@
       <c r="AD339" s="8"/>
       <c r="AE339" s="8"/>
     </row>
-    <row r="340" spans="1:32">
+    <row r="340" spans="1:31" ht="144" x14ac:dyDescent="0.3">
       <c r="A340" s="8">
         <v>1813</v>
       </c>
       <c r="B340" s="9">
-        <v>45966.375497685</v>
+        <v>45966.375497685003</v>
       </c>
       <c r="C340" s="8" t="s">
         <v>69</v>
@@ -30025,12 +30037,12 @@
       <c r="AD340" s="8"/>
       <c r="AE340" s="8"/>
     </row>
-    <row r="341" spans="1:32">
+    <row r="341" spans="1:31" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A341" s="8">
         <v>1814</v>
       </c>
       <c r="B341" s="9">
-        <v>45985.445983796</v>
+        <v>45985.445983796002</v>
       </c>
       <c r="C341" s="8" t="s">
         <v>46</v>
@@ -30098,12 +30110,12 @@
       <c r="AD341" s="8"/>
       <c r="AE341" s="8"/>
     </row>
-    <row r="342" spans="1:32">
+    <row r="342" spans="1:31" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A342" s="8">
         <v>1815</v>
       </c>
       <c r="B342" s="9">
-        <v>45985.448229167</v>
+        <v>45985.448229166999</v>
       </c>
       <c r="C342" s="8" t="s">
         <v>46</v>
@@ -30171,12 +30183,12 @@
       <c r="AD342" s="8"/>
       <c r="AE342" s="8"/>
     </row>
-    <row r="343" spans="1:32">
+    <row r="343" spans="1:31" ht="72" x14ac:dyDescent="0.3">
       <c r="A343" s="8">
         <v>1816</v>
       </c>
       <c r="B343" s="9">
-        <v>46001.378321759</v>
+        <v>46001.378321759003</v>
       </c>
       <c r="C343" s="8" t="s">
         <v>46</v>
@@ -30244,7 +30256,7 @@
       <c r="AD343" s="8"/>
       <c r="AE343" s="8"/>
     </row>
-    <row r="344" spans="1:32">
+    <row r="344" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A344" s="8">
         <v>1817</v>
       </c>
@@ -30315,12 +30327,12 @@
       <c r="AD344" s="8"/>
       <c r="AE344" s="8"/>
     </row>
-    <row r="345" spans="1:32">
+    <row r="345" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A345" s="8">
         <v>1818</v>
       </c>
       <c r="B345" s="9">
-        <v>46001.380439815</v>
+        <v>46001.380439815002</v>
       </c>
       <c r="C345" s="8" t="s">
         <v>46</v>
@@ -30388,12 +30400,12 @@
       <c r="AD345" s="8"/>
       <c r="AE345" s="8"/>
     </row>
-    <row r="346" spans="1:32">
+    <row r="346" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A346" s="8">
         <v>1819</v>
       </c>
       <c r="B346" s="9">
-        <v>46001.381342593</v>
+        <v>46001.381342592998</v>
       </c>
       <c r="C346" s="8" t="s">
         <v>46</v>
@@ -30459,12 +30471,12 @@
       <c r="AD346" s="8"/>
       <c r="AE346" s="8"/>
     </row>
-    <row r="347" spans="1:32">
+    <row r="347" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A347" s="8">
         <v>1820</v>
       </c>
       <c r="B347" s="9">
-        <v>46001.382465278</v>
+        <v>46001.382465278002</v>
       </c>
       <c r="C347" s="8" t="s">
         <v>46</v>
@@ -30530,12 +30542,12 @@
       <c r="AD347" s="8"/>
       <c r="AE347" s="8"/>
     </row>
-    <row r="348" spans="1:32">
+    <row r="348" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A348" s="8">
         <v>1821</v>
       </c>
       <c r="B348" s="9">
-        <v>46001.384444444</v>
+        <v>46001.384444443996</v>
       </c>
       <c r="C348" s="8" t="s">
         <v>46</v>
@@ -30601,12 +30613,12 @@
       <c r="AD348" s="8"/>
       <c r="AE348" s="8"/>
     </row>
-    <row r="349" spans="1:32">
+    <row r="349" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A349" s="8">
         <v>1822</v>
       </c>
       <c r="B349" s="9">
-        <v>46001.3859375</v>
+        <v>46001.385937500003</v>
       </c>
       <c r="C349" s="8" t="s">
         <v>46</v>
@@ -30674,12 +30686,12 @@
       <c r="AD349" s="8"/>
       <c r="AE349" s="8"/>
     </row>
-    <row r="350" spans="1:32">
+    <row r="350" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A350" s="8">
         <v>1823</v>
       </c>
       <c r="B350" s="9">
-        <v>46007.407291667</v>
+        <v>46007.407291666997</v>
       </c>
       <c r="C350" s="8" t="s">
         <v>46</v>
@@ -30745,12 +30757,12 @@
       <c r="AD350" s="8"/>
       <c r="AE350" s="8"/>
     </row>
-    <row r="351" spans="1:32">
+    <row r="351" spans="1:31" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A351" s="8">
         <v>1824</v>
       </c>
       <c r="B351" s="9">
-        <v>46014.367025463</v>
+        <v>46014.367025462998</v>
       </c>
       <c r="C351" s="8" t="s">
         <v>238</v>
@@ -30816,12 +30828,12 @@
       <c r="AD351" s="8"/>
       <c r="AE351" s="8"/>
     </row>
-    <row r="352" spans="1:32">
+    <row r="352" spans="1:31" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A352" s="8">
         <v>1825</v>
       </c>
       <c r="B352" s="9">
-        <v>46014.367939815</v>
+        <v>46014.367939814998</v>
       </c>
       <c r="C352" s="8" t="s">
         <v>69</v>
@@ -30889,12 +30901,12 @@
       <c r="AD352" s="8"/>
       <c r="AE352" s="8"/>
     </row>
-    <row r="353" spans="1:32">
+    <row r="353" spans="1:31" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A353" s="8">
         <v>1826</v>
       </c>
       <c r="B353" s="9">
-        <v>46014.368680556</v>
+        <v>46014.368680555999</v>
       </c>
       <c r="C353" s="8" t="s">
         <v>69</v>
@@ -30960,7 +30972,7 @@
       <c r="AD353" s="8"/>
       <c r="AE353" s="8"/>
     </row>
-    <row r="354" spans="1:32">
+    <row r="354" spans="1:31" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A354" s="8">
         <v>1827</v>
       </c>
@@ -31029,12 +31041,12 @@
       <c r="AD354" s="8"/>
       <c r="AE354" s="8"/>
     </row>
-    <row r="355" spans="1:32">
+    <row r="355" spans="1:31" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A355" s="8">
         <v>1828</v>
       </c>
       <c r="B355" s="9">
-        <v>46014.370150463</v>
+        <v>46014.370150463001</v>
       </c>
       <c r="C355" s="8" t="s">
         <v>69</v>
@@ -31098,12 +31110,12 @@
       <c r="AD355" s="8"/>
       <c r="AE355" s="8"/>
     </row>
-    <row r="356" spans="1:32">
+    <row r="356" spans="1:31" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A356" s="8">
         <v>1829</v>
       </c>
       <c r="B356" s="9">
-        <v>46014.371226852</v>
+        <v>46014.371226852003</v>
       </c>
       <c r="C356" s="8" t="s">
         <v>69</v>
@@ -31167,12 +31179,12 @@
       <c r="AD356" s="8"/>
       <c r="AE356" s="8"/>
     </row>
-    <row r="357" spans="1:32">
+    <row r="357" spans="1:31" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A357" s="8">
         <v>1830</v>
       </c>
       <c r="B357" s="9">
-        <v>46014.371990741</v>
+        <v>46014.371990740998</v>
       </c>
       <c r="C357" s="8" t="s">
         <v>69</v>
@@ -31236,12 +31248,12 @@
       <c r="AD357" s="8"/>
       <c r="AE357" s="8"/>
     </row>
-    <row r="358" spans="1:32">
+    <row r="358" spans="1:31" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A358" s="8">
         <v>1831</v>
       </c>
       <c r="B358" s="9">
-        <v>46014.383206019</v>
+        <v>46014.383206019003</v>
       </c>
       <c r="C358" s="8" t="s">
         <v>238</v>
@@ -31307,12 +31319,12 @@
       <c r="AD358" s="8"/>
       <c r="AE358" s="8"/>
     </row>
-    <row r="359" spans="1:32">
+    <row r="359" spans="1:31" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A359" s="8">
         <v>1832</v>
       </c>
       <c r="B359" s="9">
-        <v>46014.384155093</v>
+        <v>46014.384155093001</v>
       </c>
       <c r="C359" s="8" t="s">
         <v>69</v>
@@ -31378,12 +31390,12 @@
       <c r="AD359" s="8"/>
       <c r="AE359" s="8"/>
     </row>
-    <row r="360" spans="1:32">
+    <row r="360" spans="1:31" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A360" s="8">
         <v>1833</v>
       </c>
       <c r="B360" s="9">
-        <v>46014.390648148</v>
+        <v>46014.390648148001</v>
       </c>
       <c r="C360" s="8" t="s">
         <v>69</v>
@@ -31449,12 +31461,12 @@
       <c r="AD360" s="8"/>
       <c r="AE360" s="8"/>
     </row>
-    <row r="361" spans="1:32">
+    <row r="361" spans="1:31" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A361" s="8">
         <v>1834</v>
       </c>
       <c r="B361" s="9">
-        <v>46014.391527778</v>
+        <v>46014.391527778003</v>
       </c>
       <c r="C361" s="8" t="s">
         <v>69</v>
@@ -31520,12 +31532,12 @@
       <c r="AD361" s="8"/>
       <c r="AE361" s="8"/>
     </row>
-    <row r="362" spans="1:32">
+    <row r="362" spans="1:31" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A362" s="8">
         <v>1835</v>
       </c>
       <c r="B362" s="9">
-        <v>46014.392164352</v>
+        <v>46014.392164352001</v>
       </c>
       <c r="C362" s="8" t="s">
         <v>69</v>
@@ -31591,12 +31603,12 @@
       <c r="AD362" s="8"/>
       <c r="AE362" s="8"/>
     </row>
-    <row r="363" spans="1:32">
+    <row r="363" spans="1:31" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A363" s="8">
         <v>1836</v>
       </c>
       <c r="B363" s="9">
-        <v>46014.401099537</v>
+        <v>46014.401099536997</v>
       </c>
       <c r="C363" s="8" t="s">
         <v>238</v>
@@ -31662,12 +31674,12 @@
       <c r="AD363" s="8"/>
       <c r="AE363" s="8"/>
     </row>
-    <row r="364" spans="1:32">
+    <row r="364" spans="1:31" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A364" s="8">
         <v>1837</v>
       </c>
       <c r="B364" s="9">
-        <v>46014.402025463</v>
+        <v>46014.402025463001</v>
       </c>
       <c r="C364" s="8" t="s">
         <v>238</v>
@@ -31733,12 +31745,12 @@
       <c r="AD364" s="8"/>
       <c r="AE364" s="8"/>
     </row>
-    <row r="365" spans="1:32">
+    <row r="365" spans="1:31" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A365" s="8">
         <v>1838</v>
       </c>
       <c r="B365" s="9">
-        <v>46014.402569444</v>
+        <v>46014.402569443999</v>
       </c>
       <c r="C365" s="8" t="s">
         <v>69</v>
@@ -31804,7 +31816,7 @@
       <c r="AD365" s="8"/>
       <c r="AE365" s="8"/>
     </row>
-    <row r="366" spans="1:32">
+    <row r="366" spans="1:31" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A366" s="8">
         <v>1839</v>
       </c>
@@ -31875,12 +31887,12 @@
       <c r="AD366" s="8"/>
       <c r="AE366" s="8"/>
     </row>
-    <row r="367" spans="1:32">
+    <row r="367" spans="1:31" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A367" s="8">
         <v>1840</v>
       </c>
       <c r="B367" s="9">
-        <v>46014.40369213</v>
+        <v>46014.403692129999</v>
       </c>
       <c r="C367" s="8" t="s">
         <v>69</v>
@@ -31946,12 +31958,12 @@
       <c r="AD367" s="8"/>
       <c r="AE367" s="8"/>
     </row>
-    <row r="368" spans="1:32">
+    <row r="368" spans="1:31" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A368" s="8">
         <v>1841</v>
       </c>
       <c r="B368" s="9">
-        <v>46014.404409722</v>
+        <v>46014.404409722003</v>
       </c>
       <c r="C368" s="8" t="s">
         <v>238</v>
@@ -32019,7 +32031,7 @@
       <c r="AD368" s="8"/>
       <c r="AE368" s="8"/>
     </row>
-    <row r="369" spans="1:32">
+    <row r="369" spans="1:31" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A369" s="8">
         <v>1842</v>
       </c>
@@ -32088,12 +32100,12 @@
       <c r="AD369" s="8"/>
       <c r="AE369" s="8"/>
     </row>
-    <row r="370" spans="1:32">
+    <row r="370" spans="1:31" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A370" s="8">
         <v>1843</v>
       </c>
       <c r="B370" s="9">
-        <v>46014.409710648</v>
+        <v>46014.409710647997</v>
       </c>
       <c r="C370" s="8" t="s">
         <v>69</v>
@@ -32159,12 +32171,12 @@
       <c r="AD370" s="8"/>
       <c r="AE370" s="8"/>
     </row>
-    <row r="371" spans="1:32">
+    <row r="371" spans="1:31" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A371" s="8">
         <v>1844</v>
       </c>
       <c r="B371" s="9">
-        <v>46014.41025463</v>
+        <v>46014.410254629998</v>
       </c>
       <c r="C371" s="8" t="s">
         <v>69</v>
@@ -32228,12 +32240,12 @@
       <c r="AD371" s="8"/>
       <c r="AE371" s="8"/>
     </row>
-    <row r="372" spans="1:32">
+    <row r="372" spans="1:31" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A372" s="8">
         <v>1845</v>
       </c>
       <c r="B372" s="9">
-        <v>46014.411064815</v>
+        <v>46014.411064815002</v>
       </c>
       <c r="C372" s="8" t="s">
         <v>69</v>
@@ -32297,12 +32309,12 @@
       <c r="AD372" s="8"/>
       <c r="AE372" s="8"/>
     </row>
-    <row r="373" spans="1:32">
+    <row r="373" spans="1:31" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A373" s="8">
         <v>1846</v>
       </c>
       <c r="B373" s="9">
-        <v>46014.411921296</v>
+        <v>46014.411921295999</v>
       </c>
       <c r="C373" s="8" t="s">
         <v>69</v>
@@ -32366,12 +32378,12 @@
       <c r="AD373" s="8"/>
       <c r="AE373" s="8"/>
     </row>
-    <row r="374" spans="1:32">
+    <row r="374" spans="1:31" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A374" s="8">
         <v>1847</v>
       </c>
       <c r="B374" s="9">
-        <v>46014.432071759</v>
+        <v>46014.432071759002</v>
       </c>
       <c r="C374" s="8" t="s">
         <v>69</v>
@@ -32439,7 +32451,7 @@
       <c r="AD374" s="8"/>
       <c r="AE374" s="8"/>
     </row>
-    <row r="375" spans="1:32">
+    <row r="375" spans="1:31" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A375" s="8">
         <v>1848</v>
       </c>
@@ -32512,12 +32524,12 @@
       <c r="AD375" s="8"/>
       <c r="AE375" s="8"/>
     </row>
-    <row r="376" spans="1:32">
+    <row r="376" spans="1:31" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A376" s="8">
         <v>1849</v>
       </c>
       <c r="B376" s="9">
-        <v>46014.438576389</v>
+        <v>46014.438576389002</v>
       </c>
       <c r="C376" s="8" t="s">
         <v>69</v>
@@ -32581,7 +32593,7 @@
       <c r="AD376" s="8"/>
       <c r="AE376" s="8"/>
     </row>
-    <row r="377" spans="1:32">
+    <row r="377" spans="1:31" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A377" s="8">
         <v>1850</v>
       </c>
@@ -32654,12 +32666,12 @@
       <c r="AD377" s="8"/>
       <c r="AE377" s="8"/>
     </row>
-    <row r="378" spans="1:32">
+    <row r="378" spans="1:31" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A378" s="8">
         <v>1851</v>
       </c>
       <c r="B378" s="9">
-        <v>46014.443541667</v>
+        <v>46014.443541667002</v>
       </c>
       <c r="C378" s="8" t="s">
         <v>69</v>
@@ -32723,12 +32735,12 @@
       <c r="AD378" s="8"/>
       <c r="AE378" s="8"/>
     </row>
-    <row r="379" spans="1:32">
+    <row r="379" spans="1:31" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A379" s="8">
         <v>1852</v>
       </c>
       <c r="B379" s="9">
-        <v>46014.463541667</v>
+        <v>46014.463541666999</v>
       </c>
       <c r="C379" s="8" t="s">
         <v>238</v>
@@ -32798,12 +32810,12 @@
       <c r="AD379" s="8"/>
       <c r="AE379" s="8"/>
     </row>
-    <row r="380" spans="1:32">
+    <row r="380" spans="1:31" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A380" s="8">
         <v>1853</v>
       </c>
       <c r="B380" s="9">
-        <v>46014.466608796</v>
+        <v>46014.466608795999</v>
       </c>
       <c r="C380" s="8" t="s">
         <v>69</v>
@@ -32869,7 +32881,7 @@
       <c r="AD380" s="8"/>
       <c r="AE380" s="8"/>
     </row>
-    <row r="381" spans="1:32">
+    <row r="381" spans="1:31" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A381" s="8">
         <v>1854</v>
       </c>
@@ -32938,12 +32950,12 @@
       <c r="AD381" s="8"/>
       <c r="AE381" s="8"/>
     </row>
-    <row r="382" spans="1:32">
+    <row r="382" spans="1:31" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A382" s="8">
         <v>1855</v>
       </c>
       <c r="B382" s="9">
-        <v>46014.471226852</v>
+        <v>46014.471226852002</v>
       </c>
       <c r="C382" s="8" t="s">
         <v>69</v>
@@ -33007,12 +33019,12 @@
       <c r="AD382" s="8"/>
       <c r="AE382" s="8"/>
     </row>
-    <row r="383" spans="1:32">
+    <row r="383" spans="1:31" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A383" s="8">
         <v>1856</v>
       </c>
       <c r="B383" s="9">
-        <v>46059.7525</v>
+        <v>46059.752500000002</v>
       </c>
       <c r="C383" s="8" t="s">
         <v>238</v>
@@ -33078,12 +33090,12 @@
       <c r="AD383" s="8"/>
       <c r="AE383" s="8"/>
     </row>
-    <row r="384" spans="1:32">
+    <row r="384" spans="1:31" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A384" s="8">
         <v>1857</v>
       </c>
       <c r="B384" s="9">
-        <v>46059.754849537</v>
+        <v>46059.754849536999</v>
       </c>
       <c r="C384" s="8" t="s">
         <v>69</v>
@@ -33151,7 +33163,7 @@
       <c r="AD384" s="8"/>
       <c r="AE384" s="8"/>
     </row>
-    <row r="385" spans="1:32">
+    <row r="385" spans="1:31" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A385" s="8">
         <v>1858</v>
       </c>
@@ -33224,12 +33236,12 @@
       <c r="AD385" s="8"/>
       <c r="AE385" s="8"/>
     </row>
-    <row r="386" spans="1:32">
+    <row r="386" spans="1:31" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A386" s="8">
         <v>1859</v>
       </c>
       <c r="B386" s="9">
-        <v>46059.759027778</v>
+        <v>46059.759027777996</v>
       </c>
       <c r="C386" s="8" t="s">
         <v>69</v>
@@ -33295,12 +33307,12 @@
       <c r="AD386" s="8"/>
       <c r="AE386" s="8"/>
     </row>
-    <row r="387" spans="1:32">
+    <row r="387" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A387" s="8">
         <v>1860</v>
       </c>
       <c r="B387" s="9">
-        <v>46062.499699074</v>
+        <v>46062.499699073996</v>
       </c>
       <c r="C387" s="8" t="s">
         <v>46</v>
@@ -33366,12 +33378,12 @@
       <c r="AD387" s="8"/>
       <c r="AE387" s="8"/>
     </row>
-    <row r="388" spans="1:32">
+    <row r="388" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A388" s="8">
         <v>1862</v>
       </c>
       <c r="B388" s="9">
-        <v>46062.501053241</v>
+        <v>46062.501053241002</v>
       </c>
       <c r="C388" s="8" t="s">
         <v>46</v>
@@ -33433,7 +33445,7 @@
       <c r="AD388" s="8"/>
       <c r="AE388" s="8"/>
     </row>
-    <row r="389" spans="1:32">
+    <row r="389" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A389" s="8">
         <v>1863</v>
       </c>
@@ -33500,12 +33512,12 @@
       <c r="AD389" s="8"/>
       <c r="AE389" s="8"/>
     </row>
-    <row r="390" spans="1:32">
+    <row r="390" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A390" s="8">
         <v>1864</v>
       </c>
       <c r="B390" s="9">
-        <v>46062.503969907</v>
+        <v>46062.503969906997</v>
       </c>
       <c r="C390" s="8" t="s">
         <v>46</v>
@@ -33567,12 +33579,12 @@
       <c r="AD390" s="8"/>
       <c r="AE390" s="8"/>
     </row>
-    <row r="391" spans="1:32">
+    <row r="391" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A391" s="8">
         <v>1866</v>
       </c>
       <c r="B391" s="9">
-        <v>46062.602743056</v>
+        <v>46062.602743055999</v>
       </c>
       <c r="C391" s="8" t="s">
         <v>46</v>
@@ -33638,12 +33650,12 @@
       <c r="AD391" s="8"/>
       <c r="AE391" s="8"/>
     </row>
-    <row r="392" spans="1:32">
+    <row r="392" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A392" s="8">
         <v>1867</v>
       </c>
       <c r="B392" s="9">
-        <v>46062.60337963</v>
+        <v>46062.603379630003</v>
       </c>
       <c r="C392" s="8" t="s">
         <v>46</v>
@@ -33709,12 +33721,12 @@
       <c r="AD392" s="8"/>
       <c r="AE392" s="8"/>
     </row>
-    <row r="393" spans="1:32">
+    <row r="393" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A393" s="8">
         <v>1868</v>
       </c>
       <c r="B393" s="9">
-        <v>46062.603854167</v>
+        <v>46062.603854166999</v>
       </c>
       <c r="C393" s="8" t="s">
         <v>46</v>
@@ -33780,12 +33792,12 @@
       <c r="AD393" s="8"/>
       <c r="AE393" s="8"/>
     </row>
-    <row r="394" spans="1:32">
+    <row r="394" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A394" s="8">
         <v>1869</v>
       </c>
       <c r="B394" s="9">
-        <v>46062.604594907</v>
+        <v>46062.604594907003</v>
       </c>
       <c r="C394" s="8" t="s">
         <v>46</v>
@@ -33847,12 +33859,12 @@
       <c r="AD394" s="8"/>
       <c r="AE394" s="8"/>
     </row>
-    <row r="395" spans="1:32">
+    <row r="395" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A395" s="8">
         <v>1870</v>
       </c>
       <c r="B395" s="9">
-        <v>46062.605509259</v>
+        <v>46062.605509259003</v>
       </c>
       <c r="C395" s="8" t="s">
         <v>46</v>
@@ -33914,12 +33926,12 @@
       <c r="AD395" s="8"/>
       <c r="AE395" s="8"/>
     </row>
-    <row r="396" spans="1:32">
+    <row r="396" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A396" s="8">
         <v>1872</v>
       </c>
       <c r="B396" s="9">
-        <v>46062.61005787</v>
+        <v>46062.610057869999</v>
       </c>
       <c r="C396" s="8" t="s">
         <v>46</v>
@@ -33985,7 +33997,7 @@
       <c r="AD396" s="8"/>
       <c r="AE396" s="8"/>
     </row>
-    <row r="397" spans="1:32">
+    <row r="397" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A397" s="8">
         <v>1873</v>
       </c>
@@ -34056,12 +34068,12 @@
       <c r="AD397" s="8"/>
       <c r="AE397" s="8"/>
     </row>
-    <row r="398" spans="1:32">
+    <row r="398" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A398" s="8">
         <v>1874</v>
       </c>
       <c r="B398" s="9">
-        <v>46062.611226852</v>
+        <v>46062.611226852001</v>
       </c>
       <c r="C398" s="8" t="s">
         <v>46</v>
@@ -34123,12 +34135,12 @@
       <c r="AD398" s="8"/>
       <c r="AE398" s="8"/>
     </row>
-    <row r="399" spans="1:32">
+    <row r="399" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A399" s="8">
         <v>1875</v>
       </c>
       <c r="B399" s="9">
-        <v>46062.611828704</v>
+        <v>46062.611828704001</v>
       </c>
       <c r="C399" s="8" t="s">
         <v>46</v>
@@ -34190,12 +34202,12 @@
       <c r="AD399" s="8"/>
       <c r="AE399" s="8"/>
     </row>
-    <row r="400" spans="1:32">
+    <row r="400" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A400" s="8">
         <v>1876</v>
       </c>
       <c r="B400" s="9">
-        <v>46062.612453704</v>
+        <v>46062.612453704001</v>
       </c>
       <c r="C400" s="8" t="s">
         <v>46</v>
@@ -34257,12 +34269,12 @@
       <c r="AD400" s="8"/>
       <c r="AE400" s="8"/>
     </row>
-    <row r="401" spans="1:32">
+    <row r="401" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A401" s="8">
         <v>1877</v>
       </c>
       <c r="B401" s="9">
-        <v>46062.613090278</v>
+        <v>46062.613090277999</v>
       </c>
       <c r="C401" s="8" t="s">
         <v>46</v>
@@ -34324,7 +34336,7 @@
       <c r="AD401" s="8"/>
       <c r="AE401" s="8"/>
     </row>
-    <row r="402" spans="1:32">
+    <row r="402" spans="1:31" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A402" s="8">
         <v>1878</v>
       </c>
@@ -34395,12 +34407,12 @@
       <c r="AD402" s="8"/>
       <c r="AE402" s="8"/>
     </row>
-    <row r="403" spans="1:32">
+    <row r="403" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A403" s="8">
         <v>1879</v>
       </c>
       <c r="B403" s="9">
-        <v>46083.696319444</v>
+        <v>46083.696319444003</v>
       </c>
       <c r="C403" s="8" t="s">
         <v>46</v>
@@ -34466,12 +34478,12 @@
       <c r="AD403" s="8"/>
       <c r="AE403" s="8"/>
     </row>
-    <row r="404" spans="1:32">
+    <row r="404" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A404" s="8">
         <v>1880</v>
       </c>
       <c r="B404" s="9">
-        <v>46083.697071759</v>
+        <v>46083.697071759001</v>
       </c>
       <c r="C404" s="8" t="s">
         <v>46</v>
@@ -34533,12 +34545,12 @@
       <c r="AD404" s="8"/>
       <c r="AE404" s="8"/>
     </row>
-    <row r="405" spans="1:32">
+    <row r="405" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A405" s="8">
         <v>1881</v>
       </c>
       <c r="B405" s="9">
-        <v>46083.697951389</v>
+        <v>46083.697951388996</v>
       </c>
       <c r="C405" s="8" t="s">
         <v>46</v>
@@ -34600,12 +34612,12 @@
       <c r="AD405" s="8"/>
       <c r="AE405" s="8"/>
     </row>
-    <row r="406" spans="1:32">
+    <row r="406" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A406" s="8">
         <v>1882</v>
       </c>
       <c r="B406" s="9">
-        <v>46083.698865741</v>
+        <v>46083.698865740997</v>
       </c>
       <c r="C406" s="8" t="s">
         <v>46</v>
@@ -34667,7 +34679,7 @@
       <c r="AD406" s="8"/>
       <c r="AE406" s="8"/>
     </row>
-    <row r="407" spans="1:32">
+    <row r="407" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A407" s="8">
         <v>1883</v>
       </c>
@@ -34734,12 +34746,12 @@
       <c r="AD407" s="8"/>
       <c r="AE407" s="8"/>
     </row>
-    <row r="408" spans="1:32">
+    <row r="408" spans="1:31" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A408" s="8">
         <v>1885</v>
       </c>
       <c r="B408" s="9">
-        <v>46087.424247685</v>
+        <v>46087.424247684998</v>
       </c>
       <c r="C408" s="8" t="s">
         <v>46</v>
@@ -34803,12 +34815,12 @@
       <c r="AD408" s="8"/>
       <c r="AE408" s="8"/>
     </row>
-    <row r="409" spans="1:32">
+    <row r="409" spans="1:31" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A409" s="8">
         <v>1886</v>
       </c>
       <c r="B409" s="9">
-        <v>46087.424675926</v>
+        <v>46087.424675925999</v>
       </c>
       <c r="C409" s="8" t="s">
         <v>46</v>
@@ -34872,12 +34884,12 @@
       <c r="AD409" s="8"/>
       <c r="AE409" s="8"/>
     </row>
-    <row r="410" spans="1:32">
+    <row r="410" spans="1:31" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A410" s="8">
         <v>1887</v>
       </c>
       <c r="B410" s="9">
-        <v>46087.425115741</v>
+        <v>46087.425115741004</v>
       </c>
       <c r="C410" s="8" t="s">
         <v>46</v>
@@ -34941,12 +34953,12 @@
       <c r="AD410" s="8"/>
       <c r="AE410" s="8"/>
     </row>
-    <row r="411" spans="1:32">
+    <row r="411" spans="1:31" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A411" s="8">
         <v>1888</v>
       </c>
       <c r="B411" s="9">
-        <v>46087.425613426</v>
+        <v>46087.425613425999</v>
       </c>
       <c r="C411" s="8" t="s">
         <v>46</v>
@@ -35010,7 +35022,7 @@
       <c r="AD411" s="8"/>
       <c r="AE411" s="8"/>
     </row>
-    <row r="412" spans="1:32">
+    <row r="412" spans="1:31" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A412" s="8">
         <v>1889</v>
       </c>
@@ -35077,7 +35089,7 @@
       <c r="AD412" s="8"/>
       <c r="AE412" s="8"/>
     </row>
-    <row r="413" spans="1:32">
+    <row r="413" spans="1:31" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A413" s="8">
         <v>1890</v>
       </c>
@@ -35146,12 +35158,12 @@
       <c r="AD413" s="8"/>
       <c r="AE413" s="8"/>
     </row>
-    <row r="414" spans="1:32">
+    <row r="414" spans="1:31" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A414" s="8">
         <v>1891</v>
       </c>
       <c r="B414" s="9">
-        <v>46087.426805556</v>
+        <v>46087.426805556002</v>
       </c>
       <c r="C414" s="8" t="s">
         <v>46</v>
@@ -35215,12 +35227,12 @@
       <c r="AD414" s="8"/>
       <c r="AE414" s="8"/>
     </row>
-    <row r="415" spans="1:32">
+    <row r="415" spans="1:31" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A415" s="8">
         <v>1892</v>
       </c>
       <c r="B415" s="9">
-        <v>46087.427384259</v>
+        <v>46087.427384258997</v>
       </c>
       <c r="C415" s="8" t="s">
         <v>46</v>
@@ -35284,12 +35296,12 @@
       <c r="AD415" s="8"/>
       <c r="AE415" s="8"/>
     </row>
-    <row r="416" spans="1:32">
+    <row r="416" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A416" s="8">
         <v>1893</v>
       </c>
       <c r="B416" s="9">
-        <v>46112.653460648</v>
+        <v>46112.653460647998</v>
       </c>
       <c r="C416" s="8" t="s">
         <v>46</v>
@@ -35353,12 +35365,12 @@
       <c r="AD416" s="8"/>
       <c r="AE416" s="8"/>
     </row>
-    <row r="417" spans="1:32">
+    <row r="417" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A417" s="8">
         <v>1894</v>
       </c>
       <c r="B417" s="9">
-        <v>46112.655289352</v>
+        <v>46112.655289351998</v>
       </c>
       <c r="C417" s="8" t="s">
         <v>238</v>
@@ -35420,12 +35432,12 @@
       <c r="AD417" s="8"/>
       <c r="AE417" s="8"/>
     </row>
-    <row r="418" spans="1:32">
+    <row r="418" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A418" s="8">
         <v>1895</v>
       </c>
       <c r="B418" s="9">
-        <v>46112.656076389</v>
+        <v>46112.656076389001</v>
       </c>
       <c r="C418" s="8" t="s">
         <v>238</v>
@@ -35487,12 +35499,12 @@
       <c r="AD418" s="8"/>
       <c r="AE418" s="8"/>
     </row>
-    <row r="419" spans="1:32">
+    <row r="419" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A419" s="8">
         <v>1896</v>
       </c>
       <c r="B419" s="9">
-        <v>46112.657303241</v>
+        <v>46112.657303241002</v>
       </c>
       <c r="C419" s="8" t="s">
         <v>238</v>
@@ -35554,12 +35566,12 @@
       <c r="AD419" s="8"/>
       <c r="AE419" s="8"/>
     </row>
-    <row r="420" spans="1:32">
+    <row r="420" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A420" s="8">
         <v>1897</v>
       </c>
       <c r="B420" s="9">
-        <v>46112.703148148</v>
+        <v>46112.703148148001</v>
       </c>
       <c r="C420" s="8" t="s">
         <v>69</v>
@@ -35623,12 +35635,12 @@
       <c r="AD420" s="8"/>
       <c r="AE420" s="8"/>
     </row>
-    <row r="421" spans="1:32">
+    <row r="421" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A421" s="8">
         <v>1898</v>
       </c>
       <c r="B421" s="9">
-        <v>46112.703888889</v>
+        <v>46112.703888889002</v>
       </c>
       <c r="C421" s="8" t="s">
         <v>238</v>
@@ -35692,12 +35704,12 @@
       <c r="AD421" s="8"/>
       <c r="AE421" s="8"/>
     </row>
-    <row r="422" spans="1:32">
+    <row r="422" spans="1:31" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A422" s="3">
         <v>1899</v>
       </c>
       <c r="B422" s="4">
-        <v>46118.438553241</v>
+        <v>46118.438553241002</v>
       </c>
       <c r="C422" s="3" t="s">
         <v>46</v>
@@ -35762,17 +35774,7 @@
       <c r="AE422" s="3"/>
     </row>
   </sheetData>
-  <sheetProtection sheet="false" objects="false" scenarios="false" formatCells="false" formatColumns="false" formatRows="false" insertColumns="false" insertRows="false" insertHyperlinks="false" deleteColumns="false" deleteRows="false" selectLockedCells="false" sort="false" autoFilter="false" pivotTables="false" selectUnlockedCells="false"/>
-  <printOptions gridLines="false" gridLinesSet="true"/>
+  <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1"/>
-  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
-    <oddHeader/>
-    <oddFooter/>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
 </worksheet>
 </file>
--- a/data/raw/Plan de accion/PA_2.xlsx
+++ b/data/raw/Plan de accion/PA_2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Sistema_Indicadores_Poli/data/raw/Plan de accion/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="11_C4BD844F18F46918874719FA9983E268DB8A1E7B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E29A010E-3510-4FF0-9024-EA98931DC292}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="11_C4BD844F18F46918874719FA9983E268DB8A1E7B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{33C0FF22-37E5-4990-BFEE-D6ED30F7E378}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3884,6 +3884,7 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="7">
@@ -4322,6 +4323,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:AE422"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -4452,7 +4454,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:31" ht="187.2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:31" ht="187.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" s="8">
         <v>1141</v>
       </c>
@@ -4531,7 +4533,7 @@
       <c r="AD2" s="8"/>
       <c r="AE2" s="8"/>
     </row>
-    <row r="3" spans="1:31" ht="72" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:31" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" s="8">
         <v>1142</v>
       </c>
@@ -4610,7 +4612,7 @@
       <c r="AD3" s="8"/>
       <c r="AE3" s="8"/>
     </row>
-    <row r="4" spans="1:31" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:31" ht="115.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" s="8">
         <v>1244</v>
       </c>
@@ -4689,7 +4691,7 @@
       <c r="AD4" s="8"/>
       <c r="AE4" s="8"/>
     </row>
-    <row r="5" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" s="8">
         <v>1280</v>
       </c>
@@ -4768,7 +4770,7 @@
       <c r="AD5" s="8"/>
       <c r="AE5" s="8"/>
     </row>
-    <row r="6" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" s="8">
         <v>1285</v>
       </c>
@@ -4839,7 +4841,7 @@
       <c r="AD6" s="8"/>
       <c r="AE6" s="8"/>
     </row>
-    <row r="7" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" s="8">
         <v>1292</v>
       </c>
@@ -4908,7 +4910,7 @@
       <c r="AD7" s="8"/>
       <c r="AE7" s="8"/>
     </row>
-    <row r="8" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="8">
         <v>1293</v>
       </c>
@@ -4977,7 +4979,7 @@
       <c r="AD8" s="8"/>
       <c r="AE8" s="8"/>
     </row>
-    <row r="9" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="8">
         <v>1294</v>
       </c>
@@ -5046,7 +5048,7 @@
       <c r="AD9" s="8"/>
       <c r="AE9" s="8"/>
     </row>
-    <row r="10" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="8">
         <v>1295</v>
       </c>
@@ -5115,7 +5117,7 @@
       <c r="AD10" s="8"/>
       <c r="AE10" s="8"/>
     </row>
-    <row r="11" spans="1:31" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:31" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="8">
         <v>1308</v>
       </c>
@@ -5192,7 +5194,7 @@
       <c r="AD11" s="8"/>
       <c r="AE11" s="8"/>
     </row>
-    <row r="12" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="8">
         <v>1328</v>
       </c>
@@ -5271,7 +5273,7 @@
       <c r="AD12" s="8"/>
       <c r="AE12" s="8"/>
     </row>
-    <row r="13" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="8">
         <v>1332</v>
       </c>
@@ -5338,7 +5340,7 @@
       <c r="AD13" s="8"/>
       <c r="AE13" s="8"/>
     </row>
-    <row r="14" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" s="8">
         <v>1333</v>
       </c>
@@ -5405,7 +5407,7 @@
       <c r="AD14" s="8"/>
       <c r="AE14" s="8"/>
     </row>
-    <row r="15" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="8">
         <v>1334</v>
       </c>
@@ -5472,7 +5474,7 @@
       <c r="AD15" s="8"/>
       <c r="AE15" s="8"/>
     </row>
-    <row r="16" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" s="8">
         <v>1335</v>
       </c>
@@ -5539,7 +5541,7 @@
       <c r="AD16" s="8"/>
       <c r="AE16" s="8"/>
     </row>
-    <row r="17" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" s="8">
         <v>1336</v>
       </c>
@@ -5612,7 +5614,7 @@
       <c r="AD17" s="8"/>
       <c r="AE17" s="8"/>
     </row>
-    <row r="18" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="8">
         <v>1337</v>
       </c>
@@ -5683,7 +5685,7 @@
       <c r="AD18" s="8"/>
       <c r="AE18" s="8"/>
     </row>
-    <row r="19" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="8">
         <v>1338</v>
       </c>
@@ -5754,7 +5756,7 @@
       <c r="AD19" s="8"/>
       <c r="AE19" s="8"/>
     </row>
-    <row r="20" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="8">
         <v>1339</v>
       </c>
@@ -5833,7 +5835,7 @@
       <c r="AD20" s="8"/>
       <c r="AE20" s="8"/>
     </row>
-    <row r="21" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="8">
         <v>1340</v>
       </c>
@@ -5912,7 +5914,7 @@
       <c r="AD21" s="8"/>
       <c r="AE21" s="8"/>
     </row>
-    <row r="22" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="8">
         <v>1341</v>
       </c>
@@ -5991,7 +5993,7 @@
       <c r="AD22" s="8"/>
       <c r="AE22" s="8"/>
     </row>
-    <row r="23" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="8">
         <v>1342</v>
       </c>
@@ -6070,7 +6072,7 @@
       <c r="AD23" s="8"/>
       <c r="AE23" s="8"/>
     </row>
-    <row r="24" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="8">
         <v>1343</v>
       </c>
@@ -6149,7 +6151,7 @@
       <c r="AD24" s="8"/>
       <c r="AE24" s="8"/>
     </row>
-    <row r="25" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="8">
         <v>1344</v>
       </c>
@@ -6228,7 +6230,7 @@
       <c r="AD25" s="8"/>
       <c r="AE25" s="8"/>
     </row>
-    <row r="26" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="8">
         <v>1345</v>
       </c>
@@ -6307,7 +6309,7 @@
       <c r="AD26" s="8"/>
       <c r="AE26" s="8"/>
     </row>
-    <row r="27" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="8">
         <v>1346</v>
       </c>
@@ -6386,7 +6388,7 @@
       <c r="AD27" s="8"/>
       <c r="AE27" s="8"/>
     </row>
-    <row r="28" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="8">
         <v>1347</v>
       </c>
@@ -6465,7 +6467,7 @@
       <c r="AD28" s="8"/>
       <c r="AE28" s="8"/>
     </row>
-    <row r="29" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="8">
         <v>1348</v>
       </c>
@@ -6544,7 +6546,7 @@
       <c r="AD29" s="8"/>
       <c r="AE29" s="8"/>
     </row>
-    <row r="30" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="8">
         <v>1349</v>
       </c>
@@ -6623,7 +6625,7 @@
       <c r="AD30" s="8"/>
       <c r="AE30" s="8"/>
     </row>
-    <row r="31" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="8">
         <v>1350</v>
       </c>
@@ -6702,7 +6704,7 @@
       <c r="AD31" s="8"/>
       <c r="AE31" s="8"/>
     </row>
-    <row r="32" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" s="8">
         <v>1351</v>
       </c>
@@ -6781,7 +6783,7 @@
       <c r="AD32" s="8"/>
       <c r="AE32" s="8"/>
     </row>
-    <row r="33" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" s="8">
         <v>1353</v>
       </c>
@@ -6860,7 +6862,7 @@
       <c r="AD33" s="8"/>
       <c r="AE33" s="8"/>
     </row>
-    <row r="34" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" s="8">
         <v>1354</v>
       </c>
@@ -6939,7 +6941,7 @@
       <c r="AD34" s="8"/>
       <c r="AE34" s="8"/>
     </row>
-    <row r="35" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" s="8">
         <v>1355</v>
       </c>
@@ -7018,7 +7020,7 @@
       <c r="AD35" s="8"/>
       <c r="AE35" s="8"/>
     </row>
-    <row r="36" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" s="8">
         <v>1356</v>
       </c>
@@ -7097,7 +7099,7 @@
       <c r="AD36" s="8"/>
       <c r="AE36" s="8"/>
     </row>
-    <row r="37" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" s="8">
         <v>1357</v>
       </c>
@@ -7176,7 +7178,7 @@
       <c r="AD37" s="8"/>
       <c r="AE37" s="8"/>
     </row>
-    <row r="38" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" s="8">
         <v>1358</v>
       </c>
@@ -7255,7 +7257,7 @@
       <c r="AD38" s="8"/>
       <c r="AE38" s="8"/>
     </row>
-    <row r="39" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" s="8">
         <v>1359</v>
       </c>
@@ -7334,7 +7336,7 @@
       <c r="AD39" s="8"/>
       <c r="AE39" s="8"/>
     </row>
-    <row r="40" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" s="8">
         <v>1360</v>
       </c>
@@ -7413,7 +7415,7 @@
       <c r="AD40" s="8"/>
       <c r="AE40" s="8"/>
     </row>
-    <row r="41" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" s="8">
         <v>1361</v>
       </c>
@@ -7492,7 +7494,7 @@
       <c r="AD41" s="8"/>
       <c r="AE41" s="8"/>
     </row>
-    <row r="42" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" s="8">
         <v>1362</v>
       </c>
@@ -7571,7 +7573,7 @@
       <c r="AD42" s="8"/>
       <c r="AE42" s="8"/>
     </row>
-    <row r="43" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" s="8">
         <v>1363</v>
       </c>
@@ -7652,7 +7654,7 @@
       <c r="AD43" s="8"/>
       <c r="AE43" s="8"/>
     </row>
-    <row r="44" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" s="8">
         <v>1364</v>
       </c>
@@ -7731,7 +7733,7 @@
       <c r="AD44" s="8"/>
       <c r="AE44" s="8"/>
     </row>
-    <row r="45" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" s="8">
         <v>1365</v>
       </c>
@@ -7810,7 +7812,7 @@
       <c r="AD45" s="8"/>
       <c r="AE45" s="8"/>
     </row>
-    <row r="46" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" s="8">
         <v>1366</v>
       </c>
@@ -7891,7 +7893,7 @@
       <c r="AD46" s="8"/>
       <c r="AE46" s="8"/>
     </row>
-    <row r="47" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" s="8">
         <v>1367</v>
       </c>
@@ -7972,7 +7974,7 @@
       <c r="AD47" s="8"/>
       <c r="AE47" s="8"/>
     </row>
-    <row r="48" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" s="8">
         <v>1371</v>
       </c>
@@ -8051,7 +8053,7 @@
       <c r="AD48" s="8"/>
       <c r="AE48" s="8"/>
     </row>
-    <row r="49" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" s="8">
         <v>1375</v>
       </c>
@@ -8130,7 +8132,7 @@
       <c r="AD49" s="8"/>
       <c r="AE49" s="8"/>
     </row>
-    <row r="50" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" s="8">
         <v>1377</v>
       </c>
@@ -8209,7 +8211,7 @@
       <c r="AD50" s="8"/>
       <c r="AE50" s="8"/>
     </row>
-    <row r="51" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" s="8">
         <v>1378</v>
       </c>
@@ -8288,7 +8290,7 @@
       <c r="AD51" s="8"/>
       <c r="AE51" s="8"/>
     </row>
-    <row r="52" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" s="8">
         <v>1379</v>
       </c>
@@ -8365,7 +8367,7 @@
       <c r="AD52" s="8"/>
       <c r="AE52" s="8"/>
     </row>
-    <row r="53" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" s="8">
         <v>1382</v>
       </c>
@@ -8444,7 +8446,7 @@
       <c r="AD53" s="8"/>
       <c r="AE53" s="8"/>
     </row>
-    <row r="54" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" s="8">
         <v>1383</v>
       </c>
@@ -8523,7 +8525,7 @@
       <c r="AD54" s="8"/>
       <c r="AE54" s="8"/>
     </row>
-    <row r="55" spans="1:31" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:31" ht="115.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" s="8">
         <v>1395</v>
       </c>
@@ -8596,7 +8598,7 @@
       <c r="AD55" s="8"/>
       <c r="AE55" s="8"/>
     </row>
-    <row r="56" spans="1:31" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:31" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" s="8">
         <v>1401</v>
       </c>
@@ -8669,7 +8671,7 @@
       <c r="AD56" s="8"/>
       <c r="AE56" s="8"/>
     </row>
-    <row r="57" spans="1:31" ht="72" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:31" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" s="8">
         <v>1405</v>
       </c>
@@ -8740,7 +8742,7 @@
       <c r="AD57" s="8"/>
       <c r="AE57" s="8"/>
     </row>
-    <row r="58" spans="1:31" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:31" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" s="8">
         <v>1406</v>
       </c>
@@ -8813,7 +8815,7 @@
       <c r="AD58" s="8"/>
       <c r="AE58" s="8"/>
     </row>
-    <row r="59" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" s="8">
         <v>1413</v>
       </c>
@@ -8894,7 +8896,7 @@
       <c r="AD59" s="8"/>
       <c r="AE59" s="8"/>
     </row>
-    <row r="60" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" s="8">
         <v>1415</v>
       </c>
@@ -8975,7 +8977,7 @@
       <c r="AD60" s="8"/>
       <c r="AE60" s="8"/>
     </row>
-    <row r="61" spans="1:31" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:31" ht="115.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" s="8">
         <v>1433</v>
       </c>
@@ -9054,7 +9056,7 @@
       <c r="AD61" s="8"/>
       <c r="AE61" s="8"/>
     </row>
-    <row r="62" spans="1:31" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:31" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" s="8">
         <v>1435</v>
       </c>
@@ -9129,7 +9131,7 @@
       <c r="AD62" s="8"/>
       <c r="AE62" s="8"/>
     </row>
-    <row r="63" spans="1:31" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:31" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" s="8">
         <v>1436</v>
       </c>
@@ -9204,7 +9206,7 @@
       <c r="AD63" s="8"/>
       <c r="AE63" s="8"/>
     </row>
-    <row r="64" spans="1:31" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:31" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" s="8">
         <v>1437</v>
       </c>
@@ -9279,7 +9281,7 @@
       <c r="AD64" s="8"/>
       <c r="AE64" s="8"/>
     </row>
-    <row r="65" spans="1:31" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:31" ht="115.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" s="8">
         <v>1438</v>
       </c>
@@ -9358,7 +9360,7 @@
       <c r="AD65" s="8"/>
       <c r="AE65" s="8"/>
     </row>
-    <row r="66" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" s="8">
         <v>1441</v>
       </c>
@@ -9431,7 +9433,7 @@
       <c r="AD66" s="8"/>
       <c r="AE66" s="8"/>
     </row>
-    <row r="67" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" s="8">
         <v>1442</v>
       </c>
@@ -9504,7 +9506,7 @@
       <c r="AD67" s="8"/>
       <c r="AE67" s="8"/>
     </row>
-    <row r="68" spans="1:31" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:31" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" s="8">
         <v>1445</v>
       </c>
@@ -9579,7 +9581,7 @@
       <c r="AD68" s="8"/>
       <c r="AE68" s="8"/>
     </row>
-    <row r="69" spans="1:31" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:31" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" s="8">
         <v>1446</v>
       </c>
@@ -9654,7 +9656,7 @@
       <c r="AD69" s="8"/>
       <c r="AE69" s="8"/>
     </row>
-    <row r="70" spans="1:31" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:31" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" s="8">
         <v>1447</v>
       </c>
@@ -9729,7 +9731,7 @@
       <c r="AD70" s="8"/>
       <c r="AE70" s="8"/>
     </row>
-    <row r="71" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" s="8">
         <v>1468</v>
       </c>
@@ -9798,7 +9800,7 @@
       <c r="AD71" s="8"/>
       <c r="AE71" s="8"/>
     </row>
-    <row r="72" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" s="8">
         <v>1469</v>
       </c>
@@ -9867,7 +9869,7 @@
       <c r="AD72" s="8"/>
       <c r="AE72" s="8"/>
     </row>
-    <row r="73" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" s="8">
         <v>1470</v>
       </c>
@@ -9936,7 +9938,7 @@
       <c r="AD73" s="8"/>
       <c r="AE73" s="8"/>
     </row>
-    <row r="74" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" s="8">
         <v>1471</v>
       </c>
@@ -10005,7 +10007,7 @@
       <c r="AD74" s="8"/>
       <c r="AE74" s="8"/>
     </row>
-    <row r="75" spans="1:31" ht="201.6" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:31" ht="201.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" s="8">
         <v>1476</v>
       </c>
@@ -10076,7 +10078,7 @@
       <c r="AD75" s="8"/>
       <c r="AE75" s="8"/>
     </row>
-    <row r="76" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" s="8">
         <v>1478</v>
       </c>
@@ -10155,7 +10157,7 @@
       <c r="AD76" s="8"/>
       <c r="AE76" s="8"/>
     </row>
-    <row r="77" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" s="8">
         <v>1479</v>
       </c>
@@ -10234,7 +10236,7 @@
       <c r="AD77" s="8"/>
       <c r="AE77" s="8"/>
     </row>
-    <row r="78" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" s="8">
         <v>1480</v>
       </c>
@@ -10313,7 +10315,7 @@
       <c r="AD78" s="8"/>
       <c r="AE78" s="8"/>
     </row>
-    <row r="79" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" s="8">
         <v>1481</v>
       </c>
@@ -10392,7 +10394,7 @@
       <c r="AD79" s="8"/>
       <c r="AE79" s="8"/>
     </row>
-    <row r="80" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" s="8">
         <v>1482</v>
       </c>
@@ -10473,7 +10475,7 @@
       <c r="AD80" s="8"/>
       <c r="AE80" s="8"/>
     </row>
-    <row r="81" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" s="8">
         <v>1483</v>
       </c>
@@ -10554,7 +10556,7 @@
       <c r="AD81" s="8"/>
       <c r="AE81" s="8"/>
     </row>
-    <row r="82" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" s="8">
         <v>1484</v>
       </c>
@@ -10635,7 +10637,7 @@
       <c r="AD82" s="8"/>
       <c r="AE82" s="8"/>
     </row>
-    <row r="83" spans="1:31" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:31" ht="409.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" s="8">
         <v>1485</v>
       </c>
@@ -10714,7 +10716,7 @@
       <c r="AD83" s="8"/>
       <c r="AE83" s="8"/>
     </row>
-    <row r="84" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" s="8">
         <v>1487</v>
       </c>
@@ -10781,7 +10783,7 @@
       <c r="AD84" s="8"/>
       <c r="AE84" s="8"/>
     </row>
-    <row r="85" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" s="8">
         <v>1489</v>
       </c>
@@ -10848,7 +10850,7 @@
       <c r="AD85" s="8"/>
       <c r="AE85" s="8"/>
     </row>
-    <row r="86" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" s="8">
         <v>1490</v>
       </c>
@@ -10927,7 +10929,7 @@
       <c r="AD86" s="8"/>
       <c r="AE86" s="8"/>
     </row>
-    <row r="87" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" s="8">
         <v>1491</v>
       </c>
@@ -11006,7 +11008,7 @@
       <c r="AD87" s="8"/>
       <c r="AE87" s="8"/>
     </row>
-    <row r="88" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" s="8">
         <v>1492</v>
       </c>
@@ -11085,7 +11087,7 @@
       <c r="AD88" s="8"/>
       <c r="AE88" s="8"/>
     </row>
-    <row r="89" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" s="8">
         <v>1493</v>
       </c>
@@ -11164,7 +11166,7 @@
       <c r="AD89" s="8"/>
       <c r="AE89" s="8"/>
     </row>
-    <row r="90" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" s="8">
         <v>1494</v>
       </c>
@@ -11243,7 +11245,7 @@
       <c r="AD90" s="8"/>
       <c r="AE90" s="8"/>
     </row>
-    <row r="91" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" s="8">
         <v>1495</v>
       </c>
@@ -11322,7 +11324,7 @@
       <c r="AD91" s="8"/>
       <c r="AE91" s="8"/>
     </row>
-    <row r="92" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" s="8">
         <v>1496</v>
       </c>
@@ -11401,7 +11403,7 @@
       <c r="AD92" s="8"/>
       <c r="AE92" s="8"/>
     </row>
-    <row r="93" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" s="8">
         <v>1497</v>
       </c>
@@ -11480,7 +11482,7 @@
       <c r="AD93" s="8"/>
       <c r="AE93" s="8"/>
     </row>
-    <row r="94" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" s="8">
         <v>1498</v>
       </c>
@@ -11561,7 +11563,7 @@
       <c r="AD94" s="8"/>
       <c r="AE94" s="8"/>
     </row>
-    <row r="95" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" s="8">
         <v>1499</v>
       </c>
@@ -11642,7 +11644,7 @@
       <c r="AD95" s="8"/>
       <c r="AE95" s="8"/>
     </row>
-    <row r="96" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" s="8">
         <v>1500</v>
       </c>
@@ -11723,7 +11725,7 @@
       <c r="AD96" s="8"/>
       <c r="AE96" s="8"/>
     </row>
-    <row r="97" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" s="8">
         <v>1501</v>
       </c>
@@ -11802,7 +11804,7 @@
       <c r="AD97" s="8"/>
       <c r="AE97" s="8"/>
     </row>
-    <row r="98" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" s="8">
         <v>1504</v>
       </c>
@@ -11881,7 +11883,7 @@
       <c r="AD98" s="8"/>
       <c r="AE98" s="8"/>
     </row>
-    <row r="99" spans="1:31" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:31" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" s="8">
         <v>1505</v>
       </c>
@@ -11960,7 +11962,7 @@
       <c r="AD99" s="8"/>
       <c r="AE99" s="8"/>
     </row>
-    <row r="100" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" s="8">
         <v>1506</v>
       </c>
@@ -12039,7 +12041,7 @@
       <c r="AD100" s="8"/>
       <c r="AE100" s="8"/>
     </row>
-    <row r="101" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" s="8">
         <v>1507</v>
       </c>
@@ -12116,7 +12118,7 @@
       <c r="AD101" s="8"/>
       <c r="AE101" s="8"/>
     </row>
-    <row r="102" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" s="8">
         <v>1508</v>
       </c>
@@ -12193,7 +12195,7 @@
       <c r="AD102" s="8"/>
       <c r="AE102" s="8"/>
     </row>
-    <row r="103" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" s="8">
         <v>1509</v>
       </c>
@@ -12270,7 +12272,7 @@
       <c r="AD103" s="8"/>
       <c r="AE103" s="8"/>
     </row>
-    <row r="104" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" s="8">
         <v>1510</v>
       </c>
@@ -12349,7 +12351,7 @@
       <c r="AD104" s="8"/>
       <c r="AE104" s="8"/>
     </row>
-    <row r="105" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" s="8">
         <v>1511</v>
       </c>
@@ -12426,7 +12428,7 @@
       <c r="AD105" s="8"/>
       <c r="AE105" s="8"/>
     </row>
-    <row r="106" spans="1:31" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:31" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" s="8">
         <v>1512</v>
       </c>
@@ -12505,7 +12507,7 @@
       <c r="AD106" s="8"/>
       <c r="AE106" s="8"/>
     </row>
-    <row r="107" spans="1:31" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:31" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" s="8">
         <v>1513</v>
       </c>
@@ -12586,7 +12588,7 @@
       <c r="AD107" s="8"/>
       <c r="AE107" s="8"/>
     </row>
-    <row r="108" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" s="8">
         <v>1515</v>
       </c>
@@ -12665,7 +12667,7 @@
       <c r="AD108" s="8"/>
       <c r="AE108" s="8"/>
     </row>
-    <row r="109" spans="1:31" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:31" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" s="8">
         <v>1518</v>
       </c>
@@ -12744,7 +12746,7 @@
       <c r="AD109" s="8"/>
       <c r="AE109" s="8"/>
     </row>
-    <row r="110" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" s="8">
         <v>1519</v>
       </c>
@@ -12823,7 +12825,7 @@
       <c r="AD110" s="8"/>
       <c r="AE110" s="8"/>
     </row>
-    <row r="111" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" s="8">
         <v>1520</v>
       </c>
@@ -12902,7 +12904,7 @@
       <c r="AD111" s="8"/>
       <c r="AE111" s="8"/>
     </row>
-    <row r="112" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" s="8">
         <v>1521</v>
       </c>
@@ -12983,7 +12985,7 @@
       <c r="AD112" s="8"/>
       <c r="AE112" s="8"/>
     </row>
-    <row r="113" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" s="8">
         <v>1522</v>
       </c>
@@ -13064,7 +13066,7 @@
       <c r="AD113" s="8"/>
       <c r="AE113" s="8"/>
     </row>
-    <row r="114" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" s="8">
         <v>1523</v>
       </c>
@@ -13145,7 +13147,7 @@
       <c r="AD114" s="8"/>
       <c r="AE114" s="8"/>
     </row>
-    <row r="115" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" s="8">
         <v>1524</v>
       </c>
@@ -13226,7 +13228,7 @@
       <c r="AD115" s="8"/>
       <c r="AE115" s="8"/>
     </row>
-    <row r="116" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116" s="8">
         <v>1525</v>
       </c>
@@ -13307,7 +13309,7 @@
       <c r="AD116" s="8"/>
       <c r="AE116" s="8"/>
     </row>
-    <row r="117" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" s="8">
         <v>1527</v>
       </c>
@@ -13388,7 +13390,7 @@
       <c r="AD117" s="8"/>
       <c r="AE117" s="8"/>
     </row>
-    <row r="118" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118" s="8">
         <v>1529</v>
       </c>
@@ -13469,7 +13471,7 @@
       <c r="AD118" s="8"/>
       <c r="AE118" s="8"/>
     </row>
-    <row r="119" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" s="8">
         <v>1530</v>
       </c>
@@ -13550,7 +13552,7 @@
       <c r="AD119" s="8"/>
       <c r="AE119" s="8"/>
     </row>
-    <row r="120" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120" s="8">
         <v>1531</v>
       </c>
@@ -13631,7 +13633,7 @@
       <c r="AD120" s="8"/>
       <c r="AE120" s="8"/>
     </row>
-    <row r="121" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" s="8">
         <v>1532</v>
       </c>
@@ -13712,7 +13714,7 @@
       <c r="AD121" s="8"/>
       <c r="AE121" s="8"/>
     </row>
-    <row r="122" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122" s="8">
         <v>1533</v>
       </c>
@@ -13793,7 +13795,7 @@
       <c r="AD122" s="8"/>
       <c r="AE122" s="8"/>
     </row>
-    <row r="123" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123" s="8">
         <v>1534</v>
       </c>
@@ -13874,7 +13876,7 @@
       <c r="AD123" s="8"/>
       <c r="AE123" s="8"/>
     </row>
-    <row r="124" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124" s="8">
         <v>1535</v>
       </c>
@@ -13955,7 +13957,7 @@
       <c r="AD124" s="8"/>
       <c r="AE124" s="8"/>
     </row>
-    <row r="125" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" s="8">
         <v>1536</v>
       </c>
@@ -14036,7 +14038,7 @@
       <c r="AD125" s="8"/>
       <c r="AE125" s="8"/>
     </row>
-    <row r="126" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126" s="8">
         <v>1537</v>
       </c>
@@ -14115,7 +14117,7 @@
       <c r="AD126" s="8"/>
       <c r="AE126" s="8"/>
     </row>
-    <row r="127" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127" s="8">
         <v>1538</v>
       </c>
@@ -14188,7 +14190,7 @@
       <c r="AD127" s="8"/>
       <c r="AE127" s="8"/>
     </row>
-    <row r="128" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128" s="8">
         <v>1541</v>
       </c>
@@ -14261,7 +14263,7 @@
       <c r="AD128" s="8"/>
       <c r="AE128" s="8"/>
     </row>
-    <row r="129" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129" s="8">
         <v>1542</v>
       </c>
@@ -14334,7 +14336,7 @@
       <c r="AD129" s="8"/>
       <c r="AE129" s="8"/>
     </row>
-    <row r="130" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130" s="8">
         <v>1543</v>
       </c>
@@ -14407,7 +14409,7 @@
       <c r="AD130" s="8"/>
       <c r="AE130" s="8"/>
     </row>
-    <row r="131" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131" s="8">
         <v>1546</v>
       </c>
@@ -14480,7 +14482,7 @@
       <c r="AD131" s="8"/>
       <c r="AE131" s="8"/>
     </row>
-    <row r="132" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132" s="8">
         <v>1549</v>
       </c>
@@ -14553,7 +14555,7 @@
       <c r="AD132" s="8"/>
       <c r="AE132" s="8"/>
     </row>
-    <row r="133" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133" s="8">
         <v>1550</v>
       </c>
@@ -14626,7 +14628,7 @@
       <c r="AD133" s="8"/>
       <c r="AE133" s="8"/>
     </row>
-    <row r="134" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134" s="8">
         <v>1551</v>
       </c>
@@ -14699,7 +14701,7 @@
       <c r="AD134" s="8"/>
       <c r="AE134" s="8"/>
     </row>
-    <row r="135" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135" s="8">
         <v>1552</v>
       </c>
@@ -14772,7 +14774,7 @@
       <c r="AD135" s="8"/>
       <c r="AE135" s="8"/>
     </row>
-    <row r="136" spans="1:31" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:31" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136" s="8">
         <v>1555</v>
       </c>
@@ -14845,7 +14847,7 @@
       <c r="AD136" s="8"/>
       <c r="AE136" s="8"/>
     </row>
-    <row r="137" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137" s="8">
         <v>1558</v>
       </c>
@@ -14918,7 +14920,7 @@
       <c r="AD137" s="8"/>
       <c r="AE137" s="8"/>
     </row>
-    <row r="138" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138" s="8">
         <v>1559</v>
       </c>
@@ -14993,7 +14995,7 @@
       <c r="AD138" s="8"/>
       <c r="AE138" s="8"/>
     </row>
-    <row r="139" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139" s="8">
         <v>1560</v>
       </c>
@@ -15070,7 +15072,7 @@
       <c r="AD139" s="8"/>
       <c r="AE139" s="8"/>
     </row>
-    <row r="140" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140" s="8">
         <v>1561</v>
       </c>
@@ -15147,7 +15149,7 @@
       <c r="AD140" s="8"/>
       <c r="AE140" s="8"/>
     </row>
-    <row r="141" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141" s="8">
         <v>1562</v>
       </c>
@@ -15224,7 +15226,7 @@
       <c r="AD141" s="8"/>
       <c r="AE141" s="8"/>
     </row>
-    <row r="142" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142" s="8">
         <v>1563</v>
       </c>
@@ -15301,7 +15303,7 @@
       <c r="AD142" s="8"/>
       <c r="AE142" s="8"/>
     </row>
-    <row r="143" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143" s="8">
         <v>1564</v>
       </c>
@@ -15378,7 +15380,7 @@
       <c r="AD143" s="8"/>
       <c r="AE143" s="8"/>
     </row>
-    <row r="144" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144" s="8">
         <v>1565</v>
       </c>
@@ -15455,7 +15457,7 @@
       <c r="AD144" s="8"/>
       <c r="AE144" s="8"/>
     </row>
-    <row r="145" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145" s="8">
         <v>1566</v>
       </c>
@@ -15532,7 +15534,7 @@
       <c r="AD145" s="8"/>
       <c r="AE145" s="8"/>
     </row>
-    <row r="146" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146" s="8">
         <v>1567</v>
       </c>
@@ -15609,7 +15611,7 @@
       <c r="AD146" s="8"/>
       <c r="AE146" s="8"/>
     </row>
-    <row r="147" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147" s="8">
         <v>1569</v>
       </c>
@@ -15684,7 +15686,7 @@
       <c r="AD147" s="8"/>
       <c r="AE147" s="8"/>
     </row>
-    <row r="148" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148" s="8">
         <v>1572</v>
       </c>
@@ -15761,7 +15763,7 @@
       <c r="AD148" s="8"/>
       <c r="AE148" s="8"/>
     </row>
-    <row r="149" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149" s="8">
         <v>1573</v>
       </c>
@@ -15834,7 +15836,7 @@
       <c r="AD149" s="8"/>
       <c r="AE149" s="8"/>
     </row>
-    <row r="150" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150" s="8">
         <v>1576</v>
       </c>
@@ -15907,7 +15909,7 @@
       <c r="AD150" s="8"/>
       <c r="AE150" s="8"/>
     </row>
-    <row r="151" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151" s="8">
         <v>1577</v>
       </c>
@@ -15980,7 +15982,7 @@
       <c r="AD151" s="8"/>
       <c r="AE151" s="8"/>
     </row>
-    <row r="152" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152" s="8">
         <v>1580</v>
       </c>
@@ -16053,7 +16055,7 @@
       <c r="AD152" s="8"/>
       <c r="AE152" s="8"/>
     </row>
-    <row r="153" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153" s="8">
         <v>1581</v>
       </c>
@@ -16126,7 +16128,7 @@
       <c r="AD153" s="8"/>
       <c r="AE153" s="8"/>
     </row>
-    <row r="154" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154" s="8">
         <v>1586</v>
       </c>
@@ -16195,7 +16197,7 @@
       <c r="AD154" s="8"/>
       <c r="AE154" s="8"/>
     </row>
-    <row r="155" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155" s="8">
         <v>1587</v>
       </c>
@@ -16264,7 +16266,7 @@
       <c r="AD155" s="8"/>
       <c r="AE155" s="8"/>
     </row>
-    <row r="156" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156" s="8">
         <v>1589</v>
       </c>
@@ -16333,7 +16335,7 @@
       <c r="AD156" s="8"/>
       <c r="AE156" s="8"/>
     </row>
-    <row r="157" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157" s="8">
         <v>1590</v>
       </c>
@@ -16402,7 +16404,7 @@
       <c r="AD157" s="8"/>
       <c r="AE157" s="8"/>
     </row>
-    <row r="158" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158" s="8">
         <v>1591</v>
       </c>
@@ -16473,7 +16475,7 @@
       <c r="AD158" s="8"/>
       <c r="AE158" s="8"/>
     </row>
-    <row r="159" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159" s="8">
         <v>1592</v>
       </c>
@@ -16546,7 +16548,7 @@
       <c r="AD159" s="8"/>
       <c r="AE159" s="8"/>
     </row>
-    <row r="160" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160" s="8">
         <v>1593</v>
       </c>
@@ -16619,7 +16621,7 @@
       <c r="AD160" s="8"/>
       <c r="AE160" s="8"/>
     </row>
-    <row r="161" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161" s="8">
         <v>1594</v>
       </c>
@@ -16692,7 +16694,7 @@
       <c r="AD161" s="8"/>
       <c r="AE161" s="8"/>
     </row>
-    <row r="162" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A162" s="8">
         <v>1595</v>
       </c>
@@ -16773,7 +16775,7 @@
       <c r="AD162" s="8"/>
       <c r="AE162" s="8"/>
     </row>
-    <row r="163" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A163" s="8">
         <v>1596</v>
       </c>
@@ -16854,7 +16856,7 @@
       <c r="AD163" s="8"/>
       <c r="AE163" s="8"/>
     </row>
-    <row r="164" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164" s="8">
         <v>1597</v>
       </c>
@@ -16935,7 +16937,7 @@
       <c r="AD164" s="8"/>
       <c r="AE164" s="8"/>
     </row>
-    <row r="165" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A165" s="8">
         <v>1598</v>
       </c>
@@ -17016,7 +17018,7 @@
       <c r="AD165" s="8"/>
       <c r="AE165" s="8"/>
     </row>
-    <row r="166" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166" s="8">
         <v>1599</v>
       </c>
@@ -17097,7 +17099,7 @@
       <c r="AD166" s="8"/>
       <c r="AE166" s="8"/>
     </row>
-    <row r="167" spans="1:31" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:31" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A167" s="8">
         <v>1600</v>
       </c>
@@ -17170,7 +17172,7 @@
       <c r="AD167" s="8"/>
       <c r="AE167" s="8"/>
     </row>
-    <row r="168" spans="1:31" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:31" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A168" s="8">
         <v>1601</v>
       </c>
@@ -17243,7 +17245,7 @@
       <c r="AD168" s="8"/>
       <c r="AE168" s="8"/>
     </row>
-    <row r="169" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A169" s="8">
         <v>1602</v>
       </c>
@@ -17310,7 +17312,7 @@
       <c r="AD169" s="8"/>
       <c r="AE169" s="8"/>
     </row>
-    <row r="170" spans="1:31" ht="316.8" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:31" ht="316.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170" s="8">
         <v>1603</v>
       </c>
@@ -17393,7 +17395,7 @@
       <c r="AD170" s="8"/>
       <c r="AE170" s="8"/>
     </row>
-    <row r="171" spans="1:31" ht="316.8" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:31" ht="316.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171" s="8">
         <v>1604</v>
       </c>
@@ -17476,7 +17478,7 @@
       <c r="AD171" s="8"/>
       <c r="AE171" s="8"/>
     </row>
-    <row r="172" spans="1:31" ht="316.8" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:31" ht="316.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172" s="8">
         <v>1605</v>
       </c>
@@ -17559,7 +17561,7 @@
       <c r="AD172" s="8"/>
       <c r="AE172" s="8"/>
     </row>
-    <row r="173" spans="1:31" ht="316.8" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:31" ht="316.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A173" s="8">
         <v>1606</v>
       </c>
@@ -17644,7 +17646,7 @@
       <c r="AD173" s="8"/>
       <c r="AE173" s="8"/>
     </row>
-    <row r="174" spans="1:31" ht="316.8" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:31" ht="316.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A174" s="8">
         <v>1607</v>
       </c>
@@ -17729,7 +17731,7 @@
       <c r="AD174" s="8"/>
       <c r="AE174" s="8"/>
     </row>
-    <row r="175" spans="1:31" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:31" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A175" s="8">
         <v>1608</v>
       </c>
@@ -17800,7 +17802,7 @@
       <c r="AD175" s="8"/>
       <c r="AE175" s="8"/>
     </row>
-    <row r="176" spans="1:31" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:31" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A176" s="8">
         <v>1609</v>
       </c>
@@ -17871,7 +17873,7 @@
       <c r="AD176" s="8"/>
       <c r="AE176" s="8"/>
     </row>
-    <row r="177" spans="1:31" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:31" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A177" s="8">
         <v>1610</v>
       </c>
@@ -17942,7 +17944,7 @@
       <c r="AD177" s="8"/>
       <c r="AE177" s="8"/>
     </row>
-    <row r="178" spans="1:31" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:31" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A178" s="8">
         <v>1611</v>
       </c>
@@ -18013,7 +18015,7 @@
       <c r="AD178" s="8"/>
       <c r="AE178" s="8"/>
     </row>
-    <row r="179" spans="1:31" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:31" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179" s="8">
         <v>1612</v>
       </c>
@@ -18080,7 +18082,7 @@
       <c r="AD179" s="8"/>
       <c r="AE179" s="8"/>
     </row>
-    <row r="180" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A180" s="8">
         <v>1614</v>
       </c>
@@ -18161,7 +18163,7 @@
       <c r="AD180" s="8"/>
       <c r="AE180" s="8"/>
     </row>
-    <row r="181" spans="1:31" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:31" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A181" s="8">
         <v>1615</v>
       </c>
@@ -18242,7 +18244,7 @@
       <c r="AD181" s="8"/>
       <c r="AE181" s="8"/>
     </row>
-    <row r="182" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A182" s="8">
         <v>1616</v>
       </c>
@@ -18323,7 +18325,7 @@
       <c r="AD182" s="8"/>
       <c r="AE182" s="8"/>
     </row>
-    <row r="183" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A183" s="8">
         <v>1617</v>
       </c>
@@ -18404,7 +18406,7 @@
       <c r="AD183" s="8"/>
       <c r="AE183" s="8"/>
     </row>
-    <row r="184" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A184" s="8">
         <v>1618</v>
       </c>
@@ -18485,7 +18487,7 @@
       <c r="AD184" s="8"/>
       <c r="AE184" s="8"/>
     </row>
-    <row r="185" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A185" s="8">
         <v>1621</v>
       </c>
@@ -18566,7 +18568,7 @@
       <c r="AD185" s="8"/>
       <c r="AE185" s="8"/>
     </row>
-    <row r="186" spans="1:31" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:31" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A186" s="8">
         <v>1622</v>
       </c>
@@ -18647,7 +18649,7 @@
       <c r="AD186" s="8"/>
       <c r="AE186" s="8"/>
     </row>
-    <row r="187" spans="1:31" ht="72" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:31" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A187" s="8">
         <v>1623</v>
       </c>
@@ -18728,7 +18730,7 @@
       <c r="AD187" s="8"/>
       <c r="AE187" s="8"/>
     </row>
-    <row r="188" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A188" s="8">
         <v>1624</v>
       </c>
@@ -18809,7 +18811,7 @@
       <c r="AD188" s="8"/>
       <c r="AE188" s="8"/>
     </row>
-    <row r="189" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A189" s="8">
         <v>1625</v>
       </c>
@@ -18890,7 +18892,7 @@
       <c r="AD189" s="8"/>
       <c r="AE189" s="8"/>
     </row>
-    <row r="190" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A190" s="8">
         <v>1627</v>
       </c>
@@ -18961,7 +18963,7 @@
       <c r="AD190" s="8"/>
       <c r="AE190" s="8"/>
     </row>
-    <row r="191" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A191" s="8">
         <v>1628</v>
       </c>
@@ -19032,7 +19034,7 @@
       <c r="AD191" s="8"/>
       <c r="AE191" s="8"/>
     </row>
-    <row r="192" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A192" s="8">
         <v>1629</v>
       </c>
@@ -19103,7 +19105,7 @@
       <c r="AD192" s="8"/>
       <c r="AE192" s="8"/>
     </row>
-    <row r="193" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A193" s="8">
         <v>1630</v>
       </c>
@@ -19174,7 +19176,7 @@
       <c r="AD193" s="8"/>
       <c r="AE193" s="8"/>
     </row>
-    <row r="194" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A194" s="8">
         <v>1631</v>
       </c>
@@ -19241,7 +19243,7 @@
       <c r="AD194" s="8"/>
       <c r="AE194" s="8"/>
     </row>
-    <row r="195" spans="1:31" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:31" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A195" s="8">
         <v>1632</v>
       </c>
@@ -19322,7 +19324,7 @@
       <c r="AD195" s="8"/>
       <c r="AE195" s="8"/>
     </row>
-    <row r="196" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A196" s="8">
         <v>1633</v>
       </c>
@@ -19403,7 +19405,7 @@
       <c r="AD196" s="8"/>
       <c r="AE196" s="8"/>
     </row>
-    <row r="197" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A197" s="8">
         <v>1634</v>
       </c>
@@ -19484,7 +19486,7 @@
       <c r="AD197" s="8"/>
       <c r="AE197" s="8"/>
     </row>
-    <row r="198" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A198" s="8">
         <v>1635</v>
       </c>
@@ -19565,7 +19567,7 @@
       <c r="AD198" s="8"/>
       <c r="AE198" s="8"/>
     </row>
-    <row r="199" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A199" s="8">
         <v>1636</v>
       </c>
@@ -19648,7 +19650,7 @@
       <c r="AD199" s="8"/>
       <c r="AE199" s="8"/>
     </row>
-    <row r="200" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A200" s="8">
         <v>1640</v>
       </c>
@@ -19727,7 +19729,7 @@
       <c r="AD200" s="8"/>
       <c r="AE200" s="8"/>
     </row>
-    <row r="201" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A201" s="8">
         <v>1641</v>
       </c>
@@ -19806,7 +19808,7 @@
       <c r="AD201" s="8"/>
       <c r="AE201" s="8"/>
     </row>
-    <row r="202" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A202" s="8">
         <v>1642</v>
       </c>
@@ -19885,7 +19887,7 @@
       <c r="AD202" s="8"/>
       <c r="AE202" s="8"/>
     </row>
-    <row r="203" spans="1:31" ht="144" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:31" ht="144" hidden="1" x14ac:dyDescent="0.3">
       <c r="A203" s="8">
         <v>1643</v>
       </c>
@@ -19962,7 +19964,7 @@
       <c r="AD203" s="8"/>
       <c r="AE203" s="8"/>
     </row>
-    <row r="204" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A204" s="8">
         <v>1644</v>
       </c>
@@ -20039,7 +20041,7 @@
       <c r="AD204" s="8"/>
       <c r="AE204" s="8"/>
     </row>
-    <row r="205" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A205" s="8">
         <v>1645</v>
       </c>
@@ -20114,7 +20116,7 @@
       <c r="AD205" s="8"/>
       <c r="AE205" s="8"/>
     </row>
-    <row r="206" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A206" s="8">
         <v>1646</v>
       </c>
@@ -20189,7 +20191,7 @@
       <c r="AD206" s="8"/>
       <c r="AE206" s="8"/>
     </row>
-    <row r="207" spans="1:31" ht="72" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:31" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A207" s="8">
         <v>1647</v>
       </c>
@@ -20264,7 +20266,7 @@
       <c r="AD207" s="8"/>
       <c r="AE207" s="8"/>
     </row>
-    <row r="208" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A208" s="8">
         <v>1648</v>
       </c>
@@ -20339,7 +20341,7 @@
       <c r="AD208" s="8"/>
       <c r="AE208" s="8"/>
     </row>
-    <row r="209" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A209" s="8">
         <v>1649</v>
       </c>
@@ -20414,7 +20416,7 @@
       <c r="AD209" s="8"/>
       <c r="AE209" s="8"/>
     </row>
-    <row r="210" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A210" s="8">
         <v>1650</v>
       </c>
@@ -20489,7 +20491,7 @@
       <c r="AD210" s="8"/>
       <c r="AE210" s="8"/>
     </row>
-    <row r="211" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A211" s="8">
         <v>1653</v>
       </c>
@@ -20558,7 +20560,7 @@
       <c r="AD211" s="8"/>
       <c r="AE211" s="8"/>
     </row>
-    <row r="212" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A212" s="8">
         <v>1654</v>
       </c>
@@ -20627,7 +20629,7 @@
       <c r="AD212" s="8"/>
       <c r="AE212" s="8"/>
     </row>
-    <row r="213" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A213" s="8">
         <v>1655</v>
       </c>
@@ -20698,7 +20700,7 @@
       <c r="AD213" s="8"/>
       <c r="AE213" s="8"/>
     </row>
-    <row r="214" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A214" s="8">
         <v>1656</v>
       </c>
@@ -20769,7 +20771,7 @@
       <c r="AD214" s="8"/>
       <c r="AE214" s="8"/>
     </row>
-    <row r="215" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A215" s="8">
         <v>1657</v>
       </c>
@@ -20836,7 +20838,7 @@
       <c r="AD215" s="8"/>
       <c r="AE215" s="8"/>
     </row>
-    <row r="216" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A216" s="8">
         <v>1658</v>
       </c>
@@ -20907,7 +20909,7 @@
       <c r="AD216" s="8"/>
       <c r="AE216" s="8"/>
     </row>
-    <row r="217" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A217" s="8">
         <v>1659</v>
       </c>
@@ -20978,7 +20980,7 @@
       <c r="AD217" s="8"/>
       <c r="AE217" s="8"/>
     </row>
-    <row r="218" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A218" s="8">
         <v>1660</v>
       </c>
@@ -21047,7 +21049,7 @@
       <c r="AD218" s="8"/>
       <c r="AE218" s="8"/>
     </row>
-    <row r="219" spans="1:31" ht="230.4" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:31" ht="230.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A219" s="8">
         <v>1661</v>
       </c>
@@ -21116,7 +21118,7 @@
       <c r="AD219" s="8"/>
       <c r="AE219" s="8"/>
     </row>
-    <row r="220" spans="1:31" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:31" ht="158.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A220" s="8">
         <v>1662</v>
       </c>
@@ -21185,7 +21187,7 @@
       <c r="AD220" s="8"/>
       <c r="AE220" s="8"/>
     </row>
-    <row r="221" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A221" s="8">
         <v>1663</v>
       </c>
@@ -21252,7 +21254,7 @@
       <c r="AD221" s="8"/>
       <c r="AE221" s="8"/>
     </row>
-    <row r="222" spans="1:31" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:31" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A222" s="8">
         <v>1664</v>
       </c>
@@ -21321,7 +21323,7 @@
       <c r="AD222" s="8"/>
       <c r="AE222" s="8"/>
     </row>
-    <row r="223" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A223" s="8">
         <v>1665</v>
       </c>
@@ -21388,7 +21390,7 @@
       <c r="AD223" s="8"/>
       <c r="AE223" s="8"/>
     </row>
-    <row r="224" spans="1:31" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:31" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A224" s="8">
         <v>1666</v>
       </c>
@@ -21459,7 +21461,7 @@
       <c r="AD224" s="8"/>
       <c r="AE224" s="8"/>
     </row>
-    <row r="225" spans="1:31" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:31" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A225" s="8">
         <v>1667</v>
       </c>
@@ -21530,7 +21532,7 @@
       <c r="AD225" s="8"/>
       <c r="AE225" s="8"/>
     </row>
-    <row r="226" spans="1:31" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:31" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A226" s="8">
         <v>1668</v>
       </c>
@@ -21597,7 +21599,7 @@
       <c r="AD226" s="8"/>
       <c r="AE226" s="8"/>
     </row>
-    <row r="227" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A227" s="8">
         <v>1671</v>
       </c>
@@ -21678,7 +21680,7 @@
       <c r="AD227" s="8"/>
       <c r="AE227" s="8"/>
     </row>
-    <row r="228" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A228" s="8">
         <v>1672</v>
       </c>
@@ -21759,7 +21761,7 @@
       <c r="AD228" s="8"/>
       <c r="AE228" s="8"/>
     </row>
-    <row r="229" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A229" s="8">
         <v>1673</v>
       </c>
@@ -21840,7 +21842,7 @@
       <c r="AD229" s="8"/>
       <c r="AE229" s="8"/>
     </row>
-    <row r="230" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A230" s="8">
         <v>1674</v>
       </c>
@@ -21921,7 +21923,7 @@
       <c r="AD230" s="8"/>
       <c r="AE230" s="8"/>
     </row>
-    <row r="231" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A231" s="8">
         <v>1675</v>
       </c>
@@ -22002,7 +22004,7 @@
       <c r="AD231" s="8"/>
       <c r="AE231" s="8"/>
     </row>
-    <row r="232" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A232" s="8">
         <v>1677</v>
       </c>
@@ -22083,7 +22085,7 @@
       <c r="AD232" s="8"/>
       <c r="AE232" s="8"/>
     </row>
-    <row r="233" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A233" s="8">
         <v>1678</v>
       </c>
@@ -22164,7 +22166,7 @@
       <c r="AD233" s="8"/>
       <c r="AE233" s="8"/>
     </row>
-    <row r="234" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A234" s="8">
         <v>1679</v>
       </c>
@@ -22245,7 +22247,7 @@
       <c r="AD234" s="8"/>
       <c r="AE234" s="8"/>
     </row>
-    <row r="235" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A235" s="8">
         <v>1680</v>
       </c>
@@ -22326,7 +22328,7 @@
       <c r="AD235" s="8"/>
       <c r="AE235" s="8"/>
     </row>
-    <row r="236" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A236" s="8">
         <v>1682</v>
       </c>
@@ -22397,7 +22399,7 @@
       <c r="AD236" s="8"/>
       <c r="AE236" s="8"/>
     </row>
-    <row r="237" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A237" s="8">
         <v>1683</v>
       </c>
@@ -22468,7 +22470,7 @@
       <c r="AD237" s="8"/>
       <c r="AE237" s="8"/>
     </row>
-    <row r="238" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A238" s="8">
         <v>1684</v>
       </c>
@@ -22539,7 +22541,7 @@
       <c r="AD238" s="8"/>
       <c r="AE238" s="8"/>
     </row>
-    <row r="239" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A239" s="8">
         <v>1685</v>
       </c>
@@ -22606,7 +22608,7 @@
       <c r="AD239" s="8"/>
       <c r="AE239" s="8"/>
     </row>
-    <row r="240" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A240" s="8">
         <v>1686</v>
       </c>
@@ -22673,7 +22675,7 @@
       <c r="AD240" s="8"/>
       <c r="AE240" s="8"/>
     </row>
-    <row r="241" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A241" s="8">
         <v>1688</v>
       </c>
@@ -22752,7 +22754,7 @@
       <c r="AD241" s="8"/>
       <c r="AE241" s="8"/>
     </row>
-    <row r="242" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A242" s="8">
         <v>1689</v>
       </c>
@@ -22831,7 +22833,7 @@
       <c r="AD242" s="8"/>
       <c r="AE242" s="8"/>
     </row>
-    <row r="243" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A243" s="8">
         <v>1690</v>
       </c>
@@ -22910,7 +22912,7 @@
       <c r="AD243" s="8"/>
       <c r="AE243" s="8"/>
     </row>
-    <row r="244" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A244" s="8">
         <v>1691</v>
       </c>
@@ -22989,7 +22991,7 @@
       <c r="AD244" s="8"/>
       <c r="AE244" s="8"/>
     </row>
-    <row r="245" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A245" s="8">
         <v>1692</v>
       </c>
@@ -23068,7 +23070,7 @@
       <c r="AD245" s="8"/>
       <c r="AE245" s="8"/>
     </row>
-    <row r="246" spans="1:31" ht="72" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:31" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A246" s="8">
         <v>1693</v>
       </c>
@@ -23139,7 +23141,7 @@
       <c r="AD246" s="8"/>
       <c r="AE246" s="8"/>
     </row>
-    <row r="247" spans="1:31" ht="72" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:31" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A247" s="8">
         <v>1694</v>
       </c>
@@ -23208,7 +23210,7 @@
       <c r="AD247" s="8"/>
       <c r="AE247" s="8"/>
     </row>
-    <row r="248" spans="1:31" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:31" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A248" s="8">
         <v>1695</v>
       </c>
@@ -23279,7 +23281,7 @@
       <c r="AD248" s="8"/>
       <c r="AE248" s="8"/>
     </row>
-    <row r="249" spans="1:31" ht="72" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:31" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A249" s="8">
         <v>1696</v>
       </c>
@@ -23350,7 +23352,7 @@
       <c r="AD249" s="8"/>
       <c r="AE249" s="8"/>
     </row>
-    <row r="250" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A250" s="8">
         <v>1697</v>
       </c>
@@ -23421,7 +23423,7 @@
       <c r="AD250" s="8"/>
       <c r="AE250" s="8"/>
     </row>
-    <row r="251" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A251" s="8">
         <v>1698</v>
       </c>
@@ -23492,7 +23494,7 @@
       <c r="AD251" s="8"/>
       <c r="AE251" s="8"/>
     </row>
-    <row r="252" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A252" s="8">
         <v>1699</v>
       </c>
@@ -23563,7 +23565,7 @@
       <c r="AD252" s="8"/>
       <c r="AE252" s="8"/>
     </row>
-    <row r="253" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A253" s="8">
         <v>1700</v>
       </c>
@@ -23634,7 +23636,7 @@
       <c r="AD253" s="8"/>
       <c r="AE253" s="8"/>
     </row>
-    <row r="254" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A254" s="8">
         <v>1701</v>
       </c>
@@ -23705,7 +23707,7 @@
       <c r="AD254" s="8"/>
       <c r="AE254" s="8"/>
     </row>
-    <row r="255" spans="1:31" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:31" ht="129.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A255" s="8">
         <v>1707</v>
       </c>
@@ -23786,7 +23788,7 @@
       <c r="AD255" s="8"/>
       <c r="AE255" s="8"/>
     </row>
-    <row r="256" spans="1:31" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:31" ht="129.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A256" s="8">
         <v>1708</v>
       </c>
@@ -23867,7 +23869,7 @@
       <c r="AD256" s="8"/>
       <c r="AE256" s="8"/>
     </row>
-    <row r="257" spans="1:31" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:31" ht="129.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A257" s="8">
         <v>1709</v>
       </c>
@@ -23948,7 +23950,7 @@
       <c r="AD257" s="8"/>
       <c r="AE257" s="8"/>
     </row>
-    <row r="258" spans="1:31" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:31" ht="129.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A258" s="8">
         <v>1710</v>
       </c>
@@ -24029,7 +24031,7 @@
       <c r="AD258" s="8"/>
       <c r="AE258" s="8"/>
     </row>
-    <row r="259" spans="1:31" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:31" ht="129.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A259" s="8">
         <v>1711</v>
       </c>
@@ -24110,7 +24112,7 @@
       <c r="AD259" s="8"/>
       <c r="AE259" s="8"/>
     </row>
-    <row r="260" spans="1:31" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:31" ht="129.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A260" s="8">
         <v>1712</v>
       </c>
@@ -24191,7 +24193,7 @@
       <c r="AD260" s="8"/>
       <c r="AE260" s="8"/>
     </row>
-    <row r="261" spans="1:31" ht="144" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:31" ht="144" hidden="1" x14ac:dyDescent="0.3">
       <c r="A261" s="8">
         <v>1713</v>
       </c>
@@ -24262,7 +24264,7 @@
       <c r="AD261" s="8"/>
       <c r="AE261" s="8"/>
     </row>
-    <row r="262" spans="1:31" ht="144" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:31" ht="144" hidden="1" x14ac:dyDescent="0.3">
       <c r="A262" s="8">
         <v>1714</v>
       </c>
@@ -24335,7 +24337,7 @@
       <c r="AD262" s="8"/>
       <c r="AE262" s="8"/>
     </row>
-    <row r="263" spans="1:31" ht="144" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:31" ht="144" hidden="1" x14ac:dyDescent="0.3">
       <c r="A263" s="8">
         <v>1715</v>
       </c>
@@ -24408,7 +24410,7 @@
       <c r="AD263" s="8"/>
       <c r="AE263" s="8"/>
     </row>
-    <row r="264" spans="1:31" ht="144" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:31" ht="144" hidden="1" x14ac:dyDescent="0.3">
       <c r="A264" s="8">
         <v>1716</v>
       </c>
@@ -24481,7 +24483,7 @@
       <c r="AD264" s="8"/>
       <c r="AE264" s="8"/>
     </row>
-    <row r="265" spans="1:31" ht="144" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:31" ht="144" hidden="1" x14ac:dyDescent="0.3">
       <c r="A265" s="8">
         <v>1717</v>
       </c>
@@ -24554,7 +24556,7 @@
       <c r="AD265" s="8"/>
       <c r="AE265" s="8"/>
     </row>
-    <row r="266" spans="1:31" ht="144" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:31" ht="144" hidden="1" x14ac:dyDescent="0.3">
       <c r="A266" s="8">
         <v>1718</v>
       </c>
@@ -24627,7 +24629,7 @@
       <c r="AD266" s="8"/>
       <c r="AE266" s="8"/>
     </row>
-    <row r="267" spans="1:31" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:31" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A267" s="8">
         <v>1719</v>
       </c>
@@ -24706,7 +24708,7 @@
       <c r="AD267" s="8"/>
       <c r="AE267" s="8"/>
     </row>
-    <row r="268" spans="1:31" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:31" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A268" s="8">
         <v>1720</v>
       </c>
@@ -24785,7 +24787,7 @@
       <c r="AD268" s="8"/>
       <c r="AE268" s="8"/>
     </row>
-    <row r="269" spans="1:31" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:31" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A269" s="8">
         <v>1721</v>
       </c>
@@ -24864,7 +24866,7 @@
       <c r="AD269" s="8"/>
       <c r="AE269" s="8"/>
     </row>
-    <row r="270" spans="1:31" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:31" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A270" s="8">
         <v>1722</v>
       </c>
@@ -24945,7 +24947,7 @@
       <c r="AD270" s="8"/>
       <c r="AE270" s="8"/>
     </row>
-    <row r="271" spans="1:31" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:31" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A271" s="8">
         <v>1723</v>
       </c>
@@ -25024,7 +25026,7 @@
       <c r="AD271" s="8"/>
       <c r="AE271" s="8"/>
     </row>
-    <row r="272" spans="1:31" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:31" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A272" s="8">
         <v>1724</v>
       </c>
@@ -25105,7 +25107,7 @@
       <c r="AD272" s="8"/>
       <c r="AE272" s="8"/>
     </row>
-    <row r="273" spans="1:31" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:31" ht="158.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A273" s="8">
         <v>1725</v>
       </c>
@@ -25178,7 +25180,7 @@
       <c r="AD273" s="8"/>
       <c r="AE273" s="8"/>
     </row>
-    <row r="274" spans="1:31" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:31" ht="158.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A274" s="8">
         <v>1726</v>
       </c>
@@ -25251,7 +25253,7 @@
       <c r="AD274" s="8"/>
       <c r="AE274" s="8"/>
     </row>
-    <row r="275" spans="1:31" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:31" ht="158.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A275" s="8">
         <v>1727</v>
       </c>
@@ -25324,7 +25326,7 @@
       <c r="AD275" s="8"/>
       <c r="AE275" s="8"/>
     </row>
-    <row r="276" spans="1:31" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:31" ht="158.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A276" s="8">
         <v>1728</v>
       </c>
@@ -25397,7 +25399,7 @@
       <c r="AD276" s="8"/>
       <c r="AE276" s="8"/>
     </row>
-    <row r="277" spans="1:31" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:31" ht="158.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A277" s="8">
         <v>1729</v>
       </c>
@@ -25470,7 +25472,7 @@
       <c r="AD277" s="8"/>
       <c r="AE277" s="8"/>
     </row>
-    <row r="278" spans="1:31" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:31" ht="158.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A278" s="8">
         <v>1730</v>
       </c>
@@ -25543,7 +25545,7 @@
       <c r="AD278" s="8"/>
       <c r="AE278" s="8"/>
     </row>
-    <row r="279" spans="1:31" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:31" ht="158.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A279" s="8">
         <v>1731</v>
       </c>
@@ -25614,7 +25616,7 @@
       <c r="AD279" s="8"/>
       <c r="AE279" s="8"/>
     </row>
-    <row r="280" spans="1:31" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:31" ht="158.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A280" s="8">
         <v>1732</v>
       </c>
@@ -25687,7 +25689,7 @@
       <c r="AD280" s="8"/>
       <c r="AE280" s="8"/>
     </row>
-    <row r="281" spans="1:31" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:31" ht="158.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A281" s="8">
         <v>1733</v>
       </c>
@@ -25758,7 +25760,7 @@
       <c r="AD281" s="8"/>
       <c r="AE281" s="8"/>
     </row>
-    <row r="282" spans="1:31" ht="331.2" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:31" ht="331.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A282" s="8">
         <v>1734</v>
       </c>
@@ -25827,7 +25829,7 @@
       <c r="AD282" s="8"/>
       <c r="AE282" s="8"/>
     </row>
-    <row r="283" spans="1:31" ht="331.2" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:31" ht="331.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A283" s="8">
         <v>1735</v>
       </c>
@@ -25900,7 +25902,7 @@
       <c r="AD283" s="8"/>
       <c r="AE283" s="8"/>
     </row>
-    <row r="284" spans="1:31" ht="331.2" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:31" ht="331.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A284" s="8">
         <v>1736</v>
       </c>
@@ -25971,7 +25973,7 @@
       <c r="AD284" s="8"/>
       <c r="AE284" s="8"/>
     </row>
-    <row r="285" spans="1:31" ht="331.2" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:31" ht="331.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A285" s="8">
         <v>1737</v>
       </c>
@@ -26042,7 +26044,7 @@
       <c r="AD285" s="8"/>
       <c r="AE285" s="8"/>
     </row>
-    <row r="286" spans="1:31" ht="331.2" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:31" ht="331.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A286" s="8">
         <v>1738</v>
       </c>
@@ -26115,7 +26117,7 @@
       <c r="AD286" s="8"/>
       <c r="AE286" s="8"/>
     </row>
-    <row r="287" spans="1:31" ht="331.2" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:31" ht="331.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A287" s="8">
         <v>1739</v>
       </c>
@@ -26184,7 +26186,7 @@
       <c r="AD287" s="8"/>
       <c r="AE287" s="8"/>
     </row>
-    <row r="288" spans="1:31" ht="331.2" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:31" ht="331.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A288" s="8">
         <v>1740</v>
       </c>
@@ -26257,7 +26259,7 @@
       <c r="AD288" s="8"/>
       <c r="AE288" s="8"/>
     </row>
-    <row r="289" spans="1:31" ht="331.2" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:31" ht="331.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A289" s="8">
         <v>1741</v>
       </c>
@@ -26326,7 +26328,7 @@
       <c r="AD289" s="8"/>
       <c r="AE289" s="8"/>
     </row>
-    <row r="290" spans="1:31" ht="331.2" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:31" ht="331.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A290" s="8">
         <v>1742</v>
       </c>
@@ -26395,7 +26397,7 @@
       <c r="AD290" s="8"/>
       <c r="AE290" s="8"/>
     </row>
-    <row r="291" spans="1:31" ht="331.2" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:31" ht="331.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A291" s="8">
         <v>1743</v>
       </c>
@@ -26468,7 +26470,7 @@
       <c r="AD291" s="8"/>
       <c r="AE291" s="8"/>
     </row>
-    <row r="292" spans="1:31" ht="331.2" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:31" ht="331.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A292" s="8">
         <v>1744</v>
       </c>
@@ -26539,7 +26541,7 @@
       <c r="AD292" s="8"/>
       <c r="AE292" s="8"/>
     </row>
-    <row r="293" spans="1:31" ht="331.2" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:31" ht="331.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A293" s="8">
         <v>1745</v>
       </c>
@@ -26608,7 +26610,7 @@
       <c r="AD293" s="8"/>
       <c r="AE293" s="8"/>
     </row>
-    <row r="294" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A294" s="8">
         <v>1746</v>
       </c>
@@ -26689,7 +26691,7 @@
       <c r="AD294" s="8"/>
       <c r="AE294" s="8"/>
     </row>
-    <row r="295" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A295" s="8">
         <v>1747</v>
       </c>
@@ -26770,7 +26772,7 @@
       <c r="AD295" s="8"/>
       <c r="AE295" s="8"/>
     </row>
-    <row r="296" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A296" s="8">
         <v>1748</v>
       </c>
@@ -26851,7 +26853,7 @@
       <c r="AD296" s="8"/>
       <c r="AE296" s="8"/>
     </row>
-    <row r="297" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A297" s="8">
         <v>1749</v>
       </c>
@@ -26932,7 +26934,7 @@
       <c r="AD297" s="8"/>
       <c r="AE297" s="8"/>
     </row>
-    <row r="298" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A298" s="8">
         <v>1750</v>
       </c>
@@ -27013,7 +27015,7 @@
       <c r="AD298" s="8"/>
       <c r="AE298" s="8"/>
     </row>
-    <row r="299" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A299" s="8">
         <v>1752</v>
       </c>
@@ -27094,7 +27096,7 @@
       <c r="AD299" s="8"/>
       <c r="AE299" s="8"/>
     </row>
-    <row r="300" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A300" s="8">
         <v>1753</v>
       </c>
@@ -27175,7 +27177,7 @@
       <c r="AD300" s="8"/>
       <c r="AE300" s="8"/>
     </row>
-    <row r="301" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A301" s="8">
         <v>1754</v>
       </c>
@@ -27256,7 +27258,7 @@
       <c r="AD301" s="8"/>
       <c r="AE301" s="8"/>
     </row>
-    <row r="302" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A302" s="8">
         <v>1755</v>
       </c>
@@ -27337,7 +27339,7 @@
       <c r="AD302" s="8"/>
       <c r="AE302" s="8"/>
     </row>
-    <row r="303" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A303" s="8">
         <v>1756</v>
       </c>
@@ -27418,7 +27420,7 @@
       <c r="AD303" s="8"/>
       <c r="AE303" s="8"/>
     </row>
-    <row r="304" spans="1:31" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:31" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A304" s="8">
         <v>1759</v>
       </c>
@@ -27489,7 +27491,7 @@
       <c r="AD304" s="8"/>
       <c r="AE304" s="8"/>
     </row>
-    <row r="305" spans="1:31" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:31" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A305" s="8">
         <v>1760</v>
       </c>
@@ -27560,7 +27562,7 @@
       <c r="AD305" s="8"/>
       <c r="AE305" s="8"/>
     </row>
-    <row r="306" spans="1:31" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:31" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A306" s="8">
         <v>1762</v>
       </c>
@@ -27631,7 +27633,7 @@
       <c r="AD306" s="8"/>
       <c r="AE306" s="8"/>
     </row>
-    <row r="307" spans="1:31" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:31" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A307" s="8">
         <v>1763</v>
       </c>
@@ -27704,7 +27706,7 @@
       <c r="AD307" s="8"/>
       <c r="AE307" s="8"/>
     </row>
-    <row r="308" spans="1:31" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:31" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A308" s="8">
         <v>1764</v>
       </c>
@@ -27775,7 +27777,7 @@
       <c r="AD308" s="8"/>
       <c r="AE308" s="8"/>
     </row>
-    <row r="309" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A309" s="8">
         <v>1767</v>
       </c>
@@ -27846,7 +27848,7 @@
       <c r="AD309" s="8"/>
       <c r="AE309" s="8"/>
     </row>
-    <row r="310" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A310" s="8">
         <v>1768</v>
       </c>
@@ -27917,7 +27919,7 @@
       <c r="AD310" s="8"/>
       <c r="AE310" s="8"/>
     </row>
-    <row r="311" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A311" s="8">
         <v>1769</v>
       </c>
@@ -27988,7 +27990,7 @@
       <c r="AD311" s="8"/>
       <c r="AE311" s="8"/>
     </row>
-    <row r="312" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A312" s="8">
         <v>1770</v>
       </c>
@@ -28059,7 +28061,7 @@
       <c r="AD312" s="8"/>
       <c r="AE312" s="8"/>
     </row>
-    <row r="313" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A313" s="8">
         <v>1771</v>
       </c>
@@ -28440,7 +28442,7 @@
       <c r="AD317" s="8"/>
       <c r="AE317" s="8"/>
     </row>
-    <row r="318" spans="1:31" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:31" ht="409.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A318" s="8">
         <v>1776</v>
       </c>
@@ -28511,7 +28513,7 @@
       <c r="AD318" s="8"/>
       <c r="AE318" s="8"/>
     </row>
-    <row r="319" spans="1:31" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:31" ht="409.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A319" s="8">
         <v>1777</v>
       </c>
@@ -28582,7 +28584,7 @@
       <c r="AD319" s="8"/>
       <c r="AE319" s="8"/>
     </row>
-    <row r="320" spans="1:31" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:31" ht="409.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A320" s="8">
         <v>1778</v>
       </c>
@@ -28653,7 +28655,7 @@
       <c r="AD320" s="8"/>
       <c r="AE320" s="8"/>
     </row>
-    <row r="321" spans="1:31" ht="230.4" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:31" ht="230.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A321" s="8">
         <v>1779</v>
       </c>
@@ -28724,7 +28726,7 @@
       <c r="AD321" s="8"/>
       <c r="AE321" s="8"/>
     </row>
-    <row r="322" spans="1:31" ht="230.4" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:31" ht="230.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A322" s="8">
         <v>1780</v>
       </c>
@@ -28793,7 +28795,7 @@
       <c r="AD322" s="8"/>
       <c r="AE322" s="8"/>
     </row>
-    <row r="323" spans="1:31" ht="230.4" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:31" ht="230.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A323" s="8">
         <v>1781</v>
       </c>
@@ -28862,7 +28864,7 @@
       <c r="AD323" s="8"/>
       <c r="AE323" s="8"/>
     </row>
-    <row r="324" spans="1:31" ht="230.4" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:31" ht="230.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A324" s="8">
         <v>1782</v>
       </c>
@@ -28929,7 +28931,7 @@
       <c r="AD324" s="8"/>
       <c r="AE324" s="8"/>
     </row>
-    <row r="325" spans="1:31" ht="302.39999999999998" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:31" ht="302.39999999999998" hidden="1" x14ac:dyDescent="0.3">
       <c r="A325" s="8">
         <v>1783</v>
       </c>
@@ -28998,7 +29000,7 @@
       <c r="AD325" s="8"/>
       <c r="AE325" s="8"/>
     </row>
-    <row r="326" spans="1:31" ht="302.39999999999998" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:31" ht="302.39999999999998" hidden="1" x14ac:dyDescent="0.3">
       <c r="A326" s="8">
         <v>1784</v>
       </c>
@@ -29065,7 +29067,7 @@
       <c r="AD326" s="8"/>
       <c r="AE326" s="8"/>
     </row>
-    <row r="327" spans="1:31" ht="302.39999999999998" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:31" ht="302.39999999999998" hidden="1" x14ac:dyDescent="0.3">
       <c r="A327" s="8">
         <v>1785</v>
       </c>
@@ -29132,7 +29134,7 @@
       <c r="AD327" s="8"/>
       <c r="AE327" s="8"/>
     </row>
-    <row r="328" spans="1:31" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:31" ht="409.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A328" s="8">
         <v>1792</v>
       </c>
@@ -29199,7 +29201,7 @@
       <c r="AD328" s="8"/>
       <c r="AE328" s="8"/>
     </row>
-    <row r="329" spans="1:31" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:31" ht="409.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A329" s="8">
         <v>1793</v>
       </c>
@@ -29266,7 +29268,7 @@
       <c r="AD329" s="8"/>
       <c r="AE329" s="8"/>
     </row>
-    <row r="330" spans="1:31" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:31" ht="409.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A330" s="8">
         <v>1794</v>
       </c>
@@ -29333,7 +29335,7 @@
       <c r="AD330" s="8"/>
       <c r="AE330" s="8"/>
     </row>
-    <row r="331" spans="1:31" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:31" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A331" s="8">
         <v>1795</v>
       </c>
@@ -29404,7 +29406,7 @@
       <c r="AD331" s="8"/>
       <c r="AE331" s="8"/>
     </row>
-    <row r="332" spans="1:31" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:31" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A332" s="8">
         <v>1796</v>
       </c>
@@ -29475,7 +29477,7 @@
       <c r="AD332" s="8"/>
       <c r="AE332" s="8"/>
     </row>
-    <row r="333" spans="1:31" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:31" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A333" s="8">
         <v>1797</v>
       </c>
@@ -29546,7 +29548,7 @@
       <c r="AD333" s="8"/>
       <c r="AE333" s="8"/>
     </row>
-    <row r="334" spans="1:31" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:31" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A334" s="8">
         <v>1798</v>
       </c>
@@ -29619,7 +29621,7 @@
       <c r="AD334" s="8"/>
       <c r="AE334" s="8"/>
     </row>
-    <row r="335" spans="1:31" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:31" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A335" s="8">
         <v>1799</v>
       </c>
@@ -29690,7 +29692,7 @@
       <c r="AD335" s="8"/>
       <c r="AE335" s="8"/>
     </row>
-    <row r="336" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A336" s="8">
         <v>1800</v>
       </c>
@@ -29759,7 +29761,7 @@
       <c r="AD336" s="8"/>
       <c r="AE336" s="8"/>
     </row>
-    <row r="337" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A337" s="8">
         <v>1801</v>
       </c>
@@ -29826,7 +29828,7 @@
       <c r="AD337" s="8"/>
       <c r="AE337" s="8"/>
     </row>
-    <row r="338" spans="1:31" ht="144" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:31" ht="144" hidden="1" x14ac:dyDescent="0.3">
       <c r="A338" s="8">
         <v>1811</v>
       </c>
@@ -29897,7 +29899,7 @@
       <c r="AD338" s="8"/>
       <c r="AE338" s="8"/>
     </row>
-    <row r="339" spans="1:31" ht="144" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:31" ht="144" hidden="1" x14ac:dyDescent="0.3">
       <c r="A339" s="8">
         <v>1812</v>
       </c>
@@ -29968,7 +29970,7 @@
       <c r="AD339" s="8"/>
       <c r="AE339" s="8"/>
     </row>
-    <row r="340" spans="1:31" ht="144" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:31" ht="144" hidden="1" x14ac:dyDescent="0.3">
       <c r="A340" s="8">
         <v>1813</v>
       </c>
@@ -30037,7 +30039,7 @@
       <c r="AD340" s="8"/>
       <c r="AE340" s="8"/>
     </row>
-    <row r="341" spans="1:31" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:31" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A341" s="8">
         <v>1814</v>
       </c>
@@ -30110,7 +30112,7 @@
       <c r="AD341" s="8"/>
       <c r="AE341" s="8"/>
     </row>
-    <row r="342" spans="1:31" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:31" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A342" s="8">
         <v>1815</v>
       </c>
@@ -30183,7 +30185,7 @@
       <c r="AD342" s="8"/>
       <c r="AE342" s="8"/>
     </row>
-    <row r="343" spans="1:31" ht="72" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:31" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A343" s="8">
         <v>1816</v>
       </c>
@@ -30256,7 +30258,7 @@
       <c r="AD343" s="8"/>
       <c r="AE343" s="8"/>
     </row>
-    <row r="344" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A344" s="8">
         <v>1817</v>
       </c>
@@ -30327,7 +30329,7 @@
       <c r="AD344" s="8"/>
       <c r="AE344" s="8"/>
     </row>
-    <row r="345" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A345" s="8">
         <v>1818</v>
       </c>
@@ -30400,7 +30402,7 @@
       <c r="AD345" s="8"/>
       <c r="AE345" s="8"/>
     </row>
-    <row r="346" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A346" s="8">
         <v>1819</v>
       </c>
@@ -30471,7 +30473,7 @@
       <c r="AD346" s="8"/>
       <c r="AE346" s="8"/>
     </row>
-    <row r="347" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A347" s="8">
         <v>1820</v>
       </c>
@@ -30542,7 +30544,7 @@
       <c r="AD347" s="8"/>
       <c r="AE347" s="8"/>
     </row>
-    <row r="348" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A348" s="8">
         <v>1821</v>
       </c>
@@ -30613,7 +30615,7 @@
       <c r="AD348" s="8"/>
       <c r="AE348" s="8"/>
     </row>
-    <row r="349" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A349" s="8">
         <v>1822</v>
       </c>
@@ -30686,7 +30688,7 @@
       <c r="AD349" s="8"/>
       <c r="AE349" s="8"/>
     </row>
-    <row r="350" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A350" s="8">
         <v>1823</v>
       </c>
@@ -30757,7 +30759,7 @@
       <c r="AD350" s="8"/>
       <c r="AE350" s="8"/>
     </row>
-    <row r="351" spans="1:31" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:31" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A351" s="8">
         <v>1824</v>
       </c>
@@ -30828,7 +30830,7 @@
       <c r="AD351" s="8"/>
       <c r="AE351" s="8"/>
     </row>
-    <row r="352" spans="1:31" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:31" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A352" s="8">
         <v>1825</v>
       </c>
@@ -30901,7 +30903,7 @@
       <c r="AD352" s="8"/>
       <c r="AE352" s="8"/>
     </row>
-    <row r="353" spans="1:31" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:31" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A353" s="8">
         <v>1826</v>
       </c>
@@ -30972,7 +30974,7 @@
       <c r="AD353" s="8"/>
       <c r="AE353" s="8"/>
     </row>
-    <row r="354" spans="1:31" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:31" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A354" s="8">
         <v>1827</v>
       </c>
@@ -31041,7 +31043,7 @@
       <c r="AD354" s="8"/>
       <c r="AE354" s="8"/>
     </row>
-    <row r="355" spans="1:31" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:31" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A355" s="8">
         <v>1828</v>
       </c>
@@ -31110,7 +31112,7 @@
       <c r="AD355" s="8"/>
       <c r="AE355" s="8"/>
     </row>
-    <row r="356" spans="1:31" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:31" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A356" s="8">
         <v>1829</v>
       </c>
@@ -31179,7 +31181,7 @@
       <c r="AD356" s="8"/>
       <c r="AE356" s="8"/>
     </row>
-    <row r="357" spans="1:31" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:31" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A357" s="8">
         <v>1830</v>
       </c>
@@ -31248,7 +31250,7 @@
       <c r="AD357" s="8"/>
       <c r="AE357" s="8"/>
     </row>
-    <row r="358" spans="1:31" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:31" ht="115.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A358" s="8">
         <v>1831</v>
       </c>
@@ -31319,7 +31321,7 @@
       <c r="AD358" s="8"/>
       <c r="AE358" s="8"/>
     </row>
-    <row r="359" spans="1:31" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:31" ht="115.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A359" s="8">
         <v>1832</v>
       </c>
@@ -31390,7 +31392,7 @@
       <c r="AD359" s="8"/>
       <c r="AE359" s="8"/>
     </row>
-    <row r="360" spans="1:31" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:31" ht="115.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A360" s="8">
         <v>1833</v>
       </c>
@@ -31461,7 +31463,7 @@
       <c r="AD360" s="8"/>
       <c r="AE360" s="8"/>
     </row>
-    <row r="361" spans="1:31" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:31" ht="115.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A361" s="8">
         <v>1834</v>
       </c>
@@ -31532,7 +31534,7 @@
       <c r="AD361" s="8"/>
       <c r="AE361" s="8"/>
     </row>
-    <row r="362" spans="1:31" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:31" ht="115.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A362" s="8">
         <v>1835</v>
       </c>
@@ -31603,7 +31605,7 @@
       <c r="AD362" s="8"/>
       <c r="AE362" s="8"/>
     </row>
-    <row r="363" spans="1:31" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:31" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A363" s="8">
         <v>1836</v>
       </c>
@@ -31674,7 +31676,7 @@
       <c r="AD363" s="8"/>
       <c r="AE363" s="8"/>
     </row>
-    <row r="364" spans="1:31" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:31" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A364" s="8">
         <v>1837</v>
       </c>
@@ -31745,7 +31747,7 @@
       <c r="AD364" s="8"/>
       <c r="AE364" s="8"/>
     </row>
-    <row r="365" spans="1:31" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:31" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A365" s="8">
         <v>1838</v>
       </c>
@@ -31816,7 +31818,7 @@
       <c r="AD365" s="8"/>
       <c r="AE365" s="8"/>
     </row>
-    <row r="366" spans="1:31" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:31" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A366" s="8">
         <v>1839</v>
       </c>
@@ -31887,7 +31889,7 @@
       <c r="AD366" s="8"/>
       <c r="AE366" s="8"/>
     </row>
-    <row r="367" spans="1:31" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:31" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A367" s="8">
         <v>1840</v>
       </c>
@@ -31958,7 +31960,7 @@
       <c r="AD367" s="8"/>
       <c r="AE367" s="8"/>
     </row>
-    <row r="368" spans="1:31" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:31" ht="115.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A368" s="8">
         <v>1841</v>
       </c>
@@ -32031,7 +32033,7 @@
       <c r="AD368" s="8"/>
       <c r="AE368" s="8"/>
     </row>
-    <row r="369" spans="1:31" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:31" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A369" s="8">
         <v>1842</v>
       </c>
@@ -32100,7 +32102,7 @@
       <c r="AD369" s="8"/>
       <c r="AE369" s="8"/>
     </row>
-    <row r="370" spans="1:31" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:31" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A370" s="8">
         <v>1843</v>
       </c>
@@ -32171,7 +32173,7 @@
       <c r="AD370" s="8"/>
       <c r="AE370" s="8"/>
     </row>
-    <row r="371" spans="1:31" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:31" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A371" s="8">
         <v>1844</v>
       </c>
@@ -32240,7 +32242,7 @@
       <c r="AD371" s="8"/>
       <c r="AE371" s="8"/>
     </row>
-    <row r="372" spans="1:31" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:31" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A372" s="8">
         <v>1845</v>
       </c>
@@ -32309,7 +32311,7 @@
       <c r="AD372" s="8"/>
       <c r="AE372" s="8"/>
     </row>
-    <row r="373" spans="1:31" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:31" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A373" s="8">
         <v>1846</v>
       </c>
@@ -32378,7 +32380,7 @@
       <c r="AD373" s="8"/>
       <c r="AE373" s="8"/>
     </row>
-    <row r="374" spans="1:31" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:31" ht="115.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A374" s="8">
         <v>1847</v>
       </c>
@@ -32451,7 +32453,7 @@
       <c r="AD374" s="8"/>
       <c r="AE374" s="8"/>
     </row>
-    <row r="375" spans="1:31" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:31" ht="115.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A375" s="8">
         <v>1848</v>
       </c>
@@ -32524,7 +32526,7 @@
       <c r="AD375" s="8"/>
       <c r="AE375" s="8"/>
     </row>
-    <row r="376" spans="1:31" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:31" ht="115.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A376" s="8">
         <v>1849</v>
       </c>
@@ -32593,7 +32595,7 @@
       <c r="AD376" s="8"/>
       <c r="AE376" s="8"/>
     </row>
-    <row r="377" spans="1:31" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:31" ht="115.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A377" s="8">
         <v>1850</v>
       </c>
@@ -32666,7 +32668,7 @@
       <c r="AD377" s="8"/>
       <c r="AE377" s="8"/>
     </row>
-    <row r="378" spans="1:31" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:31" ht="115.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A378" s="8">
         <v>1851</v>
       </c>
@@ -32735,7 +32737,7 @@
       <c r="AD378" s="8"/>
       <c r="AE378" s="8"/>
     </row>
-    <row r="379" spans="1:31" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:31" ht="115.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A379" s="8">
         <v>1852</v>
       </c>
@@ -32810,7 +32812,7 @@
       <c r="AD379" s="8"/>
       <c r="AE379" s="8"/>
     </row>
-    <row r="380" spans="1:31" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:31" ht="115.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A380" s="8">
         <v>1853</v>
       </c>
@@ -32881,7 +32883,7 @@
       <c r="AD380" s="8"/>
       <c r="AE380" s="8"/>
     </row>
-    <row r="381" spans="1:31" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:31" ht="115.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A381" s="8">
         <v>1854</v>
       </c>
@@ -32950,7 +32952,7 @@
       <c r="AD381" s="8"/>
       <c r="AE381" s="8"/>
     </row>
-    <row r="382" spans="1:31" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:31" ht="115.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A382" s="8">
         <v>1855</v>
       </c>
@@ -33019,7 +33021,7 @@
       <c r="AD382" s="8"/>
       <c r="AE382" s="8"/>
     </row>
-    <row r="383" spans="1:31" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:31" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A383" s="8">
         <v>1856</v>
       </c>
@@ -33090,7 +33092,7 @@
       <c r="AD383" s="8"/>
       <c r="AE383" s="8"/>
     </row>
-    <row r="384" spans="1:31" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:31" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A384" s="8">
         <v>1857</v>
       </c>
@@ -33163,7 +33165,7 @@
       <c r="AD384" s="8"/>
       <c r="AE384" s="8"/>
     </row>
-    <row r="385" spans="1:31" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:31" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A385" s="8">
         <v>1858</v>
       </c>
@@ -33236,7 +33238,7 @@
       <c r="AD385" s="8"/>
       <c r="AE385" s="8"/>
     </row>
-    <row r="386" spans="1:31" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:31" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A386" s="8">
         <v>1859</v>
       </c>
@@ -33307,7 +33309,7 @@
       <c r="AD386" s="8"/>
       <c r="AE386" s="8"/>
     </row>
-    <row r="387" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A387" s="8">
         <v>1860</v>
       </c>
@@ -33378,7 +33380,7 @@
       <c r="AD387" s="8"/>
       <c r="AE387" s="8"/>
     </row>
-    <row r="388" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A388" s="8">
         <v>1862</v>
       </c>
@@ -33445,7 +33447,7 @@
       <c r="AD388" s="8"/>
       <c r="AE388" s="8"/>
     </row>
-    <row r="389" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A389" s="8">
         <v>1863</v>
       </c>
@@ -33512,7 +33514,7 @@
       <c r="AD389" s="8"/>
       <c r="AE389" s="8"/>
     </row>
-    <row r="390" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A390" s="8">
         <v>1864</v>
       </c>
@@ -33579,7 +33581,7 @@
       <c r="AD390" s="8"/>
       <c r="AE390" s="8"/>
     </row>
-    <row r="391" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A391" s="8">
         <v>1866</v>
       </c>
@@ -33650,7 +33652,7 @@
       <c r="AD391" s="8"/>
       <c r="AE391" s="8"/>
     </row>
-    <row r="392" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A392" s="8">
         <v>1867</v>
       </c>
@@ -33721,7 +33723,7 @@
       <c r="AD392" s="8"/>
       <c r="AE392" s="8"/>
     </row>
-    <row r="393" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A393" s="8">
         <v>1868</v>
       </c>
@@ -33792,7 +33794,7 @@
       <c r="AD393" s="8"/>
       <c r="AE393" s="8"/>
     </row>
-    <row r="394" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A394" s="8">
         <v>1869</v>
       </c>
@@ -33859,7 +33861,7 @@
       <c r="AD394" s="8"/>
       <c r="AE394" s="8"/>
     </row>
-    <row r="395" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A395" s="8">
         <v>1870</v>
       </c>
@@ -33926,7 +33928,7 @@
       <c r="AD395" s="8"/>
       <c r="AE395" s="8"/>
     </row>
-    <row r="396" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A396" s="8">
         <v>1872</v>
       </c>
@@ -33997,7 +33999,7 @@
       <c r="AD396" s="8"/>
       <c r="AE396" s="8"/>
     </row>
-    <row r="397" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A397" s="8">
         <v>1873</v>
       </c>
@@ -34068,7 +34070,7 @@
       <c r="AD397" s="8"/>
       <c r="AE397" s="8"/>
     </row>
-    <row r="398" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A398" s="8">
         <v>1874</v>
       </c>
@@ -34135,7 +34137,7 @@
       <c r="AD398" s="8"/>
       <c r="AE398" s="8"/>
     </row>
-    <row r="399" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A399" s="8">
         <v>1875</v>
       </c>
@@ -34202,7 +34204,7 @@
       <c r="AD399" s="8"/>
       <c r="AE399" s="8"/>
     </row>
-    <row r="400" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A400" s="8">
         <v>1876</v>
       </c>
@@ -34269,7 +34271,7 @@
       <c r="AD400" s="8"/>
       <c r="AE400" s="8"/>
     </row>
-    <row r="401" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A401" s="8">
         <v>1877</v>
       </c>
@@ -34336,7 +34338,7 @@
       <c r="AD401" s="8"/>
       <c r="AE401" s="8"/>
     </row>
-    <row r="402" spans="1:31" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:31" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A402" s="8">
         <v>1878</v>
       </c>
@@ -34407,7 +34409,7 @@
       <c r="AD402" s="8"/>
       <c r="AE402" s="8"/>
     </row>
-    <row r="403" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A403" s="8">
         <v>1879</v>
       </c>
@@ -34478,7 +34480,7 @@
       <c r="AD403" s="8"/>
       <c r="AE403" s="8"/>
     </row>
-    <row r="404" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A404" s="8">
         <v>1880</v>
       </c>
@@ -34545,7 +34547,7 @@
       <c r="AD404" s="8"/>
       <c r="AE404" s="8"/>
     </row>
-    <row r="405" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A405" s="8">
         <v>1881</v>
       </c>
@@ -34612,7 +34614,7 @@
       <c r="AD405" s="8"/>
       <c r="AE405" s="8"/>
     </row>
-    <row r="406" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A406" s="8">
         <v>1882</v>
       </c>
@@ -34679,7 +34681,7 @@
       <c r="AD406" s="8"/>
       <c r="AE406" s="8"/>
     </row>
-    <row r="407" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A407" s="8">
         <v>1883</v>
       </c>
@@ -34746,7 +34748,7 @@
       <c r="AD407" s="8"/>
       <c r="AE407" s="8"/>
     </row>
-    <row r="408" spans="1:31" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:31" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A408" s="8">
         <v>1885</v>
       </c>
@@ -34815,7 +34817,7 @@
       <c r="AD408" s="8"/>
       <c r="AE408" s="8"/>
     </row>
-    <row r="409" spans="1:31" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:31" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A409" s="8">
         <v>1886</v>
       </c>
@@ -34884,7 +34886,7 @@
       <c r="AD409" s="8"/>
       <c r="AE409" s="8"/>
     </row>
-    <row r="410" spans="1:31" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:31" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A410" s="8">
         <v>1887</v>
       </c>
@@ -34953,7 +34955,7 @@
       <c r="AD410" s="8"/>
       <c r="AE410" s="8"/>
     </row>
-    <row r="411" spans="1:31" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:31" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A411" s="8">
         <v>1888</v>
       </c>
@@ -35022,7 +35024,7 @@
       <c r="AD411" s="8"/>
       <c r="AE411" s="8"/>
     </row>
-    <row r="412" spans="1:31" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:31" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A412" s="8">
         <v>1889</v>
       </c>
@@ -35089,7 +35091,7 @@
       <c r="AD412" s="8"/>
       <c r="AE412" s="8"/>
     </row>
-    <row r="413" spans="1:31" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:31" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A413" s="8">
         <v>1890</v>
       </c>
@@ -35158,7 +35160,7 @@
       <c r="AD413" s="8"/>
       <c r="AE413" s="8"/>
     </row>
-    <row r="414" spans="1:31" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:31" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A414" s="8">
         <v>1891</v>
       </c>
@@ -35227,7 +35229,7 @@
       <c r="AD414" s="8"/>
       <c r="AE414" s="8"/>
     </row>
-    <row r="415" spans="1:31" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:31" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A415" s="8">
         <v>1892</v>
       </c>
@@ -35296,7 +35298,7 @@
       <c r="AD415" s="8"/>
       <c r="AE415" s="8"/>
     </row>
-    <row r="416" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A416" s="8">
         <v>1893</v>
       </c>
@@ -35365,7 +35367,7 @@
       <c r="AD416" s="8"/>
       <c r="AE416" s="8"/>
     </row>
-    <row r="417" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A417" s="8">
         <v>1894</v>
       </c>
@@ -35432,7 +35434,7 @@
       <c r="AD417" s="8"/>
       <c r="AE417" s="8"/>
     </row>
-    <row r="418" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A418" s="8">
         <v>1895</v>
       </c>
@@ -35499,7 +35501,7 @@
       <c r="AD418" s="8"/>
       <c r="AE418" s="8"/>
     </row>
-    <row r="419" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A419" s="8">
         <v>1896</v>
       </c>
@@ -35566,7 +35568,7 @@
       <c r="AD419" s="8"/>
       <c r="AE419" s="8"/>
     </row>
-    <row r="420" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A420" s="8">
         <v>1897</v>
       </c>
@@ -35635,7 +35637,7 @@
       <c r="AD420" s="8"/>
       <c r="AE420" s="8"/>
     </row>
-    <row r="421" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A421" s="8">
         <v>1898</v>
       </c>
@@ -35704,7 +35706,7 @@
       <c r="AD421" s="8"/>
       <c r="AE421" s="8"/>
     </row>
-    <row r="422" spans="1:31" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:31" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A422" s="3">
         <v>1899</v>
       </c>
@@ -35775,6 +35777,13 @@
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
+  <autoFilter ref="A1:AE422" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="8">
+      <filters>
+        <filter val="440"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/raw/Plan de accion/PA_2.xlsx
+++ b/data/raw/Plan de accion/PA_2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Sistema_Indicadores_Poli/data/raw/Plan de accion/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="11_C4BD844F18F46918874719FA9983E268DB8A1E7B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{33C0FF22-37E5-4990-BFEE-D6ED30F7E378}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="11_C4BD844F18F46918874719FA9983E268DB8A1E7B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{471E88A8-90D8-4FFE-ADC2-FB91EFC45FAC}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3965,7 +3965,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -4014,6 +4014,9 @@
     </xf>
     <xf numFmtId="10" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4323,7 +4326,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:AE422"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -4336,7 +4338,7 @@
     <col min="7" max="8" width="50" style="1" customWidth="1"/>
     <col min="9" max="9" width="29" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="1655" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="700" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="98.88671875" style="1" customWidth="1"/>
     <col min="12" max="12" width="71" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="42" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="30" bestFit="1" customWidth="1"/>
@@ -4390,7 +4392,7 @@
       <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="17" t="s">
         <v>10</v>
       </c>
       <c r="L1" s="2" t="s">
@@ -4454,7 +4456,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:31" ht="187.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:31" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A2" s="8">
         <v>1141</v>
       </c>
@@ -4533,7 +4535,7 @@
       <c r="AD2" s="8"/>
       <c r="AE2" s="8"/>
     </row>
-    <row r="3" spans="1:31" ht="72" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:31" ht="72" x14ac:dyDescent="0.3">
       <c r="A3" s="8">
         <v>1142</v>
       </c>
@@ -4612,7 +4614,7 @@
       <c r="AD3" s="8"/>
       <c r="AE3" s="8"/>
     </row>
-    <row r="4" spans="1:31" ht="115.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:31" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A4" s="8">
         <v>1244</v>
       </c>
@@ -4691,7 +4693,7 @@
       <c r="AD4" s="8"/>
       <c r="AE4" s="8"/>
     </row>
-    <row r="5" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="8">
         <v>1280</v>
       </c>
@@ -4770,7 +4772,7 @@
       <c r="AD5" s="8"/>
       <c r="AE5" s="8"/>
     </row>
-    <row r="6" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="8">
         <v>1285</v>
       </c>
@@ -4841,7 +4843,7 @@
       <c r="AD6" s="8"/>
       <c r="AE6" s="8"/>
     </row>
-    <row r="7" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="8">
         <v>1292</v>
       </c>
@@ -4910,7 +4912,7 @@
       <c r="AD7" s="8"/>
       <c r="AE7" s="8"/>
     </row>
-    <row r="8" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="8">
         <v>1293</v>
       </c>
@@ -4979,7 +4981,7 @@
       <c r="AD8" s="8"/>
       <c r="AE8" s="8"/>
     </row>
-    <row r="9" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="8">
         <v>1294</v>
       </c>
@@ -5048,7 +5050,7 @@
       <c r="AD9" s="8"/>
       <c r="AE9" s="8"/>
     </row>
-    <row r="10" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="8">
         <v>1295</v>
       </c>
@@ -5117,7 +5119,7 @@
       <c r="AD10" s="8"/>
       <c r="AE10" s="8"/>
     </row>
-    <row r="11" spans="1:31" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:31" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A11" s="8">
         <v>1308</v>
       </c>
@@ -5194,7 +5196,7 @@
       <c r="AD11" s="8"/>
       <c r="AE11" s="8"/>
     </row>
-    <row r="12" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="8">
         <v>1328</v>
       </c>
@@ -5273,7 +5275,7 @@
       <c r="AD12" s="8"/>
       <c r="AE12" s="8"/>
     </row>
-    <row r="13" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="8">
         <v>1332</v>
       </c>
@@ -5340,7 +5342,7 @@
       <c r="AD13" s="8"/>
       <c r="AE13" s="8"/>
     </row>
-    <row r="14" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A14" s="8">
         <v>1333</v>
       </c>
@@ -5407,7 +5409,7 @@
       <c r="AD14" s="8"/>
       <c r="AE14" s="8"/>
     </row>
-    <row r="15" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A15" s="8">
         <v>1334</v>
       </c>
@@ -5474,7 +5476,7 @@
       <c r="AD15" s="8"/>
       <c r="AE15" s="8"/>
     </row>
-    <row r="16" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A16" s="8">
         <v>1335</v>
       </c>
@@ -5541,7 +5543,7 @@
       <c r="AD16" s="8"/>
       <c r="AE16" s="8"/>
     </row>
-    <row r="17" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A17" s="8">
         <v>1336</v>
       </c>
@@ -5614,7 +5616,7 @@
       <c r="AD17" s="8"/>
       <c r="AE17" s="8"/>
     </row>
-    <row r="18" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A18" s="8">
         <v>1337</v>
       </c>
@@ -5685,7 +5687,7 @@
       <c r="AD18" s="8"/>
       <c r="AE18" s="8"/>
     </row>
-    <row r="19" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A19" s="8">
         <v>1338</v>
       </c>
@@ -5756,7 +5758,7 @@
       <c r="AD19" s="8"/>
       <c r="AE19" s="8"/>
     </row>
-    <row r="20" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A20" s="8">
         <v>1339</v>
       </c>
@@ -5835,7 +5837,7 @@
       <c r="AD20" s="8"/>
       <c r="AE20" s="8"/>
     </row>
-    <row r="21" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A21" s="8">
         <v>1340</v>
       </c>
@@ -5914,7 +5916,7 @@
       <c r="AD21" s="8"/>
       <c r="AE21" s="8"/>
     </row>
-    <row r="22" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A22" s="8">
         <v>1341</v>
       </c>
@@ -5993,7 +5995,7 @@
       <c r="AD22" s="8"/>
       <c r="AE22" s="8"/>
     </row>
-    <row r="23" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A23" s="8">
         <v>1342</v>
       </c>
@@ -6072,7 +6074,7 @@
       <c r="AD23" s="8"/>
       <c r="AE23" s="8"/>
     </row>
-    <row r="24" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A24" s="8">
         <v>1343</v>
       </c>
@@ -6151,7 +6153,7 @@
       <c r="AD24" s="8"/>
       <c r="AE24" s="8"/>
     </row>
-    <row r="25" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A25" s="8">
         <v>1344</v>
       </c>
@@ -6230,7 +6232,7 @@
       <c r="AD25" s="8"/>
       <c r="AE25" s="8"/>
     </row>
-    <row r="26" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A26" s="8">
         <v>1345</v>
       </c>
@@ -6309,7 +6311,7 @@
       <c r="AD26" s="8"/>
       <c r="AE26" s="8"/>
     </row>
-    <row r="27" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A27" s="8">
         <v>1346</v>
       </c>
@@ -6388,7 +6390,7 @@
       <c r="AD27" s="8"/>
       <c r="AE27" s="8"/>
     </row>
-    <row r="28" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A28" s="8">
         <v>1347</v>
       </c>
@@ -6467,7 +6469,7 @@
       <c r="AD28" s="8"/>
       <c r="AE28" s="8"/>
     </row>
-    <row r="29" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A29" s="8">
         <v>1348</v>
       </c>
@@ -6546,7 +6548,7 @@
       <c r="AD29" s="8"/>
       <c r="AE29" s="8"/>
     </row>
-    <row r="30" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A30" s="8">
         <v>1349</v>
       </c>
@@ -6625,7 +6627,7 @@
       <c r="AD30" s="8"/>
       <c r="AE30" s="8"/>
     </row>
-    <row r="31" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A31" s="8">
         <v>1350</v>
       </c>
@@ -6704,7 +6706,7 @@
       <c r="AD31" s="8"/>
       <c r="AE31" s="8"/>
     </row>
-    <row r="32" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A32" s="8">
         <v>1351</v>
       </c>
@@ -6783,7 +6785,7 @@
       <c r="AD32" s="8"/>
       <c r="AE32" s="8"/>
     </row>
-    <row r="33" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A33" s="8">
         <v>1353</v>
       </c>
@@ -6862,7 +6864,7 @@
       <c r="AD33" s="8"/>
       <c r="AE33" s="8"/>
     </row>
-    <row r="34" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A34" s="8">
         <v>1354</v>
       </c>
@@ -6941,7 +6943,7 @@
       <c r="AD34" s="8"/>
       <c r="AE34" s="8"/>
     </row>
-    <row r="35" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A35" s="8">
         <v>1355</v>
       </c>
@@ -7020,7 +7022,7 @@
       <c r="AD35" s="8"/>
       <c r="AE35" s="8"/>
     </row>
-    <row r="36" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A36" s="8">
         <v>1356</v>
       </c>
@@ -7099,7 +7101,7 @@
       <c r="AD36" s="8"/>
       <c r="AE36" s="8"/>
     </row>
-    <row r="37" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A37" s="8">
         <v>1357</v>
       </c>
@@ -7178,7 +7180,7 @@
       <c r="AD37" s="8"/>
       <c r="AE37" s="8"/>
     </row>
-    <row r="38" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A38" s="8">
         <v>1358</v>
       </c>
@@ -7257,7 +7259,7 @@
       <c r="AD38" s="8"/>
       <c r="AE38" s="8"/>
     </row>
-    <row r="39" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A39" s="8">
         <v>1359</v>
       </c>
@@ -7336,7 +7338,7 @@
       <c r="AD39" s="8"/>
       <c r="AE39" s="8"/>
     </row>
-    <row r="40" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A40" s="8">
         <v>1360</v>
       </c>
@@ -7415,7 +7417,7 @@
       <c r="AD40" s="8"/>
       <c r="AE40" s="8"/>
     </row>
-    <row r="41" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A41" s="8">
         <v>1361</v>
       </c>
@@ -7494,7 +7496,7 @@
       <c r="AD41" s="8"/>
       <c r="AE41" s="8"/>
     </row>
-    <row r="42" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A42" s="8">
         <v>1362</v>
       </c>
@@ -7573,7 +7575,7 @@
       <c r="AD42" s="8"/>
       <c r="AE42" s="8"/>
     </row>
-    <row r="43" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A43" s="8">
         <v>1363</v>
       </c>
@@ -7654,7 +7656,7 @@
       <c r="AD43" s="8"/>
       <c r="AE43" s="8"/>
     </row>
-    <row r="44" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A44" s="8">
         <v>1364</v>
       </c>
@@ -7733,7 +7735,7 @@
       <c r="AD44" s="8"/>
       <c r="AE44" s="8"/>
     </row>
-    <row r="45" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A45" s="8">
         <v>1365</v>
       </c>
@@ -7812,7 +7814,7 @@
       <c r="AD45" s="8"/>
       <c r="AE45" s="8"/>
     </row>
-    <row r="46" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A46" s="8">
         <v>1366</v>
       </c>
@@ -7893,7 +7895,7 @@
       <c r="AD46" s="8"/>
       <c r="AE46" s="8"/>
     </row>
-    <row r="47" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A47" s="8">
         <v>1367</v>
       </c>
@@ -7974,7 +7976,7 @@
       <c r="AD47" s="8"/>
       <c r="AE47" s="8"/>
     </row>
-    <row r="48" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A48" s="8">
         <v>1371</v>
       </c>
@@ -8053,7 +8055,7 @@
       <c r="AD48" s="8"/>
       <c r="AE48" s="8"/>
     </row>
-    <row r="49" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A49" s="8">
         <v>1375</v>
       </c>
@@ -8132,7 +8134,7 @@
       <c r="AD49" s="8"/>
       <c r="AE49" s="8"/>
     </row>
-    <row r="50" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A50" s="8">
         <v>1377</v>
       </c>
@@ -8211,7 +8213,7 @@
       <c r="AD50" s="8"/>
       <c r="AE50" s="8"/>
     </row>
-    <row r="51" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A51" s="8">
         <v>1378</v>
       </c>
@@ -8290,7 +8292,7 @@
       <c r="AD51" s="8"/>
       <c r="AE51" s="8"/>
     </row>
-    <row r="52" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A52" s="8">
         <v>1379</v>
       </c>
@@ -8367,7 +8369,7 @@
       <c r="AD52" s="8"/>
       <c r="AE52" s="8"/>
     </row>
-    <row r="53" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A53" s="8">
         <v>1382</v>
       </c>
@@ -8446,7 +8448,7 @@
       <c r="AD53" s="8"/>
       <c r="AE53" s="8"/>
     </row>
-    <row r="54" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A54" s="8">
         <v>1383</v>
       </c>
@@ -8525,7 +8527,7 @@
       <c r="AD54" s="8"/>
       <c r="AE54" s="8"/>
     </row>
-    <row r="55" spans="1:31" ht="115.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:31" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A55" s="8">
         <v>1395</v>
       </c>
@@ -8598,7 +8600,7 @@
       <c r="AD55" s="8"/>
       <c r="AE55" s="8"/>
     </row>
-    <row r="56" spans="1:31" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:31" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A56" s="8">
         <v>1401</v>
       </c>
@@ -8671,7 +8673,7 @@
       <c r="AD56" s="8"/>
       <c r="AE56" s="8"/>
     </row>
-    <row r="57" spans="1:31" ht="72" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:31" ht="72" x14ac:dyDescent="0.3">
       <c r="A57" s="8">
         <v>1405</v>
       </c>
@@ -8742,7 +8744,7 @@
       <c r="AD57" s="8"/>
       <c r="AE57" s="8"/>
     </row>
-    <row r="58" spans="1:31" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:31" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A58" s="8">
         <v>1406</v>
       </c>
@@ -8815,7 +8817,7 @@
       <c r="AD58" s="8"/>
       <c r="AE58" s="8"/>
     </row>
-    <row r="59" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A59" s="8">
         <v>1413</v>
       </c>
@@ -8896,7 +8898,7 @@
       <c r="AD59" s="8"/>
       <c r="AE59" s="8"/>
     </row>
-    <row r="60" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A60" s="8">
         <v>1415</v>
       </c>
@@ -8977,7 +8979,7 @@
       <c r="AD60" s="8"/>
       <c r="AE60" s="8"/>
     </row>
-    <row r="61" spans="1:31" ht="115.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:31" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A61" s="8">
         <v>1433</v>
       </c>
@@ -9056,7 +9058,7 @@
       <c r="AD61" s="8"/>
       <c r="AE61" s="8"/>
     </row>
-    <row r="62" spans="1:31" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:31" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A62" s="8">
         <v>1435</v>
       </c>
@@ -9131,7 +9133,7 @@
       <c r="AD62" s="8"/>
       <c r="AE62" s="8"/>
     </row>
-    <row r="63" spans="1:31" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:31" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A63" s="8">
         <v>1436</v>
       </c>
@@ -9206,7 +9208,7 @@
       <c r="AD63" s="8"/>
       <c r="AE63" s="8"/>
     </row>
-    <row r="64" spans="1:31" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:31" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A64" s="8">
         <v>1437</v>
       </c>
@@ -9281,7 +9283,7 @@
       <c r="AD64" s="8"/>
       <c r="AE64" s="8"/>
     </row>
-    <row r="65" spans="1:31" ht="115.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:31" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A65" s="8">
         <v>1438</v>
       </c>
@@ -9360,7 +9362,7 @@
       <c r="AD65" s="8"/>
       <c r="AE65" s="8"/>
     </row>
-    <row r="66" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A66" s="8">
         <v>1441</v>
       </c>
@@ -9433,7 +9435,7 @@
       <c r="AD66" s="8"/>
       <c r="AE66" s="8"/>
     </row>
-    <row r="67" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A67" s="8">
         <v>1442</v>
       </c>
@@ -9506,7 +9508,7 @@
       <c r="AD67" s="8"/>
       <c r="AE67" s="8"/>
     </row>
-    <row r="68" spans="1:31" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:31" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A68" s="8">
         <v>1445</v>
       </c>
@@ -9581,7 +9583,7 @@
       <c r="AD68" s="8"/>
       <c r="AE68" s="8"/>
     </row>
-    <row r="69" spans="1:31" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:31" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A69" s="8">
         <v>1446</v>
       </c>
@@ -9656,7 +9658,7 @@
       <c r="AD69" s="8"/>
       <c r="AE69" s="8"/>
     </row>
-    <row r="70" spans="1:31" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:31" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A70" s="8">
         <v>1447</v>
       </c>
@@ -9731,7 +9733,7 @@
       <c r="AD70" s="8"/>
       <c r="AE70" s="8"/>
     </row>
-    <row r="71" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A71" s="8">
         <v>1468</v>
       </c>
@@ -9800,7 +9802,7 @@
       <c r="AD71" s="8"/>
       <c r="AE71" s="8"/>
     </row>
-    <row r="72" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A72" s="8">
         <v>1469</v>
       </c>
@@ -9869,7 +9871,7 @@
       <c r="AD72" s="8"/>
       <c r="AE72" s="8"/>
     </row>
-    <row r="73" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A73" s="8">
         <v>1470</v>
       </c>
@@ -9938,7 +9940,7 @@
       <c r="AD73" s="8"/>
       <c r="AE73" s="8"/>
     </row>
-    <row r="74" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A74" s="8">
         <v>1471</v>
       </c>
@@ -10007,7 +10009,7 @@
       <c r="AD74" s="8"/>
       <c r="AE74" s="8"/>
     </row>
-    <row r="75" spans="1:31" ht="201.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:31" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A75" s="8">
         <v>1476</v>
       </c>
@@ -10078,7 +10080,7 @@
       <c r="AD75" s="8"/>
       <c r="AE75" s="8"/>
     </row>
-    <row r="76" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A76" s="8">
         <v>1478</v>
       </c>
@@ -10157,7 +10159,7 @@
       <c r="AD76" s="8"/>
       <c r="AE76" s="8"/>
     </row>
-    <row r="77" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A77" s="8">
         <v>1479</v>
       </c>
@@ -10236,7 +10238,7 @@
       <c r="AD77" s="8"/>
       <c r="AE77" s="8"/>
     </row>
-    <row r="78" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A78" s="8">
         <v>1480</v>
       </c>
@@ -10315,7 +10317,7 @@
       <c r="AD78" s="8"/>
       <c r="AE78" s="8"/>
     </row>
-    <row r="79" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A79" s="8">
         <v>1481</v>
       </c>
@@ -10394,7 +10396,7 @@
       <c r="AD79" s="8"/>
       <c r="AE79" s="8"/>
     </row>
-    <row r="80" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A80" s="8">
         <v>1482</v>
       </c>
@@ -10475,7 +10477,7 @@
       <c r="AD80" s="8"/>
       <c r="AE80" s="8"/>
     </row>
-    <row r="81" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A81" s="8">
         <v>1483</v>
       </c>
@@ -10556,7 +10558,7 @@
       <c r="AD81" s="8"/>
       <c r="AE81" s="8"/>
     </row>
-    <row r="82" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A82" s="8">
         <v>1484</v>
       </c>
@@ -10637,7 +10639,7 @@
       <c r="AD82" s="8"/>
       <c r="AE82" s="8"/>
     </row>
-    <row r="83" spans="1:31" ht="409.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:31" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A83" s="8">
         <v>1485</v>
       </c>
@@ -10716,7 +10718,7 @@
       <c r="AD83" s="8"/>
       <c r="AE83" s="8"/>
     </row>
-    <row r="84" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A84" s="8">
         <v>1487</v>
       </c>
@@ -10783,7 +10785,7 @@
       <c r="AD84" s="8"/>
       <c r="AE84" s="8"/>
     </row>
-    <row r="85" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A85" s="8">
         <v>1489</v>
       </c>
@@ -10850,7 +10852,7 @@
       <c r="AD85" s="8"/>
       <c r="AE85" s="8"/>
     </row>
-    <row r="86" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A86" s="8">
         <v>1490</v>
       </c>
@@ -10929,7 +10931,7 @@
       <c r="AD86" s="8"/>
       <c r="AE86" s="8"/>
     </row>
-    <row r="87" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A87" s="8">
         <v>1491</v>
       </c>
@@ -11008,7 +11010,7 @@
       <c r="AD87" s="8"/>
       <c r="AE87" s="8"/>
     </row>
-    <row r="88" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A88" s="8">
         <v>1492</v>
       </c>
@@ -11087,7 +11089,7 @@
       <c r="AD88" s="8"/>
       <c r="AE88" s="8"/>
     </row>
-    <row r="89" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A89" s="8">
         <v>1493</v>
       </c>
@@ -11166,7 +11168,7 @@
       <c r="AD89" s="8"/>
       <c r="AE89" s="8"/>
     </row>
-    <row r="90" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A90" s="8">
         <v>1494</v>
       </c>
@@ -11245,7 +11247,7 @@
       <c r="AD90" s="8"/>
       <c r="AE90" s="8"/>
     </row>
-    <row r="91" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A91" s="8">
         <v>1495</v>
       </c>
@@ -11324,7 +11326,7 @@
       <c r="AD91" s="8"/>
       <c r="AE91" s="8"/>
     </row>
-    <row r="92" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A92" s="8">
         <v>1496</v>
       </c>
@@ -11403,7 +11405,7 @@
       <c r="AD92" s="8"/>
       <c r="AE92" s="8"/>
     </row>
-    <row r="93" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A93" s="8">
         <v>1497</v>
       </c>
@@ -11482,7 +11484,7 @@
       <c r="AD93" s="8"/>
       <c r="AE93" s="8"/>
     </row>
-    <row r="94" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A94" s="8">
         <v>1498</v>
       </c>
@@ -11563,7 +11565,7 @@
       <c r="AD94" s="8"/>
       <c r="AE94" s="8"/>
     </row>
-    <row r="95" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A95" s="8">
         <v>1499</v>
       </c>
@@ -11644,7 +11646,7 @@
       <c r="AD95" s="8"/>
       <c r="AE95" s="8"/>
     </row>
-    <row r="96" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A96" s="8">
         <v>1500</v>
       </c>
@@ -11725,7 +11727,7 @@
       <c r="AD96" s="8"/>
       <c r="AE96" s="8"/>
     </row>
-    <row r="97" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A97" s="8">
         <v>1501</v>
       </c>
@@ -11804,7 +11806,7 @@
       <c r="AD97" s="8"/>
       <c r="AE97" s="8"/>
     </row>
-    <row r="98" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A98" s="8">
         <v>1504</v>
       </c>
@@ -11883,7 +11885,7 @@
       <c r="AD98" s="8"/>
       <c r="AE98" s="8"/>
     </row>
-    <row r="99" spans="1:31" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:31" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A99" s="8">
         <v>1505</v>
       </c>
@@ -11962,7 +11964,7 @@
       <c r="AD99" s="8"/>
       <c r="AE99" s="8"/>
     </row>
-    <row r="100" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A100" s="8">
         <v>1506</v>
       </c>
@@ -12041,7 +12043,7 @@
       <c r="AD100" s="8"/>
       <c r="AE100" s="8"/>
     </row>
-    <row r="101" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A101" s="8">
         <v>1507</v>
       </c>
@@ -12118,7 +12120,7 @@
       <c r="AD101" s="8"/>
       <c r="AE101" s="8"/>
     </row>
-    <row r="102" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A102" s="8">
         <v>1508</v>
       </c>
@@ -12195,7 +12197,7 @@
       <c r="AD102" s="8"/>
       <c r="AE102" s="8"/>
     </row>
-    <row r="103" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A103" s="8">
         <v>1509</v>
       </c>
@@ -12272,7 +12274,7 @@
       <c r="AD103" s="8"/>
       <c r="AE103" s="8"/>
     </row>
-    <row r="104" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A104" s="8">
         <v>1510</v>
       </c>
@@ -12351,7 +12353,7 @@
       <c r="AD104" s="8"/>
       <c r="AE104" s="8"/>
     </row>
-    <row r="105" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A105" s="8">
         <v>1511</v>
       </c>
@@ -12428,7 +12430,7 @@
       <c r="AD105" s="8"/>
       <c r="AE105" s="8"/>
     </row>
-    <row r="106" spans="1:31" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:31" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A106" s="8">
         <v>1512</v>
       </c>
@@ -12507,7 +12509,7 @@
       <c r="AD106" s="8"/>
       <c r="AE106" s="8"/>
     </row>
-    <row r="107" spans="1:31" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:31" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A107" s="8">
         <v>1513</v>
       </c>
@@ -12588,7 +12590,7 @@
       <c r="AD107" s="8"/>
       <c r="AE107" s="8"/>
     </row>
-    <row r="108" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A108" s="8">
         <v>1515</v>
       </c>
@@ -12667,7 +12669,7 @@
       <c r="AD108" s="8"/>
       <c r="AE108" s="8"/>
     </row>
-    <row r="109" spans="1:31" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:31" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A109" s="8">
         <v>1518</v>
       </c>
@@ -12746,7 +12748,7 @@
       <c r="AD109" s="8"/>
       <c r="AE109" s="8"/>
     </row>
-    <row r="110" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A110" s="8">
         <v>1519</v>
       </c>
@@ -12825,7 +12827,7 @@
       <c r="AD110" s="8"/>
       <c r="AE110" s="8"/>
     </row>
-    <row r="111" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A111" s="8">
         <v>1520</v>
       </c>
@@ -12904,7 +12906,7 @@
       <c r="AD111" s="8"/>
       <c r="AE111" s="8"/>
     </row>
-    <row r="112" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A112" s="8">
         <v>1521</v>
       </c>
@@ -12985,7 +12987,7 @@
       <c r="AD112" s="8"/>
       <c r="AE112" s="8"/>
     </row>
-    <row r="113" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A113" s="8">
         <v>1522</v>
       </c>
@@ -13066,7 +13068,7 @@
       <c r="AD113" s="8"/>
       <c r="AE113" s="8"/>
     </row>
-    <row r="114" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A114" s="8">
         <v>1523</v>
       </c>
@@ -13147,7 +13149,7 @@
       <c r="AD114" s="8"/>
       <c r="AE114" s="8"/>
     </row>
-    <row r="115" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A115" s="8">
         <v>1524</v>
       </c>
@@ -13228,7 +13230,7 @@
       <c r="AD115" s="8"/>
       <c r="AE115" s="8"/>
     </row>
-    <row r="116" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A116" s="8">
         <v>1525</v>
       </c>
@@ -13309,7 +13311,7 @@
       <c r="AD116" s="8"/>
       <c r="AE116" s="8"/>
     </row>
-    <row r="117" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A117" s="8">
         <v>1527</v>
       </c>
@@ -13390,7 +13392,7 @@
       <c r="AD117" s="8"/>
       <c r="AE117" s="8"/>
     </row>
-    <row r="118" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A118" s="8">
         <v>1529</v>
       </c>
@@ -13471,7 +13473,7 @@
       <c r="AD118" s="8"/>
       <c r="AE118" s="8"/>
     </row>
-    <row r="119" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A119" s="8">
         <v>1530</v>
       </c>
@@ -13552,7 +13554,7 @@
       <c r="AD119" s="8"/>
       <c r="AE119" s="8"/>
     </row>
-    <row r="120" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A120" s="8">
         <v>1531</v>
       </c>
@@ -13633,7 +13635,7 @@
       <c r="AD120" s="8"/>
       <c r="AE120" s="8"/>
     </row>
-    <row r="121" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A121" s="8">
         <v>1532</v>
       </c>
@@ -13714,7 +13716,7 @@
       <c r="AD121" s="8"/>
       <c r="AE121" s="8"/>
     </row>
-    <row r="122" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A122" s="8">
         <v>1533</v>
       </c>
@@ -13795,7 +13797,7 @@
       <c r="AD122" s="8"/>
       <c r="AE122" s="8"/>
     </row>
-    <row r="123" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A123" s="8">
         <v>1534</v>
       </c>
@@ -13876,7 +13878,7 @@
       <c r="AD123" s="8"/>
       <c r="AE123" s="8"/>
     </row>
-    <row r="124" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A124" s="8">
         <v>1535</v>
       </c>
@@ -13957,7 +13959,7 @@
       <c r="AD124" s="8"/>
       <c r="AE124" s="8"/>
     </row>
-    <row r="125" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A125" s="8">
         <v>1536</v>
       </c>
@@ -14038,7 +14040,7 @@
       <c r="AD125" s="8"/>
       <c r="AE125" s="8"/>
     </row>
-    <row r="126" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A126" s="8">
         <v>1537</v>
       </c>
@@ -14117,7 +14119,7 @@
       <c r="AD126" s="8"/>
       <c r="AE126" s="8"/>
     </row>
-    <row r="127" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A127" s="8">
         <v>1538</v>
       </c>
@@ -14190,7 +14192,7 @@
       <c r="AD127" s="8"/>
       <c r="AE127" s="8"/>
     </row>
-    <row r="128" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A128" s="8">
         <v>1541</v>
       </c>
@@ -14263,7 +14265,7 @@
       <c r="AD128" s="8"/>
       <c r="AE128" s="8"/>
     </row>
-    <row r="129" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A129" s="8">
         <v>1542</v>
       </c>
@@ -14336,7 +14338,7 @@
       <c r="AD129" s="8"/>
       <c r="AE129" s="8"/>
     </row>
-    <row r="130" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A130" s="8">
         <v>1543</v>
       </c>
@@ -14409,7 +14411,7 @@
       <c r="AD130" s="8"/>
       <c r="AE130" s="8"/>
     </row>
-    <row r="131" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A131" s="8">
         <v>1546</v>
       </c>
@@ -14482,7 +14484,7 @@
       <c r="AD131" s="8"/>
       <c r="AE131" s="8"/>
     </row>
-    <row r="132" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A132" s="8">
         <v>1549</v>
       </c>
@@ -14555,7 +14557,7 @@
       <c r="AD132" s="8"/>
       <c r="AE132" s="8"/>
     </row>
-    <row r="133" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A133" s="8">
         <v>1550</v>
       </c>
@@ -14628,7 +14630,7 @@
       <c r="AD133" s="8"/>
       <c r="AE133" s="8"/>
     </row>
-    <row r="134" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A134" s="8">
         <v>1551</v>
       </c>
@@ -14701,7 +14703,7 @@
       <c r="AD134" s="8"/>
       <c r="AE134" s="8"/>
     </row>
-    <row r="135" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A135" s="8">
         <v>1552</v>
       </c>
@@ -14774,7 +14776,7 @@
       <c r="AD135" s="8"/>
       <c r="AE135" s="8"/>
     </row>
-    <row r="136" spans="1:31" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:31" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A136" s="8">
         <v>1555</v>
       </c>
@@ -14847,7 +14849,7 @@
       <c r="AD136" s="8"/>
       <c r="AE136" s="8"/>
     </row>
-    <row r="137" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A137" s="8">
         <v>1558</v>
       </c>
@@ -14920,7 +14922,7 @@
       <c r="AD137" s="8"/>
       <c r="AE137" s="8"/>
     </row>
-    <row r="138" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A138" s="8">
         <v>1559</v>
       </c>
@@ -14995,7 +14997,7 @@
       <c r="AD138" s="8"/>
       <c r="AE138" s="8"/>
     </row>
-    <row r="139" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A139" s="8">
         <v>1560</v>
       </c>
@@ -15072,7 +15074,7 @@
       <c r="AD139" s="8"/>
       <c r="AE139" s="8"/>
     </row>
-    <row r="140" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A140" s="8">
         <v>1561</v>
       </c>
@@ -15149,7 +15151,7 @@
       <c r="AD140" s="8"/>
       <c r="AE140" s="8"/>
     </row>
-    <row r="141" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A141" s="8">
         <v>1562</v>
       </c>
@@ -15226,7 +15228,7 @@
       <c r="AD141" s="8"/>
       <c r="AE141" s="8"/>
     </row>
-    <row r="142" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A142" s="8">
         <v>1563</v>
       </c>
@@ -15303,7 +15305,7 @@
       <c r="AD142" s="8"/>
       <c r="AE142" s="8"/>
     </row>
-    <row r="143" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A143" s="8">
         <v>1564</v>
       </c>
@@ -15380,7 +15382,7 @@
       <c r="AD143" s="8"/>
       <c r="AE143" s="8"/>
     </row>
-    <row r="144" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A144" s="8">
         <v>1565</v>
       </c>
@@ -15457,7 +15459,7 @@
       <c r="AD144" s="8"/>
       <c r="AE144" s="8"/>
     </row>
-    <row r="145" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A145" s="8">
         <v>1566</v>
       </c>
@@ -15534,7 +15536,7 @@
       <c r="AD145" s="8"/>
       <c r="AE145" s="8"/>
     </row>
-    <row r="146" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A146" s="8">
         <v>1567</v>
       </c>
@@ -15611,7 +15613,7 @@
       <c r="AD146" s="8"/>
       <c r="AE146" s="8"/>
     </row>
-    <row r="147" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A147" s="8">
         <v>1569</v>
       </c>
@@ -15686,7 +15688,7 @@
       <c r="AD147" s="8"/>
       <c r="AE147" s="8"/>
     </row>
-    <row r="148" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A148" s="8">
         <v>1572</v>
       </c>
@@ -15763,7 +15765,7 @@
       <c r="AD148" s="8"/>
       <c r="AE148" s="8"/>
     </row>
-    <row r="149" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A149" s="8">
         <v>1573</v>
       </c>
@@ -15836,7 +15838,7 @@
       <c r="AD149" s="8"/>
       <c r="AE149" s="8"/>
     </row>
-    <row r="150" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A150" s="8">
         <v>1576</v>
       </c>
@@ -15909,7 +15911,7 @@
       <c r="AD150" s="8"/>
       <c r="AE150" s="8"/>
     </row>
-    <row r="151" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A151" s="8">
         <v>1577</v>
       </c>
@@ -15982,7 +15984,7 @@
       <c r="AD151" s="8"/>
       <c r="AE151" s="8"/>
     </row>
-    <row r="152" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A152" s="8">
         <v>1580</v>
       </c>
@@ -16055,7 +16057,7 @@
       <c r="AD152" s="8"/>
       <c r="AE152" s="8"/>
     </row>
-    <row r="153" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A153" s="8">
         <v>1581</v>
       </c>
@@ -16128,7 +16130,7 @@
       <c r="AD153" s="8"/>
       <c r="AE153" s="8"/>
     </row>
-    <row r="154" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A154" s="8">
         <v>1586</v>
       </c>
@@ -16197,7 +16199,7 @@
       <c r="AD154" s="8"/>
       <c r="AE154" s="8"/>
     </row>
-    <row r="155" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A155" s="8">
         <v>1587</v>
       </c>
@@ -16266,7 +16268,7 @@
       <c r="AD155" s="8"/>
       <c r="AE155" s="8"/>
     </row>
-    <row r="156" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A156" s="8">
         <v>1589</v>
       </c>
@@ -16335,7 +16337,7 @@
       <c r="AD156" s="8"/>
       <c r="AE156" s="8"/>
     </row>
-    <row r="157" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A157" s="8">
         <v>1590</v>
       </c>
@@ -16404,7 +16406,7 @@
       <c r="AD157" s="8"/>
       <c r="AE157" s="8"/>
     </row>
-    <row r="158" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A158" s="8">
         <v>1591</v>
       </c>
@@ -16475,7 +16477,7 @@
       <c r="AD158" s="8"/>
       <c r="AE158" s="8"/>
     </row>
-    <row r="159" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A159" s="8">
         <v>1592</v>
       </c>
@@ -16548,7 +16550,7 @@
       <c r="AD159" s="8"/>
       <c r="AE159" s="8"/>
     </row>
-    <row r="160" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A160" s="8">
         <v>1593</v>
       </c>
@@ -16621,7 +16623,7 @@
       <c r="AD160" s="8"/>
       <c r="AE160" s="8"/>
     </row>
-    <row r="161" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A161" s="8">
         <v>1594</v>
       </c>
@@ -16694,7 +16696,7 @@
       <c r="AD161" s="8"/>
       <c r="AE161" s="8"/>
     </row>
-    <row r="162" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A162" s="8">
         <v>1595</v>
       </c>
@@ -16775,7 +16777,7 @@
       <c r="AD162" s="8"/>
       <c r="AE162" s="8"/>
     </row>
-    <row r="163" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A163" s="8">
         <v>1596</v>
       </c>
@@ -16856,7 +16858,7 @@
       <c r="AD163" s="8"/>
       <c r="AE163" s="8"/>
     </row>
-    <row r="164" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A164" s="8">
         <v>1597</v>
       </c>
@@ -16937,7 +16939,7 @@
       <c r="AD164" s="8"/>
       <c r="AE164" s="8"/>
     </row>
-    <row r="165" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A165" s="8">
         <v>1598</v>
       </c>
@@ -17018,7 +17020,7 @@
       <c r="AD165" s="8"/>
       <c r="AE165" s="8"/>
     </row>
-    <row r="166" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A166" s="8">
         <v>1599</v>
       </c>
@@ -17099,7 +17101,7 @@
       <c r="AD166" s="8"/>
       <c r="AE166" s="8"/>
     </row>
-    <row r="167" spans="1:31" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:31" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A167" s="8">
         <v>1600</v>
       </c>
@@ -17172,7 +17174,7 @@
       <c r="AD167" s="8"/>
       <c r="AE167" s="8"/>
     </row>
-    <row r="168" spans="1:31" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:31" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A168" s="8">
         <v>1601</v>
       </c>
@@ -17245,7 +17247,7 @@
       <c r="AD168" s="8"/>
       <c r="AE168" s="8"/>
     </row>
-    <row r="169" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A169" s="8">
         <v>1602</v>
       </c>
@@ -17312,7 +17314,7 @@
       <c r="AD169" s="8"/>
       <c r="AE169" s="8"/>
     </row>
-    <row r="170" spans="1:31" ht="316.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:31" ht="316.8" x14ac:dyDescent="0.3">
       <c r="A170" s="8">
         <v>1603</v>
       </c>
@@ -17395,7 +17397,7 @@
       <c r="AD170" s="8"/>
       <c r="AE170" s="8"/>
     </row>
-    <row r="171" spans="1:31" ht="316.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:31" ht="316.8" x14ac:dyDescent="0.3">
       <c r="A171" s="8">
         <v>1604</v>
       </c>
@@ -17478,7 +17480,7 @@
       <c r="AD171" s="8"/>
       <c r="AE171" s="8"/>
     </row>
-    <row r="172" spans="1:31" ht="316.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:31" ht="316.8" x14ac:dyDescent="0.3">
       <c r="A172" s="8">
         <v>1605</v>
       </c>
@@ -17561,7 +17563,7 @@
       <c r="AD172" s="8"/>
       <c r="AE172" s="8"/>
     </row>
-    <row r="173" spans="1:31" ht="316.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:31" ht="316.8" x14ac:dyDescent="0.3">
       <c r="A173" s="8">
         <v>1606</v>
       </c>
@@ -17646,7 +17648,7 @@
       <c r="AD173" s="8"/>
       <c r="AE173" s="8"/>
     </row>
-    <row r="174" spans="1:31" ht="316.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:31" ht="316.8" x14ac:dyDescent="0.3">
       <c r="A174" s="8">
         <v>1607</v>
       </c>
@@ -17731,7 +17733,7 @@
       <c r="AD174" s="8"/>
       <c r="AE174" s="8"/>
     </row>
-    <row r="175" spans="1:31" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:31" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A175" s="8">
         <v>1608</v>
       </c>
@@ -17802,7 +17804,7 @@
       <c r="AD175" s="8"/>
       <c r="AE175" s="8"/>
     </row>
-    <row r="176" spans="1:31" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:31" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A176" s="8">
         <v>1609</v>
       </c>
@@ -17873,7 +17875,7 @@
       <c r="AD176" s="8"/>
       <c r="AE176" s="8"/>
     </row>
-    <row r="177" spans="1:31" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:31" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A177" s="8">
         <v>1610</v>
       </c>
@@ -17944,7 +17946,7 @@
       <c r="AD177" s="8"/>
       <c r="AE177" s="8"/>
     </row>
-    <row r="178" spans="1:31" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:31" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A178" s="8">
         <v>1611</v>
       </c>
@@ -18015,7 +18017,7 @@
       <c r="AD178" s="8"/>
       <c r="AE178" s="8"/>
     </row>
-    <row r="179" spans="1:31" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:31" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A179" s="8">
         <v>1612</v>
       </c>
@@ -18082,7 +18084,7 @@
       <c r="AD179" s="8"/>
       <c r="AE179" s="8"/>
     </row>
-    <row r="180" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A180" s="8">
         <v>1614</v>
       </c>
@@ -18163,7 +18165,7 @@
       <c r="AD180" s="8"/>
       <c r="AE180" s="8"/>
     </row>
-    <row r="181" spans="1:31" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:31" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A181" s="8">
         <v>1615</v>
       </c>
@@ -18244,7 +18246,7 @@
       <c r="AD181" s="8"/>
       <c r="AE181" s="8"/>
     </row>
-    <row r="182" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A182" s="8">
         <v>1616</v>
       </c>
@@ -18325,7 +18327,7 @@
       <c r="AD182" s="8"/>
       <c r="AE182" s="8"/>
     </row>
-    <row r="183" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A183" s="8">
         <v>1617</v>
       </c>
@@ -18406,7 +18408,7 @@
       <c r="AD183" s="8"/>
       <c r="AE183" s="8"/>
     </row>
-    <row r="184" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A184" s="8">
         <v>1618</v>
       </c>
@@ -18487,7 +18489,7 @@
       <c r="AD184" s="8"/>
       <c r="AE184" s="8"/>
     </row>
-    <row r="185" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A185" s="8">
         <v>1621</v>
       </c>
@@ -18568,7 +18570,7 @@
       <c r="AD185" s="8"/>
       <c r="AE185" s="8"/>
     </row>
-    <row r="186" spans="1:31" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:31" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A186" s="8">
         <v>1622</v>
       </c>
@@ -18649,7 +18651,7 @@
       <c r="AD186" s="8"/>
       <c r="AE186" s="8"/>
     </row>
-    <row r="187" spans="1:31" ht="72" hidden="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:31" ht="72" x14ac:dyDescent="0.3">
       <c r="A187" s="8">
         <v>1623</v>
       </c>
@@ -18730,7 +18732,7 @@
       <c r="AD187" s="8"/>
       <c r="AE187" s="8"/>
     </row>
-    <row r="188" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A188" s="8">
         <v>1624</v>
       </c>
@@ -18811,7 +18813,7 @@
       <c r="AD188" s="8"/>
       <c r="AE188" s="8"/>
     </row>
-    <row r="189" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A189" s="8">
         <v>1625</v>
       </c>
@@ -18892,7 +18894,7 @@
       <c r="AD189" s="8"/>
       <c r="AE189" s="8"/>
     </row>
-    <row r="190" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A190" s="8">
         <v>1627</v>
       </c>
@@ -18963,7 +18965,7 @@
       <c r="AD190" s="8"/>
       <c r="AE190" s="8"/>
     </row>
-    <row r="191" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A191" s="8">
         <v>1628</v>
       </c>
@@ -19034,7 +19036,7 @@
       <c r="AD191" s="8"/>
       <c r="AE191" s="8"/>
     </row>
-    <row r="192" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A192" s="8">
         <v>1629</v>
       </c>
@@ -19105,7 +19107,7 @@
       <c r="AD192" s="8"/>
       <c r="AE192" s="8"/>
     </row>
-    <row r="193" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A193" s="8">
         <v>1630</v>
       </c>
@@ -19176,7 +19178,7 @@
       <c r="AD193" s="8"/>
       <c r="AE193" s="8"/>
     </row>
-    <row r="194" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A194" s="8">
         <v>1631</v>
       </c>
@@ -19243,7 +19245,7 @@
       <c r="AD194" s="8"/>
       <c r="AE194" s="8"/>
     </row>
-    <row r="195" spans="1:31" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:31" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A195" s="8">
         <v>1632</v>
       </c>
@@ -19324,7 +19326,7 @@
       <c r="AD195" s="8"/>
       <c r="AE195" s="8"/>
     </row>
-    <row r="196" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A196" s="8">
         <v>1633</v>
       </c>
@@ -19405,7 +19407,7 @@
       <c r="AD196" s="8"/>
       <c r="AE196" s="8"/>
     </row>
-    <row r="197" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A197" s="8">
         <v>1634</v>
       </c>
@@ -19486,7 +19488,7 @@
       <c r="AD197" s="8"/>
       <c r="AE197" s="8"/>
     </row>
-    <row r="198" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A198" s="8">
         <v>1635</v>
       </c>
@@ -19567,7 +19569,7 @@
       <c r="AD198" s="8"/>
       <c r="AE198" s="8"/>
     </row>
-    <row r="199" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A199" s="8">
         <v>1636</v>
       </c>
@@ -19650,7 +19652,7 @@
       <c r="AD199" s="8"/>
       <c r="AE199" s="8"/>
     </row>
-    <row r="200" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A200" s="8">
         <v>1640</v>
       </c>
@@ -19729,7 +19731,7 @@
       <c r="AD200" s="8"/>
       <c r="AE200" s="8"/>
     </row>
-    <row r="201" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A201" s="8">
         <v>1641</v>
       </c>
@@ -19808,7 +19810,7 @@
       <c r="AD201" s="8"/>
       <c r="AE201" s="8"/>
     </row>
-    <row r="202" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A202" s="8">
         <v>1642</v>
       </c>
@@ -19887,7 +19889,7 @@
       <c r="AD202" s="8"/>
       <c r="AE202" s="8"/>
     </row>
-    <row r="203" spans="1:31" ht="144" hidden="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:31" ht="144" x14ac:dyDescent="0.3">
       <c r="A203" s="8">
         <v>1643</v>
       </c>
@@ -19964,7 +19966,7 @@
       <c r="AD203" s="8"/>
       <c r="AE203" s="8"/>
     </row>
-    <row r="204" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A204" s="8">
         <v>1644</v>
       </c>
@@ -20041,7 +20043,7 @@
       <c r="AD204" s="8"/>
       <c r="AE204" s="8"/>
     </row>
-    <row r="205" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A205" s="8">
         <v>1645</v>
       </c>
@@ -20116,7 +20118,7 @@
       <c r="AD205" s="8"/>
       <c r="AE205" s="8"/>
     </row>
-    <row r="206" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A206" s="8">
         <v>1646</v>
       </c>
@@ -20191,7 +20193,7 @@
       <c r="AD206" s="8"/>
       <c r="AE206" s="8"/>
     </row>
-    <row r="207" spans="1:31" ht="72" hidden="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:31" ht="72" x14ac:dyDescent="0.3">
       <c r="A207" s="8">
         <v>1647</v>
       </c>
@@ -20266,7 +20268,7 @@
       <c r="AD207" s="8"/>
       <c r="AE207" s="8"/>
     </row>
-    <row r="208" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A208" s="8">
         <v>1648</v>
       </c>
@@ -20341,7 +20343,7 @@
       <c r="AD208" s="8"/>
       <c r="AE208" s="8"/>
     </row>
-    <row r="209" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A209" s="8">
         <v>1649</v>
       </c>
@@ -20416,7 +20418,7 @@
       <c r="AD209" s="8"/>
       <c r="AE209" s="8"/>
     </row>
-    <row r="210" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A210" s="8">
         <v>1650</v>
       </c>
@@ -20491,7 +20493,7 @@
       <c r="AD210" s="8"/>
       <c r="AE210" s="8"/>
     </row>
-    <row r="211" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A211" s="8">
         <v>1653</v>
       </c>
@@ -20560,7 +20562,7 @@
       <c r="AD211" s="8"/>
       <c r="AE211" s="8"/>
     </row>
-    <row r="212" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A212" s="8">
         <v>1654</v>
       </c>
@@ -20629,7 +20631,7 @@
       <c r="AD212" s="8"/>
       <c r="AE212" s="8"/>
     </row>
-    <row r="213" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A213" s="8">
         <v>1655</v>
       </c>
@@ -20700,7 +20702,7 @@
       <c r="AD213" s="8"/>
       <c r="AE213" s="8"/>
     </row>
-    <row r="214" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A214" s="8">
         <v>1656</v>
       </c>
@@ -20771,7 +20773,7 @@
       <c r="AD214" s="8"/>
       <c r="AE214" s="8"/>
     </row>
-    <row r="215" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A215" s="8">
         <v>1657</v>
       </c>
@@ -20838,7 +20840,7 @@
       <c r="AD215" s="8"/>
       <c r="AE215" s="8"/>
     </row>
-    <row r="216" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A216" s="8">
         <v>1658</v>
       </c>
@@ -20909,7 +20911,7 @@
       <c r="AD216" s="8"/>
       <c r="AE216" s="8"/>
     </row>
-    <row r="217" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A217" s="8">
         <v>1659</v>
       </c>
@@ -20980,7 +20982,7 @@
       <c r="AD217" s="8"/>
       <c r="AE217" s="8"/>
     </row>
-    <row r="218" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A218" s="8">
         <v>1660</v>
       </c>
@@ -21049,7 +21051,7 @@
       <c r="AD218" s="8"/>
       <c r="AE218" s="8"/>
     </row>
-    <row r="219" spans="1:31" ht="230.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:31" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A219" s="8">
         <v>1661</v>
       </c>
@@ -21118,7 +21120,7 @@
       <c r="AD219" s="8"/>
       <c r="AE219" s="8"/>
     </row>
-    <row r="220" spans="1:31" ht="158.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:31" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A220" s="8">
         <v>1662</v>
       </c>
@@ -21187,7 +21189,7 @@
       <c r="AD220" s="8"/>
       <c r="AE220" s="8"/>
     </row>
-    <row r="221" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A221" s="8">
         <v>1663</v>
       </c>
@@ -21254,7 +21256,7 @@
       <c r="AD221" s="8"/>
       <c r="AE221" s="8"/>
     </row>
-    <row r="222" spans="1:31" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:31" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A222" s="8">
         <v>1664</v>
       </c>
@@ -21323,7 +21325,7 @@
       <c r="AD222" s="8"/>
       <c r="AE222" s="8"/>
     </row>
-    <row r="223" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A223" s="8">
         <v>1665</v>
       </c>
@@ -21390,7 +21392,7 @@
       <c r="AD223" s="8"/>
       <c r="AE223" s="8"/>
     </row>
-    <row r="224" spans="1:31" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:31" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A224" s="8">
         <v>1666</v>
       </c>
@@ -21461,7 +21463,7 @@
       <c r="AD224" s="8"/>
       <c r="AE224" s="8"/>
     </row>
-    <row r="225" spans="1:31" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:31" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A225" s="8">
         <v>1667</v>
       </c>
@@ -21532,7 +21534,7 @@
       <c r="AD225" s="8"/>
       <c r="AE225" s="8"/>
     </row>
-    <row r="226" spans="1:31" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:31" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A226" s="8">
         <v>1668</v>
       </c>
@@ -21599,7 +21601,7 @@
       <c r="AD226" s="8"/>
       <c r="AE226" s="8"/>
     </row>
-    <row r="227" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A227" s="8">
         <v>1671</v>
       </c>
@@ -21680,7 +21682,7 @@
       <c r="AD227" s="8"/>
       <c r="AE227" s="8"/>
     </row>
-    <row r="228" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A228" s="8">
         <v>1672</v>
       </c>
@@ -21761,7 +21763,7 @@
       <c r="AD228" s="8"/>
       <c r="AE228" s="8"/>
     </row>
-    <row r="229" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A229" s="8">
         <v>1673</v>
       </c>
@@ -21842,7 +21844,7 @@
       <c r="AD229" s="8"/>
       <c r="AE229" s="8"/>
     </row>
-    <row r="230" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A230" s="8">
         <v>1674</v>
       </c>
@@ -21923,7 +21925,7 @@
       <c r="AD230" s="8"/>
       <c r="AE230" s="8"/>
     </row>
-    <row r="231" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A231" s="8">
         <v>1675</v>
       </c>
@@ -22004,7 +22006,7 @@
       <c r="AD231" s="8"/>
       <c r="AE231" s="8"/>
     </row>
-    <row r="232" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A232" s="8">
         <v>1677</v>
       </c>
@@ -22085,7 +22087,7 @@
       <c r="AD232" s="8"/>
       <c r="AE232" s="8"/>
     </row>
-    <row r="233" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A233" s="8">
         <v>1678</v>
       </c>
@@ -22166,7 +22168,7 @@
       <c r="AD233" s="8"/>
       <c r="AE233" s="8"/>
     </row>
-    <row r="234" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A234" s="8">
         <v>1679</v>
       </c>
@@ -22247,7 +22249,7 @@
       <c r="AD234" s="8"/>
       <c r="AE234" s="8"/>
     </row>
-    <row r="235" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A235" s="8">
         <v>1680</v>
       </c>
@@ -22328,7 +22330,7 @@
       <c r="AD235" s="8"/>
       <c r="AE235" s="8"/>
     </row>
-    <row r="236" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A236" s="8">
         <v>1682</v>
       </c>
@@ -22399,7 +22401,7 @@
       <c r="AD236" s="8"/>
       <c r="AE236" s="8"/>
     </row>
-    <row r="237" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A237" s="8">
         <v>1683</v>
       </c>
@@ -22470,7 +22472,7 @@
       <c r="AD237" s="8"/>
       <c r="AE237" s="8"/>
     </row>
-    <row r="238" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A238" s="8">
         <v>1684</v>
       </c>
@@ -22541,7 +22543,7 @@
       <c r="AD238" s="8"/>
       <c r="AE238" s="8"/>
     </row>
-    <row r="239" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A239" s="8">
         <v>1685</v>
       </c>
@@ -22608,7 +22610,7 @@
       <c r="AD239" s="8"/>
       <c r="AE239" s="8"/>
     </row>
-    <row r="240" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A240" s="8">
         <v>1686</v>
       </c>
@@ -22675,7 +22677,7 @@
       <c r="AD240" s="8"/>
       <c r="AE240" s="8"/>
     </row>
-    <row r="241" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A241" s="8">
         <v>1688</v>
       </c>
@@ -22754,7 +22756,7 @@
       <c r="AD241" s="8"/>
       <c r="AE241" s="8"/>
     </row>
-    <row r="242" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A242" s="8">
         <v>1689</v>
       </c>
@@ -22833,7 +22835,7 @@
       <c r="AD242" s="8"/>
       <c r="AE242" s="8"/>
     </row>
-    <row r="243" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A243" s="8">
         <v>1690</v>
       </c>
@@ -22912,7 +22914,7 @@
       <c r="AD243" s="8"/>
       <c r="AE243" s="8"/>
     </row>
-    <row r="244" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A244" s="8">
         <v>1691</v>
       </c>
@@ -22991,7 +22993,7 @@
       <c r="AD244" s="8"/>
       <c r="AE244" s="8"/>
     </row>
-    <row r="245" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A245" s="8">
         <v>1692</v>
       </c>
@@ -23070,7 +23072,7 @@
       <c r="AD245" s="8"/>
       <c r="AE245" s="8"/>
     </row>
-    <row r="246" spans="1:31" ht="72" hidden="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:31" ht="72" x14ac:dyDescent="0.3">
       <c r="A246" s="8">
         <v>1693</v>
       </c>
@@ -23141,7 +23143,7 @@
       <c r="AD246" s="8"/>
       <c r="AE246" s="8"/>
     </row>
-    <row r="247" spans="1:31" ht="72" hidden="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:31" ht="72" x14ac:dyDescent="0.3">
       <c r="A247" s="8">
         <v>1694</v>
       </c>
@@ -23210,7 +23212,7 @@
       <c r="AD247" s="8"/>
       <c r="AE247" s="8"/>
     </row>
-    <row r="248" spans="1:31" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:31" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A248" s="8">
         <v>1695</v>
       </c>
@@ -23281,7 +23283,7 @@
       <c r="AD248" s="8"/>
       <c r="AE248" s="8"/>
     </row>
-    <row r="249" spans="1:31" ht="72" hidden="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:31" ht="72" x14ac:dyDescent="0.3">
       <c r="A249" s="8">
         <v>1696</v>
       </c>
@@ -23352,7 +23354,7 @@
       <c r="AD249" s="8"/>
       <c r="AE249" s="8"/>
     </row>
-    <row r="250" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A250" s="8">
         <v>1697</v>
       </c>
@@ -23423,7 +23425,7 @@
       <c r="AD250" s="8"/>
       <c r="AE250" s="8"/>
     </row>
-    <row r="251" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A251" s="8">
         <v>1698</v>
       </c>
@@ -23494,7 +23496,7 @@
       <c r="AD251" s="8"/>
       <c r="AE251" s="8"/>
     </row>
-    <row r="252" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A252" s="8">
         <v>1699</v>
       </c>
@@ -23565,7 +23567,7 @@
       <c r="AD252" s="8"/>
       <c r="AE252" s="8"/>
     </row>
-    <row r="253" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A253" s="8">
         <v>1700</v>
       </c>
@@ -23636,7 +23638,7 @@
       <c r="AD253" s="8"/>
       <c r="AE253" s="8"/>
     </row>
-    <row r="254" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A254" s="8">
         <v>1701</v>
       </c>
@@ -23707,7 +23709,7 @@
       <c r="AD254" s="8"/>
       <c r="AE254" s="8"/>
     </row>
-    <row r="255" spans="1:31" ht="129.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:31" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A255" s="8">
         <v>1707</v>
       </c>
@@ -23788,7 +23790,7 @@
       <c r="AD255" s="8"/>
       <c r="AE255" s="8"/>
     </row>
-    <row r="256" spans="1:31" ht="129.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:31" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A256" s="8">
         <v>1708</v>
       </c>
@@ -23869,7 +23871,7 @@
       <c r="AD256" s="8"/>
       <c r="AE256" s="8"/>
     </row>
-    <row r="257" spans="1:31" ht="129.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:31" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A257" s="8">
         <v>1709</v>
       </c>
@@ -23950,7 +23952,7 @@
       <c r="AD257" s="8"/>
       <c r="AE257" s="8"/>
     </row>
-    <row r="258" spans="1:31" ht="129.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:31" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A258" s="8">
         <v>1710</v>
       </c>
@@ -24031,7 +24033,7 @@
       <c r="AD258" s="8"/>
       <c r="AE258" s="8"/>
     </row>
-    <row r="259" spans="1:31" ht="129.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:31" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A259" s="8">
         <v>1711</v>
       </c>
@@ -24112,7 +24114,7 @@
       <c r="AD259" s="8"/>
       <c r="AE259" s="8"/>
     </row>
-    <row r="260" spans="1:31" ht="129.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:31" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A260" s="8">
         <v>1712</v>
       </c>
@@ -24193,7 +24195,7 @@
       <c r="AD260" s="8"/>
       <c r="AE260" s="8"/>
     </row>
-    <row r="261" spans="1:31" ht="144" hidden="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:31" ht="144" x14ac:dyDescent="0.3">
       <c r="A261" s="8">
         <v>1713</v>
       </c>
@@ -24264,7 +24266,7 @@
       <c r="AD261" s="8"/>
       <c r="AE261" s="8"/>
     </row>
-    <row r="262" spans="1:31" ht="144" hidden="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:31" ht="144" x14ac:dyDescent="0.3">
       <c r="A262" s="8">
         <v>1714</v>
       </c>
@@ -24337,7 +24339,7 @@
       <c r="AD262" s="8"/>
       <c r="AE262" s="8"/>
     </row>
-    <row r="263" spans="1:31" ht="144" hidden="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:31" ht="144" x14ac:dyDescent="0.3">
       <c r="A263" s="8">
         <v>1715</v>
       </c>
@@ -24410,7 +24412,7 @@
       <c r="AD263" s="8"/>
       <c r="AE263" s="8"/>
     </row>
-    <row r="264" spans="1:31" ht="144" hidden="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:31" ht="144" x14ac:dyDescent="0.3">
       <c r="A264" s="8">
         <v>1716</v>
       </c>
@@ -24483,7 +24485,7 @@
       <c r="AD264" s="8"/>
       <c r="AE264" s="8"/>
     </row>
-    <row r="265" spans="1:31" ht="144" hidden="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:31" ht="144" x14ac:dyDescent="0.3">
       <c r="A265" s="8">
         <v>1717</v>
       </c>
@@ -24556,7 +24558,7 @@
       <c r="AD265" s="8"/>
       <c r="AE265" s="8"/>
     </row>
-    <row r="266" spans="1:31" ht="144" hidden="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:31" ht="144" x14ac:dyDescent="0.3">
       <c r="A266" s="8">
         <v>1718</v>
       </c>
@@ -24629,7 +24631,7 @@
       <c r="AD266" s="8"/>
       <c r="AE266" s="8"/>
     </row>
-    <row r="267" spans="1:31" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:31" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A267" s="8">
         <v>1719</v>
       </c>
@@ -24708,7 +24710,7 @@
       <c r="AD267" s="8"/>
       <c r="AE267" s="8"/>
     </row>
-    <row r="268" spans="1:31" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:31" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A268" s="8">
         <v>1720</v>
       </c>
@@ -24787,7 +24789,7 @@
       <c r="AD268" s="8"/>
       <c r="AE268" s="8"/>
     </row>
-    <row r="269" spans="1:31" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:31" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A269" s="8">
         <v>1721</v>
       </c>
@@ -24866,7 +24868,7 @@
       <c r="AD269" s="8"/>
       <c r="AE269" s="8"/>
     </row>
-    <row r="270" spans="1:31" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:31" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A270" s="8">
         <v>1722</v>
       </c>
@@ -24947,7 +24949,7 @@
       <c r="AD270" s="8"/>
       <c r="AE270" s="8"/>
     </row>
-    <row r="271" spans="1:31" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:31" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A271" s="8">
         <v>1723</v>
       </c>
@@ -25026,7 +25028,7 @@
       <c r="AD271" s="8"/>
       <c r="AE271" s="8"/>
     </row>
-    <row r="272" spans="1:31" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:31" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A272" s="8">
         <v>1724</v>
       </c>
@@ -25107,7 +25109,7 @@
       <c r="AD272" s="8"/>
       <c r="AE272" s="8"/>
     </row>
-    <row r="273" spans="1:31" ht="158.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:31" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A273" s="8">
         <v>1725</v>
       </c>
@@ -25180,7 +25182,7 @@
       <c r="AD273" s="8"/>
       <c r="AE273" s="8"/>
     </row>
-    <row r="274" spans="1:31" ht="158.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:31" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A274" s="8">
         <v>1726</v>
       </c>
@@ -25253,7 +25255,7 @@
       <c r="AD274" s="8"/>
       <c r="AE274" s="8"/>
     </row>
-    <row r="275" spans="1:31" ht="158.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:31" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A275" s="8">
         <v>1727</v>
       </c>
@@ -25326,7 +25328,7 @@
       <c r="AD275" s="8"/>
       <c r="AE275" s="8"/>
     </row>
-    <row r="276" spans="1:31" ht="158.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:31" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A276" s="8">
         <v>1728</v>
       </c>
@@ -25399,7 +25401,7 @@
       <c r="AD276" s="8"/>
       <c r="AE276" s="8"/>
     </row>
-    <row r="277" spans="1:31" ht="158.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:31" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A277" s="8">
         <v>1729</v>
       </c>
@@ -25472,7 +25474,7 @@
       <c r="AD277" s="8"/>
       <c r="AE277" s="8"/>
     </row>
-    <row r="278" spans="1:31" ht="158.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:31" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A278" s="8">
         <v>1730</v>
       </c>
@@ -25545,7 +25547,7 @@
       <c r="AD278" s="8"/>
       <c r="AE278" s="8"/>
     </row>
-    <row r="279" spans="1:31" ht="158.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:31" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A279" s="8">
         <v>1731</v>
       </c>
@@ -25616,7 +25618,7 @@
       <c r="AD279" s="8"/>
       <c r="AE279" s="8"/>
     </row>
-    <row r="280" spans="1:31" ht="158.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:31" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A280" s="8">
         <v>1732</v>
       </c>
@@ -25689,7 +25691,7 @@
       <c r="AD280" s="8"/>
       <c r="AE280" s="8"/>
     </row>
-    <row r="281" spans="1:31" ht="158.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:31" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A281" s="8">
         <v>1733</v>
       </c>
@@ -25760,7 +25762,7 @@
       <c r="AD281" s="8"/>
       <c r="AE281" s="8"/>
     </row>
-    <row r="282" spans="1:31" ht="331.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:31" ht="331.2" x14ac:dyDescent="0.3">
       <c r="A282" s="8">
         <v>1734</v>
       </c>
@@ -25829,7 +25831,7 @@
       <c r="AD282" s="8"/>
       <c r="AE282" s="8"/>
     </row>
-    <row r="283" spans="1:31" ht="331.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:31" ht="331.2" x14ac:dyDescent="0.3">
       <c r="A283" s="8">
         <v>1735</v>
       </c>
@@ -25902,7 +25904,7 @@
       <c r="AD283" s="8"/>
       <c r="AE283" s="8"/>
     </row>
-    <row r="284" spans="1:31" ht="331.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:31" ht="331.2" x14ac:dyDescent="0.3">
       <c r="A284" s="8">
         <v>1736</v>
       </c>
@@ -25973,7 +25975,7 @@
       <c r="AD284" s="8"/>
       <c r="AE284" s="8"/>
     </row>
-    <row r="285" spans="1:31" ht="331.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:31" ht="331.2" x14ac:dyDescent="0.3">
       <c r="A285" s="8">
         <v>1737</v>
       </c>
@@ -26044,7 +26046,7 @@
       <c r="AD285" s="8"/>
       <c r="AE285" s="8"/>
     </row>
-    <row r="286" spans="1:31" ht="331.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:31" ht="331.2" x14ac:dyDescent="0.3">
       <c r="A286" s="8">
         <v>1738</v>
       </c>
@@ -26117,7 +26119,7 @@
       <c r="AD286" s="8"/>
       <c r="AE286" s="8"/>
     </row>
-    <row r="287" spans="1:31" ht="331.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:31" ht="331.2" x14ac:dyDescent="0.3">
       <c r="A287" s="8">
         <v>1739</v>
       </c>
@@ -26186,7 +26188,7 @@
       <c r="AD287" s="8"/>
       <c r="AE287" s="8"/>
     </row>
-    <row r="288" spans="1:31" ht="331.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:31" ht="331.2" x14ac:dyDescent="0.3">
       <c r="A288" s="8">
         <v>1740</v>
       </c>
@@ -26259,7 +26261,7 @@
       <c r="AD288" s="8"/>
       <c r="AE288" s="8"/>
     </row>
-    <row r="289" spans="1:31" ht="331.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:31" ht="331.2" x14ac:dyDescent="0.3">
       <c r="A289" s="8">
         <v>1741</v>
       </c>
@@ -26328,7 +26330,7 @@
       <c r="AD289" s="8"/>
       <c r="AE289" s="8"/>
     </row>
-    <row r="290" spans="1:31" ht="331.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:31" ht="331.2" x14ac:dyDescent="0.3">
       <c r="A290" s="8">
         <v>1742</v>
       </c>
@@ -26397,7 +26399,7 @@
       <c r="AD290" s="8"/>
       <c r="AE290" s="8"/>
     </row>
-    <row r="291" spans="1:31" ht="331.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:31" ht="331.2" x14ac:dyDescent="0.3">
       <c r="A291" s="8">
         <v>1743</v>
       </c>
@@ -26470,7 +26472,7 @@
       <c r="AD291" s="8"/>
       <c r="AE291" s="8"/>
     </row>
-    <row r="292" spans="1:31" ht="331.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:31" ht="331.2" x14ac:dyDescent="0.3">
       <c r="A292" s="8">
         <v>1744</v>
       </c>
@@ -26541,7 +26543,7 @@
       <c r="AD292" s="8"/>
       <c r="AE292" s="8"/>
     </row>
-    <row r="293" spans="1:31" ht="331.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:31" ht="331.2" x14ac:dyDescent="0.3">
       <c r="A293" s="8">
         <v>1745</v>
       </c>
@@ -26610,7 +26612,7 @@
       <c r="AD293" s="8"/>
       <c r="AE293" s="8"/>
     </row>
-    <row r="294" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A294" s="8">
         <v>1746</v>
       </c>
@@ -26691,7 +26693,7 @@
       <c r="AD294" s="8"/>
       <c r="AE294" s="8"/>
     </row>
-    <row r="295" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A295" s="8">
         <v>1747</v>
       </c>
@@ -26772,7 +26774,7 @@
       <c r="AD295" s="8"/>
       <c r="AE295" s="8"/>
     </row>
-    <row r="296" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A296" s="8">
         <v>1748</v>
       </c>
@@ -26853,7 +26855,7 @@
       <c r="AD296" s="8"/>
       <c r="AE296" s="8"/>
     </row>
-    <row r="297" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A297" s="8">
         <v>1749</v>
       </c>
@@ -26934,7 +26936,7 @@
       <c r="AD297" s="8"/>
       <c r="AE297" s="8"/>
     </row>
-    <row r="298" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A298" s="8">
         <v>1750</v>
       </c>
@@ -27015,7 +27017,7 @@
       <c r="AD298" s="8"/>
       <c r="AE298" s="8"/>
     </row>
-    <row r="299" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A299" s="8">
         <v>1752</v>
       </c>
@@ -27096,7 +27098,7 @@
       <c r="AD299" s="8"/>
       <c r="AE299" s="8"/>
     </row>
-    <row r="300" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A300" s="8">
         <v>1753</v>
       </c>
@@ -27177,7 +27179,7 @@
       <c r="AD300" s="8"/>
       <c r="AE300" s="8"/>
     </row>
-    <row r="301" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A301" s="8">
         <v>1754</v>
       </c>
@@ -27258,7 +27260,7 @@
       <c r="AD301" s="8"/>
       <c r="AE301" s="8"/>
     </row>
-    <row r="302" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A302" s="8">
         <v>1755</v>
       </c>
@@ -27339,7 +27341,7 @@
       <c r="AD302" s="8"/>
       <c r="AE302" s="8"/>
     </row>
-    <row r="303" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A303" s="8">
         <v>1756</v>
       </c>
@@ -27420,7 +27422,7 @@
       <c r="AD303" s="8"/>
       <c r="AE303" s="8"/>
     </row>
-    <row r="304" spans="1:31" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:31" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A304" s="8">
         <v>1759</v>
       </c>
@@ -27491,7 +27493,7 @@
       <c r="AD304" s="8"/>
       <c r="AE304" s="8"/>
     </row>
-    <row r="305" spans="1:31" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:31" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A305" s="8">
         <v>1760</v>
       </c>
@@ -27562,7 +27564,7 @@
       <c r="AD305" s="8"/>
       <c r="AE305" s="8"/>
     </row>
-    <row r="306" spans="1:31" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:31" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A306" s="8">
         <v>1762</v>
       </c>
@@ -27633,7 +27635,7 @@
       <c r="AD306" s="8"/>
       <c r="AE306" s="8"/>
     </row>
-    <row r="307" spans="1:31" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:31" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A307" s="8">
         <v>1763</v>
       </c>
@@ -27706,7 +27708,7 @@
       <c r="AD307" s="8"/>
       <c r="AE307" s="8"/>
     </row>
-    <row r="308" spans="1:31" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:31" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A308" s="8">
         <v>1764</v>
       </c>
@@ -27777,7 +27779,7 @@
       <c r="AD308" s="8"/>
       <c r="AE308" s="8"/>
     </row>
-    <row r="309" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A309" s="8">
         <v>1767</v>
       </c>
@@ -27848,7 +27850,7 @@
       <c r="AD309" s="8"/>
       <c r="AE309" s="8"/>
     </row>
-    <row r="310" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A310" s="8">
         <v>1768</v>
       </c>
@@ -27919,7 +27921,7 @@
       <c r="AD310" s="8"/>
       <c r="AE310" s="8"/>
     </row>
-    <row r="311" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A311" s="8">
         <v>1769</v>
       </c>
@@ -27990,7 +27992,7 @@
       <c r="AD311" s="8"/>
       <c r="AE311" s="8"/>
     </row>
-    <row r="312" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A312" s="8">
         <v>1770</v>
       </c>
@@ -28061,7 +28063,7 @@
       <c r="AD312" s="8"/>
       <c r="AE312" s="8"/>
     </row>
-    <row r="313" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A313" s="8">
         <v>1771</v>
       </c>
@@ -28161,7 +28163,7 @@
       <c r="J314" s="11" t="s">
         <v>953</v>
       </c>
-      <c r="K314" s="8" t="s">
+      <c r="K314" s="11" t="s">
         <v>954</v>
       </c>
       <c r="L314" s="8" t="s">
@@ -28238,7 +28240,7 @@
       <c r="J315" s="11" t="s">
         <v>953</v>
       </c>
-      <c r="K315" s="8" t="s">
+      <c r="K315" s="11" t="s">
         <v>958</v>
       </c>
       <c r="L315" s="8" t="s">
@@ -28317,7 +28319,7 @@
       <c r="J316" s="11" t="s">
         <v>953</v>
       </c>
-      <c r="K316" s="8" t="s">
+      <c r="K316" s="11" t="s">
         <v>961</v>
       </c>
       <c r="L316" s="8" t="s">
@@ -28394,7 +28396,7 @@
       <c r="J317" s="11" t="s">
         <v>953</v>
       </c>
-      <c r="K317" s="8" t="s">
+      <c r="K317" s="11" t="s">
         <v>963</v>
       </c>
       <c r="L317" s="8" t="s">
@@ -28442,7 +28444,7 @@
       <c r="AD317" s="8"/>
       <c r="AE317" s="8"/>
     </row>
-    <row r="318" spans="1:31" ht="409.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:31" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A318" s="8">
         <v>1776</v>
       </c>
@@ -28513,7 +28515,7 @@
       <c r="AD318" s="8"/>
       <c r="AE318" s="8"/>
     </row>
-    <row r="319" spans="1:31" ht="409.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:31" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A319" s="8">
         <v>1777</v>
       </c>
@@ -28584,7 +28586,7 @@
       <c r="AD319" s="8"/>
       <c r="AE319" s="8"/>
     </row>
-    <row r="320" spans="1:31" ht="409.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:31" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A320" s="8">
         <v>1778</v>
       </c>
@@ -28655,7 +28657,7 @@
       <c r="AD320" s="8"/>
       <c r="AE320" s="8"/>
     </row>
-    <row r="321" spans="1:31" ht="230.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:31" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A321" s="8">
         <v>1779</v>
       </c>
@@ -28726,7 +28728,7 @@
       <c r="AD321" s="8"/>
       <c r="AE321" s="8"/>
     </row>
-    <row r="322" spans="1:31" ht="230.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:31" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A322" s="8">
         <v>1780</v>
       </c>
@@ -28795,7 +28797,7 @@
       <c r="AD322" s="8"/>
       <c r="AE322" s="8"/>
     </row>
-    <row r="323" spans="1:31" ht="230.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:31" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A323" s="8">
         <v>1781</v>
       </c>
@@ -28864,7 +28866,7 @@
       <c r="AD323" s="8"/>
       <c r="AE323" s="8"/>
     </row>
-    <row r="324" spans="1:31" ht="230.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:31" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A324" s="8">
         <v>1782</v>
       </c>
@@ -28931,7 +28933,7 @@
       <c r="AD324" s="8"/>
       <c r="AE324" s="8"/>
     </row>
-    <row r="325" spans="1:31" ht="302.39999999999998" hidden="1" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:31" ht="302.39999999999998" x14ac:dyDescent="0.3">
       <c r="A325" s="8">
         <v>1783</v>
       </c>
@@ -29000,7 +29002,7 @@
       <c r="AD325" s="8"/>
       <c r="AE325" s="8"/>
     </row>
-    <row r="326" spans="1:31" ht="302.39999999999998" hidden="1" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:31" ht="302.39999999999998" x14ac:dyDescent="0.3">
       <c r="A326" s="8">
         <v>1784</v>
       </c>
@@ -29067,7 +29069,7 @@
       <c r="AD326" s="8"/>
       <c r="AE326" s="8"/>
     </row>
-    <row r="327" spans="1:31" ht="302.39999999999998" hidden="1" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:31" ht="302.39999999999998" x14ac:dyDescent="0.3">
       <c r="A327" s="8">
         <v>1785</v>
       </c>
@@ -29134,7 +29136,7 @@
       <c r="AD327" s="8"/>
       <c r="AE327" s="8"/>
     </row>
-    <row r="328" spans="1:31" ht="409.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:31" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A328" s="8">
         <v>1792</v>
       </c>
@@ -29201,7 +29203,7 @@
       <c r="AD328" s="8"/>
       <c r="AE328" s="8"/>
     </row>
-    <row r="329" spans="1:31" ht="409.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:31" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A329" s="8">
         <v>1793</v>
       </c>
@@ -29268,7 +29270,7 @@
       <c r="AD329" s="8"/>
       <c r="AE329" s="8"/>
     </row>
-    <row r="330" spans="1:31" ht="409.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:31" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A330" s="8">
         <v>1794</v>
       </c>
@@ -29335,7 +29337,7 @@
       <c r="AD330" s="8"/>
       <c r="AE330" s="8"/>
     </row>
-    <row r="331" spans="1:31" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:31" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A331" s="8">
         <v>1795</v>
       </c>
@@ -29406,7 +29408,7 @@
       <c r="AD331" s="8"/>
       <c r="AE331" s="8"/>
     </row>
-    <row r="332" spans="1:31" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:31" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A332" s="8">
         <v>1796</v>
       </c>
@@ -29477,7 +29479,7 @@
       <c r="AD332" s="8"/>
       <c r="AE332" s="8"/>
     </row>
-    <row r="333" spans="1:31" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:31" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A333" s="8">
         <v>1797</v>
       </c>
@@ -29548,7 +29550,7 @@
       <c r="AD333" s="8"/>
       <c r="AE333" s="8"/>
     </row>
-    <row r="334" spans="1:31" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:31" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A334" s="8">
         <v>1798</v>
       </c>
@@ -29621,7 +29623,7 @@
       <c r="AD334" s="8"/>
       <c r="AE334" s="8"/>
     </row>
-    <row r="335" spans="1:31" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:31" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A335" s="8">
         <v>1799</v>
       </c>
@@ -29692,7 +29694,7 @@
       <c r="AD335" s="8"/>
       <c r="AE335" s="8"/>
     </row>
-    <row r="336" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A336" s="8">
         <v>1800</v>
       </c>
@@ -29761,7 +29763,7 @@
       <c r="AD336" s="8"/>
       <c r="AE336" s="8"/>
     </row>
-    <row r="337" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A337" s="8">
         <v>1801</v>
       </c>
@@ -29828,7 +29830,7 @@
       <c r="AD337" s="8"/>
       <c r="AE337" s="8"/>
     </row>
-    <row r="338" spans="1:31" ht="144" hidden="1" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:31" ht="144" x14ac:dyDescent="0.3">
       <c r="A338" s="8">
         <v>1811</v>
       </c>
@@ -29899,7 +29901,7 @@
       <c r="AD338" s="8"/>
       <c r="AE338" s="8"/>
     </row>
-    <row r="339" spans="1:31" ht="144" hidden="1" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:31" ht="144" x14ac:dyDescent="0.3">
       <c r="A339" s="8">
         <v>1812</v>
       </c>
@@ -29970,7 +29972,7 @@
       <c r="AD339" s="8"/>
       <c r="AE339" s="8"/>
     </row>
-    <row r="340" spans="1:31" ht="144" hidden="1" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:31" ht="144" x14ac:dyDescent="0.3">
       <c r="A340" s="8">
         <v>1813</v>
       </c>
@@ -30039,7 +30041,7 @@
       <c r="AD340" s="8"/>
       <c r="AE340" s="8"/>
     </row>
-    <row r="341" spans="1:31" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:31" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A341" s="8">
         <v>1814</v>
       </c>
@@ -30112,7 +30114,7 @@
       <c r="AD341" s="8"/>
       <c r="AE341" s="8"/>
     </row>
-    <row r="342" spans="1:31" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:31" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A342" s="8">
         <v>1815</v>
       </c>
@@ -30185,7 +30187,7 @@
       <c r="AD342" s="8"/>
       <c r="AE342" s="8"/>
     </row>
-    <row r="343" spans="1:31" ht="72" hidden="1" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:31" ht="72" x14ac:dyDescent="0.3">
       <c r="A343" s="8">
         <v>1816</v>
       </c>
@@ -30258,7 +30260,7 @@
       <c r="AD343" s="8"/>
       <c r="AE343" s="8"/>
     </row>
-    <row r="344" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A344" s="8">
         <v>1817</v>
       </c>
@@ -30329,7 +30331,7 @@
       <c r="AD344" s="8"/>
       <c r="AE344" s="8"/>
     </row>
-    <row r="345" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A345" s="8">
         <v>1818</v>
       </c>
@@ -30402,7 +30404,7 @@
       <c r="AD345" s="8"/>
       <c r="AE345" s="8"/>
     </row>
-    <row r="346" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A346" s="8">
         <v>1819</v>
       </c>
@@ -30473,7 +30475,7 @@
       <c r="AD346" s="8"/>
       <c r="AE346" s="8"/>
     </row>
-    <row r="347" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A347" s="8">
         <v>1820</v>
       </c>
@@ -30544,7 +30546,7 @@
       <c r="AD347" s="8"/>
       <c r="AE347" s="8"/>
     </row>
-    <row r="348" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A348" s="8">
         <v>1821</v>
       </c>
@@ -30615,7 +30617,7 @@
       <c r="AD348" s="8"/>
       <c r="AE348" s="8"/>
     </row>
-    <row r="349" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A349" s="8">
         <v>1822</v>
       </c>
@@ -30688,7 +30690,7 @@
       <c r="AD349" s="8"/>
       <c r="AE349" s="8"/>
     </row>
-    <row r="350" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A350" s="8">
         <v>1823</v>
       </c>
@@ -30759,7 +30761,7 @@
       <c r="AD350" s="8"/>
       <c r="AE350" s="8"/>
     </row>
-    <row r="351" spans="1:31" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:31" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A351" s="8">
         <v>1824</v>
       </c>
@@ -30830,7 +30832,7 @@
       <c r="AD351" s="8"/>
       <c r="AE351" s="8"/>
     </row>
-    <row r="352" spans="1:31" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:31" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A352" s="8">
         <v>1825</v>
       </c>
@@ -30903,7 +30905,7 @@
       <c r="AD352" s="8"/>
       <c r="AE352" s="8"/>
     </row>
-    <row r="353" spans="1:31" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:31" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A353" s="8">
         <v>1826</v>
       </c>
@@ -30974,7 +30976,7 @@
       <c r="AD353" s="8"/>
       <c r="AE353" s="8"/>
     </row>
-    <row r="354" spans="1:31" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:31" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A354" s="8">
         <v>1827</v>
       </c>
@@ -31043,7 +31045,7 @@
       <c r="AD354" s="8"/>
       <c r="AE354" s="8"/>
     </row>
-    <row r="355" spans="1:31" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:31" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A355" s="8">
         <v>1828</v>
       </c>
@@ -31112,7 +31114,7 @@
       <c r="AD355" s="8"/>
       <c r="AE355" s="8"/>
     </row>
-    <row r="356" spans="1:31" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:31" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A356" s="8">
         <v>1829</v>
       </c>
@@ -31181,7 +31183,7 @@
       <c r="AD356" s="8"/>
       <c r="AE356" s="8"/>
     </row>
-    <row r="357" spans="1:31" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:31" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A357" s="8">
         <v>1830</v>
       </c>
@@ -31250,7 +31252,7 @@
       <c r="AD357" s="8"/>
       <c r="AE357" s="8"/>
     </row>
-    <row r="358" spans="1:31" ht="115.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:31" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A358" s="8">
         <v>1831</v>
       </c>
@@ -31321,7 +31323,7 @@
       <c r="AD358" s="8"/>
       <c r="AE358" s="8"/>
     </row>
-    <row r="359" spans="1:31" ht="115.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:31" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A359" s="8">
         <v>1832</v>
       </c>
@@ -31392,7 +31394,7 @@
       <c r="AD359" s="8"/>
       <c r="AE359" s="8"/>
     </row>
-    <row r="360" spans="1:31" ht="115.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:31" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A360" s="8">
         <v>1833</v>
       </c>
@@ -31463,7 +31465,7 @@
       <c r="AD360" s="8"/>
       <c r="AE360" s="8"/>
     </row>
-    <row r="361" spans="1:31" ht="115.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:31" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A361" s="8">
         <v>1834</v>
       </c>
@@ -31534,7 +31536,7 @@
       <c r="AD361" s="8"/>
       <c r="AE361" s="8"/>
     </row>
-    <row r="362" spans="1:31" ht="115.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:31" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A362" s="8">
         <v>1835</v>
       </c>
@@ -31605,7 +31607,7 @@
       <c r="AD362" s="8"/>
       <c r="AE362" s="8"/>
     </row>
-    <row r="363" spans="1:31" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:31" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A363" s="8">
         <v>1836</v>
       </c>
@@ -31676,7 +31678,7 @@
       <c r="AD363" s="8"/>
       <c r="AE363" s="8"/>
     </row>
-    <row r="364" spans="1:31" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:31" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A364" s="8">
         <v>1837</v>
       </c>
@@ -31747,7 +31749,7 @@
       <c r="AD364" s="8"/>
       <c r="AE364" s="8"/>
     </row>
-    <row r="365" spans="1:31" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:31" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A365" s="8">
         <v>1838</v>
       </c>
@@ -31818,7 +31820,7 @@
       <c r="AD365" s="8"/>
       <c r="AE365" s="8"/>
     </row>
-    <row r="366" spans="1:31" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:31" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A366" s="8">
         <v>1839</v>
       </c>
@@ -31889,7 +31891,7 @@
       <c r="AD366" s="8"/>
       <c r="AE366" s="8"/>
     </row>
-    <row r="367" spans="1:31" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:31" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A367" s="8">
         <v>1840</v>
       </c>
@@ -31960,7 +31962,7 @@
       <c r="AD367" s="8"/>
       <c r="AE367" s="8"/>
     </row>
-    <row r="368" spans="1:31" ht="115.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:31" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A368" s="8">
         <v>1841</v>
       </c>
@@ -32033,7 +32035,7 @@
       <c r="AD368" s="8"/>
       <c r="AE368" s="8"/>
     </row>
-    <row r="369" spans="1:31" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:31" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A369" s="8">
         <v>1842</v>
       </c>
@@ -32102,7 +32104,7 @@
       <c r="AD369" s="8"/>
       <c r="AE369" s="8"/>
     </row>
-    <row r="370" spans="1:31" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:31" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A370" s="8">
         <v>1843</v>
       </c>
@@ -32173,7 +32175,7 @@
       <c r="AD370" s="8"/>
       <c r="AE370" s="8"/>
     </row>
-    <row r="371" spans="1:31" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:31" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A371" s="8">
         <v>1844</v>
       </c>
@@ -32242,7 +32244,7 @@
       <c r="AD371" s="8"/>
       <c r="AE371" s="8"/>
     </row>
-    <row r="372" spans="1:31" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:31" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A372" s="8">
         <v>1845</v>
       </c>
@@ -32311,7 +32313,7 @@
       <c r="AD372" s="8"/>
       <c r="AE372" s="8"/>
     </row>
-    <row r="373" spans="1:31" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:31" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A373" s="8">
         <v>1846</v>
       </c>
@@ -32380,7 +32382,7 @@
       <c r="AD373" s="8"/>
       <c r="AE373" s="8"/>
     </row>
-    <row r="374" spans="1:31" ht="115.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:31" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A374" s="8">
         <v>1847</v>
       </c>
@@ -32453,7 +32455,7 @@
       <c r="AD374" s="8"/>
       <c r="AE374" s="8"/>
     </row>
-    <row r="375" spans="1:31" ht="115.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:31" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A375" s="8">
         <v>1848</v>
       </c>
@@ -32526,7 +32528,7 @@
       <c r="AD375" s="8"/>
       <c r="AE375" s="8"/>
     </row>
-    <row r="376" spans="1:31" ht="115.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:31" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A376" s="8">
         <v>1849</v>
       </c>
@@ -32595,7 +32597,7 @@
       <c r="AD376" s="8"/>
       <c r="AE376" s="8"/>
     </row>
-    <row r="377" spans="1:31" ht="115.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:31" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A377" s="8">
         <v>1850</v>
       </c>
@@ -32668,7 +32670,7 @@
       <c r="AD377" s="8"/>
       <c r="AE377" s="8"/>
     </row>
-    <row r="378" spans="1:31" ht="115.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:31" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A378" s="8">
         <v>1851</v>
       </c>
@@ -32737,7 +32739,7 @@
       <c r="AD378" s="8"/>
       <c r="AE378" s="8"/>
     </row>
-    <row r="379" spans="1:31" ht="115.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:31" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A379" s="8">
         <v>1852</v>
       </c>
@@ -32812,7 +32814,7 @@
       <c r="AD379" s="8"/>
       <c r="AE379" s="8"/>
     </row>
-    <row r="380" spans="1:31" ht="115.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:31" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A380" s="8">
         <v>1853</v>
       </c>
@@ -32883,7 +32885,7 @@
       <c r="AD380" s="8"/>
       <c r="AE380" s="8"/>
     </row>
-    <row r="381" spans="1:31" ht="115.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:31" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A381" s="8">
         <v>1854</v>
       </c>
@@ -32952,7 +32954,7 @@
       <c r="AD381" s="8"/>
       <c r="AE381" s="8"/>
     </row>
-    <row r="382" spans="1:31" ht="115.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:31" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A382" s="8">
         <v>1855</v>
       </c>
@@ -33021,7 +33023,7 @@
       <c r="AD382" s="8"/>
       <c r="AE382" s="8"/>
     </row>
-    <row r="383" spans="1:31" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:31" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A383" s="8">
         <v>1856</v>
       </c>
@@ -33092,7 +33094,7 @@
       <c r="AD383" s="8"/>
       <c r="AE383" s="8"/>
     </row>
-    <row r="384" spans="1:31" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:31" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A384" s="8">
         <v>1857</v>
       </c>
@@ -33165,7 +33167,7 @@
       <c r="AD384" s="8"/>
       <c r="AE384" s="8"/>
     </row>
-    <row r="385" spans="1:31" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:31" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A385" s="8">
         <v>1858</v>
       </c>
@@ -33238,7 +33240,7 @@
       <c r="AD385" s="8"/>
       <c r="AE385" s="8"/>
     </row>
-    <row r="386" spans="1:31" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:31" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A386" s="8">
         <v>1859</v>
       </c>
@@ -33309,7 +33311,7 @@
       <c r="AD386" s="8"/>
       <c r="AE386" s="8"/>
     </row>
-    <row r="387" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A387" s="8">
         <v>1860</v>
       </c>
@@ -33380,7 +33382,7 @@
       <c r="AD387" s="8"/>
       <c r="AE387" s="8"/>
     </row>
-    <row r="388" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A388" s="8">
         <v>1862</v>
       </c>
@@ -33447,7 +33449,7 @@
       <c r="AD388" s="8"/>
       <c r="AE388" s="8"/>
     </row>
-    <row r="389" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A389" s="8">
         <v>1863</v>
       </c>
@@ -33514,7 +33516,7 @@
       <c r="AD389" s="8"/>
       <c r="AE389" s="8"/>
     </row>
-    <row r="390" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A390" s="8">
         <v>1864</v>
       </c>
@@ -33581,7 +33583,7 @@
       <c r="AD390" s="8"/>
       <c r="AE390" s="8"/>
     </row>
-    <row r="391" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A391" s="8">
         <v>1866</v>
       </c>
@@ -33652,7 +33654,7 @@
       <c r="AD391" s="8"/>
       <c r="AE391" s="8"/>
     </row>
-    <row r="392" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A392" s="8">
         <v>1867</v>
       </c>
@@ -33723,7 +33725,7 @@
       <c r="AD392" s="8"/>
       <c r="AE392" s="8"/>
     </row>
-    <row r="393" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A393" s="8">
         <v>1868</v>
       </c>
@@ -33794,7 +33796,7 @@
       <c r="AD393" s="8"/>
       <c r="AE393" s="8"/>
     </row>
-    <row r="394" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A394" s="8">
         <v>1869</v>
       </c>
@@ -33861,7 +33863,7 @@
       <c r="AD394" s="8"/>
       <c r="AE394" s="8"/>
     </row>
-    <row r="395" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A395" s="8">
         <v>1870</v>
       </c>
@@ -33928,7 +33930,7 @@
       <c r="AD395" s="8"/>
       <c r="AE395" s="8"/>
     </row>
-    <row r="396" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A396" s="8">
         <v>1872</v>
       </c>
@@ -33999,7 +34001,7 @@
       <c r="AD396" s="8"/>
       <c r="AE396" s="8"/>
     </row>
-    <row r="397" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A397" s="8">
         <v>1873</v>
       </c>
@@ -34070,7 +34072,7 @@
       <c r="AD397" s="8"/>
       <c r="AE397" s="8"/>
     </row>
-    <row r="398" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A398" s="8">
         <v>1874</v>
       </c>
@@ -34137,7 +34139,7 @@
       <c r="AD398" s="8"/>
       <c r="AE398" s="8"/>
     </row>
-    <row r="399" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A399" s="8">
         <v>1875</v>
       </c>
@@ -34204,7 +34206,7 @@
       <c r="AD399" s="8"/>
       <c r="AE399" s="8"/>
     </row>
-    <row r="400" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A400" s="8">
         <v>1876</v>
       </c>
@@ -34271,7 +34273,7 @@
       <c r="AD400" s="8"/>
       <c r="AE400" s="8"/>
     </row>
-    <row r="401" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A401" s="8">
         <v>1877</v>
       </c>
@@ -34338,7 +34340,7 @@
       <c r="AD401" s="8"/>
       <c r="AE401" s="8"/>
     </row>
-    <row r="402" spans="1:31" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:31" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A402" s="8">
         <v>1878</v>
       </c>
@@ -34409,7 +34411,7 @@
       <c r="AD402" s="8"/>
       <c r="AE402" s="8"/>
     </row>
-    <row r="403" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A403" s="8">
         <v>1879</v>
       </c>
@@ -34480,7 +34482,7 @@
       <c r="AD403" s="8"/>
       <c r="AE403" s="8"/>
     </row>
-    <row r="404" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A404" s="8">
         <v>1880</v>
       </c>
@@ -34547,7 +34549,7 @@
       <c r="AD404" s="8"/>
       <c r="AE404" s="8"/>
     </row>
-    <row r="405" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A405" s="8">
         <v>1881</v>
       </c>
@@ -34614,7 +34616,7 @@
       <c r="AD405" s="8"/>
       <c r="AE405" s="8"/>
     </row>
-    <row r="406" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A406" s="8">
         <v>1882</v>
       </c>
@@ -34681,7 +34683,7 @@
       <c r="AD406" s="8"/>
       <c r="AE406" s="8"/>
     </row>
-    <row r="407" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A407" s="8">
         <v>1883</v>
       </c>
@@ -34748,7 +34750,7 @@
       <c r="AD407" s="8"/>
       <c r="AE407" s="8"/>
     </row>
-    <row r="408" spans="1:31" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:31" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A408" s="8">
         <v>1885</v>
       </c>
@@ -34817,7 +34819,7 @@
       <c r="AD408" s="8"/>
       <c r="AE408" s="8"/>
     </row>
-    <row r="409" spans="1:31" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:31" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A409" s="8">
         <v>1886</v>
       </c>
@@ -34886,7 +34888,7 @@
       <c r="AD409" s="8"/>
       <c r="AE409" s="8"/>
     </row>
-    <row r="410" spans="1:31" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:31" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A410" s="8">
         <v>1887</v>
       </c>
@@ -34955,7 +34957,7 @@
       <c r="AD410" s="8"/>
       <c r="AE410" s="8"/>
     </row>
-    <row r="411" spans="1:31" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:31" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A411" s="8">
         <v>1888</v>
       </c>
@@ -35024,7 +35026,7 @@
       <c r="AD411" s="8"/>
       <c r="AE411" s="8"/>
     </row>
-    <row r="412" spans="1:31" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:31" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A412" s="8">
         <v>1889</v>
       </c>
@@ -35091,7 +35093,7 @@
       <c r="AD412" s="8"/>
       <c r="AE412" s="8"/>
     </row>
-    <row r="413" spans="1:31" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:31" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A413" s="8">
         <v>1890</v>
       </c>
@@ -35160,7 +35162,7 @@
       <c r="AD413" s="8"/>
       <c r="AE413" s="8"/>
     </row>
-    <row r="414" spans="1:31" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:31" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A414" s="8">
         <v>1891</v>
       </c>
@@ -35229,7 +35231,7 @@
       <c r="AD414" s="8"/>
       <c r="AE414" s="8"/>
     </row>
-    <row r="415" spans="1:31" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:31" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A415" s="8">
         <v>1892</v>
       </c>
@@ -35298,7 +35300,7 @@
       <c r="AD415" s="8"/>
       <c r="AE415" s="8"/>
     </row>
-    <row r="416" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A416" s="8">
         <v>1893</v>
       </c>
@@ -35367,7 +35369,7 @@
       <c r="AD416" s="8"/>
       <c r="AE416" s="8"/>
     </row>
-    <row r="417" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A417" s="8">
         <v>1894</v>
       </c>
@@ -35434,7 +35436,7 @@
       <c r="AD417" s="8"/>
       <c r="AE417" s="8"/>
     </row>
-    <row r="418" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A418" s="8">
         <v>1895</v>
       </c>
@@ -35501,7 +35503,7 @@
       <c r="AD418" s="8"/>
       <c r="AE418" s="8"/>
     </row>
-    <row r="419" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A419" s="8">
         <v>1896</v>
       </c>
@@ -35568,7 +35570,7 @@
       <c r="AD419" s="8"/>
       <c r="AE419" s="8"/>
     </row>
-    <row r="420" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A420" s="8">
         <v>1897</v>
       </c>
@@ -35637,7 +35639,7 @@
       <c r="AD420" s="8"/>
       <c r="AE420" s="8"/>
     </row>
-    <row r="421" spans="1:31" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:31" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A421" s="8">
         <v>1898</v>
       </c>
@@ -35706,7 +35708,7 @@
       <c r="AD421" s="8"/>
       <c r="AE421" s="8"/>
     </row>
-    <row r="422" spans="1:31" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:31" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A422" s="3">
         <v>1899</v>
       </c>
@@ -35777,13 +35779,6 @@
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
-  <autoFilter ref="A1:AE422" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="8">
-      <filters>
-        <filter val="440"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>